--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-678.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.0%</t>
+          <t>449.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.2%</t>
+          <t>-551.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-271.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.3%</t>
+          <t>-180.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-209.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-172.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-199.0%</t>
+          <t>-205.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-83.0%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.2177198195886446</v>
+        <v>0.3537084394200811</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.205221693012986</v>
+        <v>3.259617140945561</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.08127492936123193</v>
+        <v>0.2172635491926684</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.154723719543688</v>
+        <v>3.209119167476263</v>
       </c>
       <c r="F1838" t="n">
         <v>1.568940374610322</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1558565624885632</v>
+        <v>-0.01986794265712671</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.094812207301312</v>
+        <v>3.149207655233886</v>
       </c>
       <c r="F1839" t="n">
         <v>1.568940374610322</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1508189717609766</v>
+        <v>-0.01483035192954019</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.095404683777685</v>
+        <v>3.149800131710259</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.4080130064690334</v>
+        <v>-0.2720243866375969</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.971273451518199</v>
+        <v>3.025668899450773</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.4737803965184454</v>
+        <v>-0.337791776687009</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.945984104628904</v>
+        <v>3.000379552561479</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.67902507357569</v>
+        <v>-0.5430364537442536</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.854514265793762</v>
+        <v>2.908909713726337</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.7607969740034417</v>
+        <v>-0.6248083541720053</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.8118882315779</v>
+        <v>2.866283679510474</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8280060818753194</v>
+        <v>-0.692017462043883</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.789769905262851</v>
+        <v>2.844165353195425</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.035571866266931</v>
+        <v>-0.8995832464354949</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.704568387625446</v>
+        <v>2.758963835558021</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.453325889813768</v>
+        <v>-1.317337269982332</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.535393669711775</v>
+        <v>2.589789117644349</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.7434575564192</v>
+        <v>-1.607468936587763</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.419207219668524</v>
+        <v>2.473602667601098</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.951461614772277</v>
+        <v>-1.815472994940841</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.340897740881218</v>
+        <v>2.395293188813793</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.162874035660252</v>
+        <v>-2.026885415828816</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.305809676796591</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.528942762804905</v>
+        <v>-2.392954142973469</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.152466485245179</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.737433544256589</v>
+        <v>-2.601444924425153</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>2.089408462403274</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.984634729021811</v>
+        <v>-2.848646109190375</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>1.998626738905753</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.477019757045908</v>
+        <v>-3.341031137214471</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.802779119739847</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.86220014797598</v>
+        <v>-3.726211528144544</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.647249502180681</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.112070827990562</v>
+        <v>-3.976082208159125</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.549070353629465</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.318582604877583</v>
+        <v>-4.182593985046147</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.462571701530914</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.637926679958085</v>
+        <v>-4.501938060126649</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.336606998198973</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-4.933743853276436</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.150217568406462</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.168437847408988</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>1.044624745755532</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.504100494639441</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.9089402785193159</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-5.867726739539754</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.7699773407934325</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.232854122178501</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.6231809027437651</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.641442899359179</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.4585069358862528</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-6.918018999675011</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.3430619282313803</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.334410873962009</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.174499229125459</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.578682274689078</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.08704935950331016</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.783933293925839</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>0.001048516954301082</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-7.947513172110222</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.06597851426445134</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.24417451392042</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.1808640750593224</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.430894222229723</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.2595782629174468</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.813895610972354</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.4128809197360832</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-8.995765401957389</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.4830573201586668</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.35529572446139</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.6215191458622176</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.405644787915612</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.6337427512867286</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.503264065337008</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.6697487116335181</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937501</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.650790153342651</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.7258655905142031</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141704</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-9.855048328672515</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.8020556635275065</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729893</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-9.929381304932679</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.8273062995471361</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440636</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-9.85591147326523</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.7825466653867355</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.03103589065177</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.8380412115938363</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.26548798466626</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-0.9390412141012274</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.36986271569271</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-0.9874632972857822</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.42264887129304</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.007461969687357</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297401</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.54868566466133</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.055182958405558</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322546</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.49667015069251</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.030386417131631</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.63834199241663</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.088530380720021</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940722</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.5887511479918</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.053640632785215</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770583</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.57594375498702</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.061568809229989</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615287</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.35009860226761</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-0.9616516751060167</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812106</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.22551994593002</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.9106810680149207</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646221</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.27841523397431</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9292054090705273</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611572</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.20628205868643</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.8946184347167385</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955332</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.13491566607678</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.8758091400667452</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.04145663209156</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.8483090077855624</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436234</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.774214831223158</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.7432468479375776</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311954</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.676307792546668</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.7043843474404419</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409725</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.65235425157071</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.6941344249045653</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017778</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.388294313247913</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.6017707657371987</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783973</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.681214689743076</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.3217259499955647</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388735</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.641030391376885</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.3053086067612472</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626481</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.477630520437522</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.2405818371647448</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291817</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.244149298207923</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.1392649194350524</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785793</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.094482907200408</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.08229057334500611</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390433</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-7.962207433569522</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.03401289714562461</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105957</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.80646910100978</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>0.03109749656590921</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960992</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.557469302326199</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.143603757263</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607651</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.663059292099303</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.0266081682454602</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.77042258398791</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.6817941942179</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>0.01444221278418745</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710817</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.533854152810301</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.04626069334094041</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.72356622940921</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.480884630556313</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.03378687069282327</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098114</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.437336223785622</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.02332812007964025</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493425</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.195187830331764</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.0879935916830461</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722821</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.086928693209242</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.1258293669912498</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82805292879205</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-6.963637558392112</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.1726439149286789</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919912</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-6.942488359488668</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.1888045727273813</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318098</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.698722917505224</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.2820914578678098</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057531</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.596960097227929</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.3249208998987436</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279191</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.347109703278854</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.4176031324620757</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011504</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.171217610811421</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.4915590929696978</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392992</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-5.999771147788958</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.5734651842332368</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632787</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-5.925481582050619</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.6022014881448694</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988308</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-5.861845839816684</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.6323505860927607</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107479</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.750419080490764</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.6581155486069243</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242302</v>
+        <v>3.797694884242298</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.509988583685904</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.7560308239537457</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367692</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.437746015514709</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.7888571650570437</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879973</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.384747693233321</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.8107350778869389</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502345</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.275942807753594</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.8512551032988234</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675947</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.055922009716584</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.9408424595242417</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539958</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-4.923054320653306</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>1.009883717951376</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496266</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.802881237288807</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>1.059098795737477</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577003</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.65820909218907</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.127055756338812</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942108</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.718083919546762</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.089143316797161</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767452</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.631284421767754</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.146263609231331</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430699</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.63375412822956</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.14534812802002</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003608</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.70212431455357</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.129006975965118</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508376</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.715912367400617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.113928463458191</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417711</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.746905526729322</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.9262407647670954</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205906</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.571431266936854</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>1.000997700675871</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225451</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.682367519578102</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.9323652283805783</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.7732102971113</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.64870397410582</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.9489620317893968</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434395226417</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.588851354902097</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>0.9830754659030183</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742306</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.502607891875719</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>1.01251912168743</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316053</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.547914711274699</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>0.9861721693723633</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803198</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.576947815977</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>0.9751108005245444</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809504</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.484137334526141</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.941507684996254</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.528526803855568</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.9256253731890838</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.415855585619318</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.9657695689953067</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.303478584436645</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>1.016211665299043</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.331258982337998</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>1.016596707907041</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705332</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.414260263363277</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.821751915497583</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729277</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.522874341806608</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.8984559448394562</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190776</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.487465303558465</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.9271325862410362</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913433</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.449081641000314</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.9399054926066654</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532494</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.271965310965148</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>1.007481053466034</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793912</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.317057555798693</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>0.9901275472945286</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011244</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.137682134559926</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>1.05566469109645</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982238</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.182696348080531</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>1.018466461019798</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509547</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.449700858352966</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.9173562192497693</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760818</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.550898639790139</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.8760810285714016</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.680376293007264</v>
+        <v>-4.544387673175827</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8218899288388686</v>
+        <v>0.8762853767714434</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.661338165299966</v>
+        <v>-4.525349545468529</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8260298991300323</v>
+        <v>0.8804253470626071</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131258</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.692464796450585</v>
+        <v>-4.556476176619148</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9911611156084654</v>
+        <v>1.04555656354104</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.706331557784503</v>
+        <v>-4.570342937953066</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9864477400610319</v>
+        <v>1.040843187993607</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789131</v>
+        <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.661527386244573</v>
+        <v>-4.525538766413136</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.01037793907393</v>
+        <v>1.064773387006505</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519918</v>
+        <v>3.781501250519917</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.51378441600957</v>
+        <v>-4.377795796178133</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.148627774959953</v>
+        <v>1.203023222892527</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918118</v>
+        <v>3.802245929181179</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.615799098540792</v>
+        <v>-4.479810478709354</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110615523478945</v>
+        <v>1.16501097141152</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539474</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.609646392488007</v>
+        <v>-4.47365777265657</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113738954291717</v>
+        <v>1.168134402224292</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890617</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.626455690638509</v>
+        <v>-4.490467070807072</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.106095711771627</v>
+        <v>1.160491159704202</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.564157691862387</v>
+        <v>-4.42816907203095</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.197350465078897</v>
+        <v>1.251745913011471</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.362367494197229</v>
+        <v>-4.226378874365792</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9866474165343577</v>
+        <v>1.041042864466933</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852431</v>
+        <v>3.84144481785243</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.288989397108493</v>
+        <v>-4.153000777277056</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.086288887692028</v>
+        <v>1.140684335624602</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.08018922680401847</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319556</v>
+        <v>3.819063300319555</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.386729941733467</v>
+        <v>-4.25074132190203</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.061820405958081</v>
+        <v>1.116215853890656</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.09607850493699865</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489395</v>
+        <v>3.831819032489394</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.563067701856396</v>
+        <v>-4.427079082024959</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9898212827335813</v>
+        <v>1.044216730666156</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2724162650599281</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397804</v>
+        <v>3.836411672397803</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.48664565542447</v>
+        <v>-4.350657035593033</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.018881719346281</v>
+        <v>1.073277167278855</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2724162650599281</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024972</v>
+        <v>3.836023391024971</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.442272523785901</v>
+        <v>-4.306283903954464</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.036493839437144</v>
+        <v>1.090889287369719</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2280431334213595</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863233</v>
+        <v>3.821591150863232</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.434318553491129</v>
+        <v>-4.298329933659692</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.039675427555053</v>
+        <v>1.094070875487628</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2280431334213595</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947592</v>
+        <v>3.83304018194759</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.386662822930073</v>
+        <v>-4.250674203098636</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06511947680728</v>
+        <v>1.119514924739855</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1803874028603038</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.286144664431318</v>
+        <v>-4.150156044599881</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.110219113581507</v>
+        <v>1.164614561514082</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.07986924436154924</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314559</v>
+        <v>3.828837911314558</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.346811254833707</v>
+        <v>-4.21082263500227</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.072707149896424</v>
+        <v>1.127102597828998</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1615675610800829</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690034</v>
+        <v>3.816866067690033</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.301972853225308</v>
+        <v>-4.165984233393871</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.094740213150412</v>
+        <v>1.149135661082986</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1570241281352134</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674318</v>
+        <v>3.817961388674317</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.402731488982306</v>
+        <v>-4.266742869150869</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.05859769847869</v>
+        <v>1.112993146411265</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2458496968622189</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163227</v>
+        <v>3.826713779163226</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.358528651896406</v>
+        <v>-4.222540032064969</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.082158435840888</v>
+        <v>1.136553883773463</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.2016468597763184</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022912</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.395507679559849</v>
+        <v>-4.259519059728412</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.065776825244758</v>
+        <v>1.120172273177333</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1646729579849879</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042146</v>
+        <v>3.863924114042145</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.415565758424689</v>
+        <v>-4.279577138593252</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.109001358881861</v>
+        <v>1.163396806814436</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1646729579849879</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078289</v>
+        <v>3.865367715078287</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.375635085246799</v>
+        <v>-4.239646465415362</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.123414332747271</v>
+        <v>1.177809780679846</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1247422848070975</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232406</v>
+        <v>3.864518876232404</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.324602992524271</v>
+        <v>-4.188614372692834</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.138775398074552</v>
+        <v>1.193170846007127</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.07371019208456958</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162122</v>
+        <v>3.84257639416212</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.259378811397066</v>
+        <v>-4.123390191565629</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.182052474618139</v>
+        <v>1.236447922550714</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.008486010957363954</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639826</v>
+        <v>3.840090220639824</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.221951791325932</v>
+        <v>-4.085963171494495</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.192984254945873</v>
+        <v>1.247379702878448</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.003234472928182297</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274993</v>
+        <v>3.845198842749928</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.24206344736064</v>
+        <v>-4.106074827529203</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.18619638486323</v>
+        <v>1.240591832795805</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0077928720692369</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393556</v>
+        <v>3.828690479393554</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.188318632933435</v>
+        <v>-4.052330013101998</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.368252081655323</v>
+        <v>1.422647529587898</v>
       </c>
       <c r="F1991" t="n">
         <v>0.01785618150969887</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714894</v>
+        <v>3.813251854714892</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.164527064327293</v>
+        <v>-4.028538444495856</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.497881618315597</v>
+        <v>1.552277066248172</v>
       </c>
       <c r="F1992" t="n">
         <v>0.04164775011584115</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175602</v>
+        <v>3.814259761756018</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.138442980063485</v>
+        <v>-4.002454360232049</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.500023228034979</v>
+        <v>1.554418675967554</v>
       </c>
       <c r="F1993" t="n">
         <v>0.04164775011584115</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.008150449133876</v>
+        <v>-3.872161829302439</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.550333435990602</v>
+        <v>1.604728883923177</v>
       </c>
       <c r="F1994" t="n">
         <v>0.278183374643576</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.999257987740592</v>
+        <v>-3.863269367909156</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.571444826274707</v>
+        <v>1.625840274207281</v>
       </c>
       <c r="F1995" t="n">
         <v>0.278183374643576</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.167734104710469</v>
+        <v>-4.031745484879034</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.49590942689134</v>
+        <v>1.550304874823915</v>
       </c>
       <c r="F1996" t="n">
         <v>0.2502355389269952</v>
@@ -47482,10 +47482,10 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.469934575848886</v>
+        <v>-3.33394595601745</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.756298935623835</v>
+        <v>1.81069438355641</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1798874795565845</v>
@@ -47505,10 +47505,10 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.447213472165733</v>
+        <v>-3.311224852334298</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.756051399594001</v>
+        <v>1.810446847526575</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1798874795565845</v>
@@ -47528,10 +47528,10 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.44548842887569</v>
+        <v>-3.309499809044254</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.915647542761187</v>
+        <v>1.970042990693762</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1816125228466282</v>
@@ -47551,10 +47551,10 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.600269435653945</v>
+        <v>-3.46428081582251</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.890812962543532</v>
+        <v>1.945208410476106</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1482448487921521</v>
@@ -47574,10 +47574,10 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.667529879675862</v>
+        <v>-3.531541259844427</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.86058414092431</v>
+        <v>1.914979588856885</v>
       </c>
       <c r="F2001" t="n">
         <v>0.080984404770235</v>
@@ -47597,10 +47597,10 @@
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.64505834563703</v>
+        <v>-3.509069725805595</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.879578908184584</v>
+        <v>1.933974356117159</v>
       </c>
       <c r="F2002" t="n">
         <v>0.2166898895862062</v>
@@ -47620,10 +47620,10 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.781011353693346</v>
+        <v>-3.645022733861911</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.009300837107018</v>
+        <v>2.063696285039592</v>
       </c>
       <c r="F2003" t="n">
         <v>0.2166898895862062</v>
@@ -47643,10 +47643,10 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.803419471498218</v>
+        <v>-3.667430851666783</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.992454284888062</v>
+        <v>2.046849732820637</v>
       </c>
       <c r="F2004" t="n">
         <v>0.2166898895862062</v>
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.443396491684473</v>
+        <v>3.811634855083665</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.916320849268834</v>
+        <v>-3.894337373739642</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.949347733329453</v>
+        <v>1.95814112354113</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2496462332921589</v>
+        <v>0.1899610141075</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.66602023732603</v>
+        <v>3.630209105815234</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-678.4%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.9%</t>
+          <t>455.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.0%</t>
+          <t>-551.1%</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-271.8%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,17 +1150,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.0%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-209.9%</t>
+          <t>-205.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-171.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-205.0%</t>
+          <t>-209.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.0%</t>
+          <t>-85.9%</t>
         </is>
       </c>
     </row>
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.3537084394200811</v>
+        <v>0.2177198195886446</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.259617140945561</v>
+        <v>3.205221693012986</v>
       </c>
       <c r="F1837" t="n">
         <v>1.705385264837735</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2172635491926684</v>
+        <v>0.08127492936123193</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.209119167476263</v>
+        <v>3.154723719543688</v>
       </c>
       <c r="F1838" t="n">
         <v>1.568940374610322</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.01986794265712671</v>
+        <v>-0.1558565624885632</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.149207655233886</v>
+        <v>3.094812207301312</v>
       </c>
       <c r="F1839" t="n">
         <v>1.568940374610322</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.01483035192954019</v>
+        <v>-0.1508189717609766</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.149800131710259</v>
+        <v>3.095404683777685</v>
       </c>
       <c r="F1840" t="n">
         <v>1.62458483087664</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2720243866375969</v>
+        <v>-0.4080130064690334</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.025668899450773</v>
+        <v>2.971273451518199</v>
       </c>
       <c r="F1841" t="n">
         <v>1.367390796168583</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.337791776687009</v>
+        <v>-0.4737803965184454</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.000379552561479</v>
+        <v>2.945984104628904</v>
       </c>
       <c r="F1842" t="n">
         <v>1.367390796168583</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5430364537442536</v>
+        <v>-0.67902507357569</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.908909713726337</v>
+        <v>2.854514265793762</v>
       </c>
       <c r="F1843" t="n">
         <v>1.367390796168583</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6248083541720053</v>
+        <v>-0.7607969740034417</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.866283679510474</v>
+        <v>2.8118882315779</v>
       </c>
       <c r="F1844" t="n">
         <v>1.394426369574719</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.692017462043883</v>
+        <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.844165353195425</v>
+        <v>2.789769905262851</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8995832464354949</v>
+        <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.758963835558021</v>
+        <v>2.704568387625446</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.317337269982332</v>
+        <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.589789117644349</v>
+        <v>2.535393669711775</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.607468936587763</v>
+        <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.473602667601098</v>
+        <v>2.419207219668524</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.815472994940841</v>
+        <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.395293188813793</v>
+        <v>2.340897740881218</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.026885415828816</v>
+        <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.305809676796591</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.392954142973469</v>
+        <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.152466485245179</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.601444924425153</v>
+        <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.089408462403274</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.848646109190375</v>
+        <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.998626738905753</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.341031137214471</v>
+        <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.802779119739847</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.726211528144544</v>
+        <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.647249502180681</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.976082208159125</v>
+        <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.549070353629465</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.182593985046147</v>
+        <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.462571701530914</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.501938060126649</v>
+        <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.336606998198973</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.933743853276436</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.150217568406462</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.168437847408988</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.044624745755532</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.504100494639441</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9089402785193159</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.867726739539754</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7699773407934325</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.232854122178501</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6231809027437651</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.641442899359179</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4585069358862528</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.918018999675011</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3430619282313803</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.334410873962009</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.174499229125459</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.578682274689078</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08704935950331016</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.783933293925839</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.001048516954301082</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.947513172110222</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.06597851426445134</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.24417451392042</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1808640750593224</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.430894222229723</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2595782629174468</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.813895610972354</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4128809197360832</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.995765401957389</v>
+        <v>-9.131754021788826</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4830573201586668</v>
+        <v>-0.5374527680912418</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.35529572446139</v>
+        <v>-9.491284344292827</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6215191458622176</v>
+        <v>-0.6759145937947921</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.405644787915612</v>
+        <v>-9.541633407747049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6337427512867286</v>
+        <v>-0.6881381992193036</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.503264065337008</v>
+        <v>-9.639252685168445</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6697487116335181</v>
+        <v>-0.7241441595660931</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.650790153342651</v>
+        <v>-9.786778773174088</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7258655905142031</v>
+        <v>-0.7802610384467781</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.855048328672515</v>
+        <v>-9.991036948503952</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8020556635275065</v>
+        <v>-0.856451111460081</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.929381304932679</v>
+        <v>-10.06536992476412</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8273062995471361</v>
+        <v>-0.8817017474797111</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.85591147326523</v>
+        <v>-9.991900093096667</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7825466653867355</v>
+        <v>-0.83694211331931</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.03103589065177</v>
+        <v>-10.16702451048321</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8380412115938363</v>
+        <v>-0.8924366595264104</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.26548798466626</v>
+        <v>-10.4014766044977</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9390412141012274</v>
+        <v>-0.9934366620338024</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.36986271569271</v>
+        <v>-10.50585133552415</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9874632972857822</v>
+        <v>-1.041858745218357</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.42264887129304</v>
+        <v>-10.55863749112447</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.007461969687357</v>
+        <v>-1.061857417619931</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.54868566466133</v>
+        <v>-10.68467428449276</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.055182958405558</v>
+        <v>-1.109578406338132</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.49667015069251</v>
+        <v>-10.63265877052395</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.030386417131631</v>
+        <v>-1.084781865064206</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.63834199241663</v>
+        <v>-10.77433061224807</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.088530380720021</v>
+        <v>-1.142925828652596</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.5887511479918</v>
+        <v>-10.72473976782324</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.053640632785215</v>
+        <v>-1.10803608071779</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.57594375498702</v>
+        <v>-10.71193237481846</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.061568809229989</v>
+        <v>-1.115964257162564</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.35009860226761</v>
+        <v>-10.48608722209905</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9616516751060167</v>
+        <v>-1.016047123038591</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.22551994593002</v>
+        <v>-10.36150856576146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9106810680149207</v>
+        <v>-0.9650765159474957</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.27841523397431</v>
+        <v>-10.41440385380575</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9292054090705273</v>
+        <v>-0.9836008570031023</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.20628205868643</v>
+        <v>-10.34227067851787</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8946184347167385</v>
+        <v>-0.9490138826493135</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.13491566607678</v>
+        <v>-10.27090428590822</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8758091400667452</v>
+        <v>-0.9302045879993202</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.04145663209156</v>
+        <v>-10.17744525192299</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8483090077855624</v>
+        <v>-0.9027044557181374</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.774214831223158</v>
+        <v>-9.910203451054596</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7432468479375776</v>
+        <v>-0.7976422958701521</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.676307792546668</v>
+        <v>-9.812296412378105</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7043843474404419</v>
+        <v>-0.7587797953730169</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.65235425157071</v>
+        <v>-9.788342871402147</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6941344249045653</v>
+        <v>-0.7485298728371399</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.388294313247913</v>
+        <v>-9.52428293307935</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6017707657371987</v>
+        <v>-0.6561662136697732</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.681214689743076</v>
+        <v>-8.817203309574513</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3217259499955647</v>
+        <v>-0.3761213979281393</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.641030391376885</v>
+        <v>-8.777019011208322</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3053086067612472</v>
+        <v>-0.3597040546938217</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.477630520437522</v>
+        <v>-8.613619140268959</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2405818371647448</v>
+        <v>-0.2949772850973194</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.244149298207923</v>
+        <v>-8.38013791803936</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1392649194350524</v>
+        <v>-0.1936603673676274</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.094482907200408</v>
+        <v>-8.230471527031845</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.08229057334500611</v>
+        <v>-0.1366860212775807</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.962207433569522</v>
+        <v>-8.098196053400958</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.03401289714562461</v>
+        <v>-0.08840834507819872</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.80646910100978</v>
+        <v>-7.942457720841216</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03109749656590921</v>
+        <v>-0.02329795136666535</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.557469302326199</v>
+        <v>-7.693457922157635</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.143603757263</v>
+        <v>0.08920830933042589</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.663059292099303</v>
+        <v>-7.79904791193074</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.0266081682454602</v>
+        <v>-0.08100361617803475</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.6817941942179</v>
+        <v>-7.817782814049337</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01444221278418745</v>
+        <v>-0.03995323514838711</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.533854152810301</v>
+        <v>-7.669842772641737</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04626069334094041</v>
+        <v>-0.100656141273515</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.480884630556313</v>
+        <v>-7.616873250387749</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03378687069282327</v>
+        <v>-0.08818231862539783</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.437336223785622</v>
+        <v>-7.573324843617058</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02332812007964025</v>
+        <v>-0.07772356801221481</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.195187830331764</v>
+        <v>-7.3311764501632</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0879935916830461</v>
+        <v>0.03359814375047154</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.086928693209242</v>
+        <v>-7.222917313040679</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1258293669912498</v>
+        <v>0.07143391905867524</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.963637558392112</v>
+        <v>-7.099626178223548</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1726439149286789</v>
+        <v>0.1182484669961044</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.942488359488668</v>
+        <v>-7.078476979320104</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1888045727273813</v>
+        <v>0.1344091247948072</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.698722917505224</v>
+        <v>-6.83471153733666</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2820914578678098</v>
+        <v>0.2276960099352352</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.596960097227929</v>
+        <v>-6.732948717059365</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3249208998987436</v>
+        <v>0.2705254519661695</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.347109703278854</v>
+        <v>-6.483098323110291</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4176031324620757</v>
+        <v>0.3632076845295011</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.171217610811421</v>
+        <v>-6.307206230642858</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4915590929696978</v>
+        <v>0.4371636450371228</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.999771147788958</v>
+        <v>-6.135759767620395</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5734651842332368</v>
+        <v>0.5190697363006618</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.925481582050619</v>
+        <v>-6.061470201882056</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6022014881448694</v>
+        <v>0.5478060402122944</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.861845839816684</v>
+        <v>-5.997834459648121</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6323505860927607</v>
+        <v>0.5779551381601857</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.750419080490764</v>
+        <v>-5.886407700322201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6581155486069243</v>
+        <v>0.6037201006743493</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.509988583685904</v>
+        <v>-5.645977203517341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7560308239537457</v>
+        <v>0.7016353760211711</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.437746015514709</v>
+        <v>-5.573734635346146</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7888571650570437</v>
+        <v>0.7344617171244692</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.384747693233321</v>
+        <v>-5.520736313064758</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8107350778869389</v>
+        <v>0.7563396299543643</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.275942807753594</v>
+        <v>-5.411931427585031</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8512551032988234</v>
+        <v>0.7968596553662484</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.055922009716584</v>
+        <v>-5.191910629548021</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9408424595242417</v>
+        <v>0.8864470115916667</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.923054320653306</v>
+        <v>-5.059042940484743</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.009883717951376</v>
+        <v>0.955488270018801</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.802881237288807</v>
+        <v>-4.938869857120245</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.059098795737477</v>
+        <v>1.004703347804903</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.65820909218907</v>
+        <v>-4.794197712020507</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.127055756338812</v>
+        <v>1.072660308406237</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.718083919546762</v>
+        <v>-4.854072539378199</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.089143316797161</v>
+        <v>1.034747868864586</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.631284421767754</v>
+        <v>-4.767273041599191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.146263609231331</v>
+        <v>1.091868161298756</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.63375412822956</v>
+        <v>-4.769742748060997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.14534812802002</v>
+        <v>1.090952680087445</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.70212431455357</v>
+        <v>-4.838112934385007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.129006975965118</v>
+        <v>1.074611528032543</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.715912367400617</v>
+        <v>-4.851900987232054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.113928463458191</v>
+        <v>1.059533015525616</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.746905526729322</v>
+        <v>-4.882894146560759</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9262407647670954</v>
+        <v>0.8718453168345206</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.571431266936854</v>
+        <v>-4.707419886768291</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.000997700675871</v>
+        <v>0.946602252743296</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.682367519578102</v>
+        <v>-4.81835613940954</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9323652283805783</v>
+        <v>0.8779697804480033</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.64870397410582</v>
+        <v>-4.784692593937257</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9489620317893968</v>
+        <v>0.8945665838568218</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.588851354902097</v>
+        <v>-4.724839974733534</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9830754659030183</v>
+        <v>0.9286800179704435</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.502607891875719</v>
+        <v>-4.638596511707156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.01251912168743</v>
+        <v>0.9581236737548549</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.547914711274699</v>
+        <v>-4.683903331106136</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9861721693723633</v>
+        <v>0.9317767214397885</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.576947815977</v>
+        <v>-4.712936435808437</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9751108005245444</v>
+        <v>0.9207153525919696</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.484137334526141</v>
+        <v>-4.620125954357578</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.941507684996254</v>
+        <v>0.887112237063679</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.528526803855568</v>
+        <v>-4.664515423687005</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9256253731890838</v>
+        <v>0.871229925256509</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.415855585619318</v>
+        <v>-4.551844205450755</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9657695689953067</v>
+        <v>0.911374121062732</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.303478584436645</v>
+        <v>-4.439467204268082</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.016211665299043</v>
+        <v>0.9618162173664684</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.331258982337998</v>
+        <v>-4.467247602169435</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.016596707907041</v>
+        <v>0.9622012599744665</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.414260263363277</v>
+        <v>-4.550248883194714</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.821751915497583</v>
+        <v>0.7673564675650082</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.522874341806608</v>
+        <v>-4.658862961638045</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8984559448394562</v>
+        <v>0.8440604969068812</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.487465303558465</v>
+        <v>-4.623453923389902</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9271325862410362</v>
+        <v>0.8727371383084614</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.449081641000314</v>
+        <v>-4.585070260831751</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9399054926066654</v>
+        <v>0.8855100446740907</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.271965310965148</v>
+        <v>-4.407953930796585</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.007481053466034</v>
+        <v>0.9530856055334589</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.317057555798693</v>
+        <v>-4.45304617563013</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9901275472945286</v>
+        <v>0.9357320993619538</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.137682134559926</v>
+        <v>-4.273670754391363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.05566469109645</v>
+        <v>1.001269243163875</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.182696348080531</v>
+        <v>-4.318684967911969</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.018466461019798</v>
+        <v>0.9640710130872225</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.449700858352966</v>
+        <v>-4.585689478184404</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9173562192497693</v>
+        <v>0.8629607713171943</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.550898639790139</v>
+        <v>-4.686887259621576</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8760810285714016</v>
+        <v>0.8216855806388268</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.544387673175827</v>
+        <v>-4.680376293007264</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8762853767714434</v>
+        <v>0.8218899288388686</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.525349545468529</v>
+        <v>-4.661338165299966</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8804253470626071</v>
+        <v>0.8260298991300323</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.556476176619148</v>
+        <v>-4.692464796450585</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.04555656354104</v>
+        <v>0.9911611156084654</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.570342937953066</v>
+        <v>-4.706331557784503</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.040843187993607</v>
+        <v>0.9864477400610319</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.5087362811990752</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.525538766413136</v>
+        <v>-4.661527386244573</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.064773387006505</v>
+        <v>1.01037793907393</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.5087362811990752</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.377795796178133</v>
+        <v>-4.51378441600957</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.203023222892527</v>
+        <v>1.148627774959953</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.3409289239641921</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.479810478709354</v>
+        <v>-4.615799098540792</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.16501097141152</v>
+        <v>1.110615523478945</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.3409289239641921</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.47365777265657</v>
+        <v>-4.609646392488007</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.168134402224292</v>
+        <v>1.113738954291717</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.3347762179114078</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.490467070807072</v>
+        <v>-4.626455690638509</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.160491159704202</v>
+        <v>1.106095711771627</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.3515855160619094</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.42816907203095</v>
+        <v>-4.564157691862387</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.251745913011471</v>
+        <v>1.197350465078897</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.3515855160619094</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.226378874365792</v>
+        <v>-4.362367494197229</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.041042864466933</v>
+        <v>0.9866474165343577</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.153567323892755</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.153000777277056</v>
+        <v>-4.288989397108493</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.140684335624602</v>
+        <v>1.086288887692028</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.08018922680401847</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.25074132190203</v>
+        <v>-4.386729941733467</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.116215853890656</v>
+        <v>1.061820405958081</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.09607850493699865</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.427079082024959</v>
+        <v>-4.563067701856396</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.044216730666156</v>
+        <v>0.9898212827335813</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2724162650599281</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.350657035593033</v>
+        <v>-4.48664565542447</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.073277167278855</v>
+        <v>1.018881719346281</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2724162650599281</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.306283903954464</v>
+        <v>-4.442272523785901</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.090889287369719</v>
+        <v>1.036493839437144</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.2280431334213595</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.298329933659692</v>
+        <v>-4.434318553491129</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.094070875487628</v>
+        <v>1.039675427555053</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.2280431334213595</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.250674203098636</v>
+        <v>-4.386662822930073</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.119514924739855</v>
+        <v>1.06511947680728</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1803874028603038</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.150156044599881</v>
+        <v>-4.286144664431318</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.164614561514082</v>
+        <v>1.110219113581507</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.07986924436154924</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.21082263500227</v>
+        <v>-4.346811254833707</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.127102597828998</v>
+        <v>1.072707149896424</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.1615675610800829</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.165984233393871</v>
+        <v>-4.301972853225308</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.149135661082986</v>
+        <v>1.094740213150412</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.1570241281352134</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.266742869150869</v>
+        <v>-4.402731488982306</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.112993146411265</v>
+        <v>1.05859769847869</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.2458496968622189</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.222540032064969</v>
+        <v>-4.358528651896406</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.136553883773463</v>
+        <v>1.082158435840888</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.2016468597763184</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.259519059728412</v>
+        <v>-4.395507679559849</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.120172273177333</v>
+        <v>1.065776825244758</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.1646729579849879</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.279577138593252</v>
+        <v>-4.415565758424689</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.163396806814436</v>
+        <v>1.109001358881861</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.1646729579849879</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.239646465415362</v>
+        <v>-4.375635085246799</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.177809780679846</v>
+        <v>1.123414332747271</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.1247422848070975</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.188614372692834</v>
+        <v>-4.324602992524271</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.193170846007127</v>
+        <v>1.138775398074552</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.07371019208456958</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.123390191565629</v>
+        <v>-4.259378811397066</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.236447922550714</v>
+        <v>1.182052474618139</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.008486010957363954</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.085963171494495</v>
+        <v>-4.221951791325932</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.247379702878448</v>
+        <v>1.192984254945873</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.003234472928182297</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.106074827529203</v>
+        <v>-4.24206344736064</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.240591832795805</v>
+        <v>1.18619638486323</v>
       </c>
       <c r="F1990" t="n">
         <v>0.0077928720692369</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.052330013101998</v>
+        <v>-4.188318632933435</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.422647529587898</v>
+        <v>1.368252081655323</v>
       </c>
       <c r="F1991" t="n">
         <v>0.01785618150969887</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.028538444495856</v>
+        <v>-4.164527064327293</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.552277066248172</v>
+        <v>1.497881618315597</v>
       </c>
       <c r="F1992" t="n">
         <v>0.04164775011584115</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.002454360232049</v>
+        <v>-4.138442980063485</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.554418675967554</v>
+        <v>1.500023228034979</v>
       </c>
       <c r="F1993" t="n">
         <v>0.04164775011584115</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.872161829302439</v>
+        <v>-4.008150449133876</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.604728883923177</v>
+        <v>1.550333435990602</v>
       </c>
       <c r="F1994" t="n">
         <v>0.278183374643576</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.863269367909156</v>
+        <v>-3.999257987740592</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.625840274207281</v>
+        <v>1.571444826274707</v>
       </c>
       <c r="F1995" t="n">
         <v>0.278183374643576</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.031745484879034</v>
+        <v>-4.167734104710469</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.550304874823915</v>
+        <v>1.49590942689134</v>
       </c>
       <c r="F1996" t="n">
         <v>0.2502355389269952</v>
@@ -47482,10 +47482,10 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.33394595601745</v>
+        <v>-3.469934575848886</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.81069438355641</v>
+        <v>1.756298935623835</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1798874795565845</v>
@@ -47505,10 +47505,10 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.311224852334298</v>
+        <v>-3.447213472165733</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.810446847526575</v>
+        <v>1.756051399594001</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1798874795565845</v>
@@ -47528,10 +47528,10 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.309499809044254</v>
+        <v>-3.44548842887569</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.970042990693762</v>
+        <v>1.915647542761187</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1816125228466282</v>
@@ -47551,10 +47551,10 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.46428081582251</v>
+        <v>-3.600269435653945</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.945208410476106</v>
+        <v>1.890812962543532</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1482448487921521</v>
@@ -47574,10 +47574,10 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.531541259844427</v>
+        <v>-3.667529879675862</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.914979588856885</v>
+        <v>1.86058414092431</v>
       </c>
       <c r="F2001" t="n">
         <v>0.080984404770235</v>
@@ -47597,16 +47597,16 @@
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.509069725805595</v>
+        <v>-3.621637230468715</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.933974356117159</v>
+        <v>1.88894735425191</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.1104041269447376</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.467972604504868</v>
+        <v>3.404201146919986</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.645022733861911</v>
+        <v>-3.757590238525031</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.063696285039592</v>
+        <v>2.018669283174344</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.1104041269447376</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.652075736649827</v>
+        <v>3.588304279064946</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.667430851666783</v>
+        <v>-3.779998356329903</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.046849732820637</v>
+        <v>2.001822730955388</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.1104041269447376</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.64419243155282</v>
+        <v>3.580420973967939</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.811634855083665</v>
+        <v>3.486119917601559</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.894337373739642</v>
+        <v>-3.895077814970246</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.95814112354113</v>
+        <v>1.957844947048888</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1899610141075</v>
+        <v>0.1424139176592999</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.630209105815234</v>
+        <v>3.601680847946314</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.6%</t>
+          <t>454.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-551.1%</t>
+          <t>-553.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.4%</t>
+          <t>-181.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-208.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.8%</t>
+          <t>-202.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.9%</t>
+          <t>-81.3%</t>
         </is>
       </c>
     </row>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.999257987740592</v>
+        <v>-3.966870011656242</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.571444826274707</v>
+        <v>1.584400016708447</v>
       </c>
       <c r="F1995" t="n">
         <v>0.278183374643576</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.167734104710469</v>
+        <v>-4.13534612862612</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.49590942689134</v>
+        <v>1.50886461732508</v>
       </c>
       <c r="F1996" t="n">
         <v>0.2502355389269952</v>
@@ -47482,10 +47482,10 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.469934575848886</v>
+        <v>-3.437546599764536</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.756298935623835</v>
+        <v>1.769254126057575</v>
       </c>
       <c r="F1997" t="n">
         <v>0.1798874795565845</v>
@@ -47505,10 +47505,10 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.447213472165733</v>
+        <v>-3.414825496081384</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.756051399594001</v>
+        <v>1.769006590027741</v>
       </c>
       <c r="F1998" t="n">
         <v>0.1798874795565845</v>
@@ -47528,10 +47528,10 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.44548842887569</v>
+        <v>-3.41310045279134</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.915647542761187</v>
+        <v>1.928602733194928</v>
       </c>
       <c r="F1999" t="n">
         <v>0.1816125228466282</v>
@@ -47551,10 +47551,10 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.600269435653945</v>
+        <v>-3.567881459569596</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.890812962543532</v>
+        <v>1.903768152977272</v>
       </c>
       <c r="F2000" t="n">
         <v>0.1482448487921521</v>
@@ -47574,10 +47574,10 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.667529879675862</v>
+        <v>-3.635141903591513</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.86058414092431</v>
+        <v>1.87353933135805</v>
       </c>
       <c r="F2001" t="n">
         <v>0.080984404770235</v>
@@ -47597,16 +47597,16 @@
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.621637230468715</v>
+        <v>-3.612670369552681</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.88894735425191</v>
+        <v>1.892534098618324</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.1104041269447376</v>
+        <v>0.2166898895862062</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.404201146919986</v>
+        <v>3.467972604504868</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.757590238525031</v>
+        <v>-3.748623377608997</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.018669283174344</v>
+        <v>2.022256027540758</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.1104041269447376</v>
+        <v>0.2166898895862062</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.588304279064946</v>
+        <v>3.652075736649827</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.779998356329903</v>
+        <v>-3.771031495413869</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.001822730955388</v>
+        <v>2.005409475321802</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.1104041269447376</v>
+        <v>0.2166898895862062</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.580420973967939</v>
+        <v>3.64419243155282</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.486119917601559</v>
+        <v>3.422908915724431</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.895077814970246</v>
+        <v>-3.918709834572739</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.957844947048888</v>
+        <v>1.948392139207892</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1424139176592999</v>
+        <v>0.2183325288124588</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.601680847946314</v>
+        <v>3.64723201463821</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.0%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-692.0%</t>
+          <t>-696.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-70.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.7%</t>
+          <t>458.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.4%</t>
+          <t>-553.2%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.2%</t>
+          <t>-278.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>204.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.4%</t>
+          <t>-181.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-208.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-173.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.2%</t>
+          <t>-194.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-81.3%</t>
+          <t>-92.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2005"/>
+  <dimension ref="A1:G2006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8280060818753194</v>
+        <v>-0.8681992688924716</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.789769905262851</v>
+        <v>2.77369263045599</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.035571866266931</v>
+        <v>-1.075765053284083</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.704568387625446</v>
+        <v>2.688491112818586</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.453325889813768</v>
+        <v>-1.493519076830921</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.535393669711775</v>
+        <v>2.519316394904914</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.7434575564192</v>
+        <v>-1.783650743436352</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.419207219668524</v>
+        <v>2.403129944861663</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.951461614772277</v>
+        <v>-1.991654801789429</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.340897740881218</v>
+        <v>2.324820466074357</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.162874035660252</v>
+        <v>-2.203067222677404</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.251414228864017</v>
+        <v>2.235336954057156</v>
       </c>
       <c r="F1850" t="n">
         <v>0.5817759354884754</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.528942762804905</v>
+        <v>-2.569135949822057</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.098071037312605</v>
+        <v>2.081993762505744</v>
       </c>
       <c r="F1851" t="n">
         <v>0.2157072083438227</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.737433544256589</v>
+        <v>-2.777626731273742</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.035013014470699</v>
+        <v>2.018935739663838</v>
       </c>
       <c r="F1852" t="n">
         <v>0.007216426892138306</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.984634729021811</v>
+        <v>-3.024827916038963</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.944231290973179</v>
+        <v>1.928154016166318</v>
       </c>
       <c r="F1853" t="n">
         <v>0.02736978039095073</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.477019757045908</v>
+        <v>-3.51721294406306</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.748383671807272</v>
+        <v>1.732306397000411</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.465015247633146</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.86220014797598</v>
+        <v>-3.902393334993132</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.592854054248107</v>
+        <v>1.576776779441246</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.465015247633146</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.112070827990562</v>
+        <v>-4.152264015007714</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.49467490569689</v>
+        <v>1.478597630890029</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.4287525278026827</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.318582604877583</v>
+        <v>-4.358775791894735</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.40817625359834</v>
+        <v>1.392098978791479</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6352643046897042</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.637926679958085</v>
+        <v>-4.678119866975237</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.282211550266398</v>
+        <v>1.266134275459537</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6352643046897042</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.069732473107872</v>
+        <v>-5.109925660125024</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.095822120473888</v>
+        <v>1.079744845667027</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7716818011309712</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.304426467240424</v>
+        <v>-5.344619654257577</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9902292978229577</v>
+        <v>0.9741520230160967</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.765345533901716</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.640089114470877</v>
+        <v>-5.680282301488029</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8545448305867418</v>
+        <v>0.8384675557798809</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8332765193906209</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.00371535937119</v>
+        <v>-6.043908546388343</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7155818928608579</v>
+        <v>0.699504618053997</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9314981562577467</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.368842742009937</v>
+        <v>-6.409035929027089</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5687854548111906</v>
+        <v>0.5527081800043296</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.227808940556759</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.777431519190616</v>
+        <v>-6.817624706207768</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4041114879536778</v>
+        <v>0.3880342131468169</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.636397717737438</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.054007619506448</v>
+        <v>-7.094200806523601</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2886664802988057</v>
+        <v>0.2725892054919448</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.470399493793446</v>
+        <v>-7.510592680810598</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.120103781192884</v>
+        <v>0.1040265063860231</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.714670894520515</v>
+        <v>-7.754864081537668</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03265391157073516</v>
+        <v>0.01657663676387422</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.919921913757276</v>
+        <v>-7.960115100774428</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05334693097827392</v>
+        <v>-0.06942420578513486</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.083501791941659</v>
+        <v>-8.123694978958811</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1203739621970263</v>
+        <v>-0.1364512370038873</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.380163133751857</v>
+        <v>-8.42035632076901</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2352595229918975</v>
+        <v>-0.2513367977987584</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.705140853471316</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.56688284206116</v>
+        <v>-8.607076029078312</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3139737108500213</v>
+        <v>-0.3300509856568823</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.705140853471316</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.949884230803791</v>
+        <v>-8.990077417820943</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4672763676686582</v>
+        <v>-0.4833536424755192</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.705140853471316</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.131754021788826</v>
+        <v>-9.171947208805978</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5374527680912418</v>
+        <v>-0.5535300428981027</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.887010644456351</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.491284344292827</v>
+        <v>-9.53147753130998</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6759145937947921</v>
+        <v>-0.6919918686016531</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.887010644456351</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.541633407747049</v>
+        <v>-9.581826594764202</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6881381992193036</v>
+        <v>-0.7042154740261646</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.937359707910573</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.639252685168445</v>
+        <v>-9.679445872185598</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7241441595660931</v>
+        <v>-0.7402214343729541</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.03497898533197</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.786778773174088</v>
+        <v>-9.826971960191241</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7802610384467781</v>
+        <v>-0.796338313253639</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.182505073337614</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.991036948503952</v>
+        <v>-10.0312301355211</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.856451111460081</v>
+        <v>-0.872528386266942</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.310144017951603</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.06536992476412</v>
+        <v>-10.10556311178127</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8817017474797111</v>
+        <v>-0.897779022286572</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.454843541886275</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.991900093096667</v>
+        <v>-10.03209328011382</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.83694211331931</v>
+        <v>-0.853019388126171</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.381373710218827</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.16702451048321</v>
+        <v>-10.20721769750036</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8924366595264104</v>
+        <v>-0.9085139343332713</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.556498127605371</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.4014766044977</v>
+        <v>-10.44166979151485</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9934366620338024</v>
+        <v>-1.009513936840663</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.556498127605371</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.50585133552415</v>
+        <v>-10.5460445225413</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.041858745218357</v>
+        <v>-1.057936020025218</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.660872858631816</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.55863749112447</v>
+        <v>-10.59883067814163</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.061857417619931</v>
+        <v>-1.077934692426792</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.756548345214213</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.68467428449276</v>
+        <v>-10.72486747150992</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.109578406338132</v>
+        <v>-1.125655681144993</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.731296722404471</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.63265877052395</v>
+        <v>-10.6728519575411</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.084781865064206</v>
+        <v>-1.100859139871067</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.731296722404471</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.77433061224807</v>
+        <v>-10.81452379926522</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.142925828652596</v>
+        <v>-1.159003103459457</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.731296722404471</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.72473976782324</v>
+        <v>-10.76493295484039</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.10803608071779</v>
+        <v>-1.124113355524651</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.681705877979637</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.71193237481846</v>
+        <v>-10.75212556183561</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.115964257162564</v>
+        <v>-1.132041531969425</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.730561652988538</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.48608722209905</v>
+        <v>-10.5262804091162</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.016047123038591</v>
+        <v>-1.032124397845452</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.688634977401374</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.36150856576146</v>
+        <v>-10.40170175277861</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9650765159474957</v>
+        <v>-0.9811537907543566</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.688634977401374</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.41440385380575</v>
+        <v>-10.4545970408229</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9836008570031023</v>
+        <v>-0.9996781318099632</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.683679631312928</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.34227067851787</v>
+        <v>-10.38246386553502</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9490138826493135</v>
+        <v>-0.9650911574561745</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.683679631312928</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.27090428590822</v>
+        <v>-10.31109747292537</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9302045879993202</v>
+        <v>-0.9462818628061811</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.61231323870328</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.17744525192299</v>
+        <v>-10.21763843894015</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9027044557181374</v>
+        <v>-0.9187817305249983</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.61231323870328</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.910203451054596</v>
+        <v>-9.950396638071748</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7976422958701521</v>
+        <v>-0.8137195706770131</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.61231323870328</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.812296412378105</v>
+        <v>-9.852489599395257</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7587797953730169</v>
+        <v>-0.7748570701798778</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.544327488842724</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.788342871402147</v>
+        <v>-9.828536058419299</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7485298728371399</v>
+        <v>-0.7646071476440008</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.520373947866766</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.52428293307935</v>
+        <v>-9.564476120096502</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6561662136697732</v>
+        <v>-0.6722434884766342</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.25631400954397</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.817203309574513</v>
+        <v>-8.857396496591665</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3761213979281393</v>
+        <v>-0.3921986727350002</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.25631400954397</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.777019011208322</v>
+        <v>-8.817212198225475</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3597040546938217</v>
+        <v>-0.3757813295006827</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.216129711177779</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.613619140268959</v>
+        <v>-8.653812327286111</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2949772850973194</v>
+        <v>-0.3110545599041803</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.052729840238417</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.38013791803936</v>
+        <v>-8.420331105056512</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1936603673676274</v>
+        <v>-0.2097376421744883</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.819248618008818</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.230471527031845</v>
+        <v>-8.270664714048998</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1366860212775807</v>
+        <v>-0.1527632960844416</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.726345126766282</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.098196053400958</v>
+        <v>-8.13838924041811</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.08840834507819872</v>
+        <v>-0.1044856198850597</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.594069653135396</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.942457720841216</v>
+        <v>-7.982650907858369</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02329795136666535</v>
+        <v>-0.03937522617352629</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.438331320575654</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.693457922157635</v>
+        <v>-7.733651109174787</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08920830933042589</v>
+        <v>0.07313103452356495</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.438331320575654</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.79904791193074</v>
+        <v>-7.839241098947892</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08100361617803475</v>
+        <v>-0.0970808909848957</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.543921310348759</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.817782814049337</v>
+        <v>-7.857976001066489</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.03995323514838711</v>
+        <v>-0.05603050995524805</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.54951732000889</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.669842772641737</v>
+        <v>-7.71003595965889</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.100656141273515</v>
+        <v>-0.1167334160803759</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.529196404100332</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.616873250387749</v>
+        <v>-7.657066437404901</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.08818231862539783</v>
+        <v>-0.1042595934322588</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.476226881846344</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.573324843617058</v>
+        <v>-7.613518030634211</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07772356801221481</v>
+        <v>-0.09380084281907575</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.476226881846344</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.3311764501632</v>
+        <v>-7.371369637180353</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.03359814375047154</v>
+        <v>0.0175208689436106</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.476226881846344</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.222917313040679</v>
+        <v>-7.263110500057831</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.07143391905867524</v>
+        <v>0.0553566442518143</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.476226881846344</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.099626178223548</v>
+        <v>-7.1398193652407</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1182484669961044</v>
+        <v>0.1021711921892434</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.352935747029213</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.078476979320104</v>
+        <v>-7.118670166337257</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1344091247948072</v>
+        <v>0.1183318499879462</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.33178654812577</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.83471153733666</v>
+        <v>-6.874904724353812</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2276960099352352</v>
+        <v>0.2116187351283743</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.33178654812577</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.732948717059365</v>
+        <v>-6.773141904076518</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2705254519661695</v>
+        <v>0.2544481771593086</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.318567479733341</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.483098323110291</v>
+        <v>-6.523291510127443</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3632076845295011</v>
+        <v>0.3471304097226402</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.318567479733341</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.307206230642858</v>
+        <v>-6.347399417660011</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4371636450371228</v>
+        <v>0.4210863702302619</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.318567479733341</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.135759767620395</v>
+        <v>-6.175952954637547</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5190697363006618</v>
+        <v>0.5029924614938008</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.147121016710878</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.061470201882056</v>
+        <v>-6.101663388899208</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5478060402122944</v>
+        <v>0.5317287654054335</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.072831450972539</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.997834459648121</v>
+        <v>-6.038027646665274</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5779551381601857</v>
+        <v>0.5618778633533248</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.009195708738604</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.886407700322201</v>
+        <v>-5.926600887339354</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6037201006743493</v>
+        <v>0.5876428258674884</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.009195708738604</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.645977203517341</v>
+        <v>-5.686170390534493</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7016353760211711</v>
+        <v>0.6855581012143102</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.7687652119337436</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.573734635346146</v>
+        <v>-5.613927822363299</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7344617171244692</v>
+        <v>0.7183844423176082</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.7687652119337436</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.520736313064758</v>
+        <v>-5.560929500081911</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7563396299543643</v>
+        <v>0.7402623551475034</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7134289529318047</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.411931427585031</v>
+        <v>-5.452124614602184</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7968596553662484</v>
+        <v>0.7807823805593874</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7134289529318047</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.191910629548021</v>
+        <v>-5.232103816565173</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8864470115916667</v>
+        <v>0.8703697367848058</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.5722091078638245</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.059042940484743</v>
+        <v>-5.099236127501896</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.955488270018801</v>
+        <v>0.93941099521194</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.5722091078638245</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.938869857120245</v>
+        <v>-4.979063044137397</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.004703347804903</v>
+        <v>0.9886260729980416</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4520360244993256</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.794197712020507</v>
+        <v>-4.834390899037659</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.072660308406237</v>
+        <v>1.056583033599376</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3073638793995881</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.854072539378199</v>
+        <v>-4.894265726395352</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.034747868864586</v>
+        <v>1.018670594057725</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.3672387067572803</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.767273041599191</v>
+        <v>-4.807466228616343</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.091868161298756</v>
+        <v>1.075790886491895</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.3672387067572803</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.769742748060997</v>
+        <v>-4.809935935078149</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.090952680087445</v>
+        <v>1.074875405280584</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3697084132190864</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.838112934385007</v>
+        <v>-4.87830612140216</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.074611528032543</v>
+        <v>1.058534253225683</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3604327141828715</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.851900987232054</v>
+        <v>-4.892094174249206</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.059533015525616</v>
+        <v>1.043455740718755</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3604327141828715</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.882894146560759</v>
+        <v>-4.923087333577912</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8718453168345206</v>
+        <v>0.8557680420276597</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3604327141828715</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.707419886768291</v>
+        <v>-4.747613073785443</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.946602252743296</v>
+        <v>0.9305249779364351</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3604327141828715</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.81835613940954</v>
+        <v>-4.858549326426692</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8779697804480033</v>
+        <v>0.8618925056411424</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3604327141828715</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.784692593937257</v>
+        <v>-4.82488578095441</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8945665838568218</v>
+        <v>0.8784893090499608</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.3267691687105896</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.724839974733534</v>
+        <v>-4.765033161750686</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9286800179704435</v>
+        <v>0.9126027431635826</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.3267691687105896</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.638596511707156</v>
+        <v>-4.678789698724309</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9581236737548549</v>
+        <v>0.9420463989479939</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.3267691687105896</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.683903331106136</v>
+        <v>-4.724096518123289</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9317767214397885</v>
+        <v>0.9156994466329276</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.3675793317198204</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.712936435808437</v>
+        <v>-4.75312962282559</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9207153525919696</v>
+        <v>0.9046380777851086</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.3675793317198204</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.620125954357578</v>
+        <v>-4.66031914137473</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.887112237063679</v>
+        <v>0.8710349622568181</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.2747688502689611</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.664515423687005</v>
+        <v>-4.704708610704158</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.871229925256509</v>
+        <v>0.8551526504496481</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.3191583195983888</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.551844205450755</v>
+        <v>-4.592037392467907</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.911374121062732</v>
+        <v>0.895296846255871</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.2064871013621385</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.439467204268082</v>
+        <v>-4.479660391285234</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9618162173664684</v>
+        <v>0.9457389425596074</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.2064871013621385</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.467247602169435</v>
+        <v>-4.507440789186587</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9622012599744665</v>
+        <v>0.9461239851676055</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2342674992634916</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.550248883194714</v>
+        <v>-4.590442070211866</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7673564675650082</v>
+        <v>0.7512791927581473</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2528383837906654</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.658862961638045</v>
+        <v>-4.699056148655197</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8440604969068812</v>
+        <v>0.8279832221000203</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2528383837906654</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.623453923389902</v>
+        <v>-4.663647110407054</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8727371383084614</v>
+        <v>0.8566598635016005</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2528383837906654</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.585070260831751</v>
+        <v>-4.625263447848903</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8855100446740907</v>
+        <v>0.8694327698672297</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2144547212325142</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.407953930796585</v>
+        <v>-4.448147117813737</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9530856055334589</v>
+        <v>0.9370083307265979</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2144547212325142</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.45304617563013</v>
+        <v>-4.493239362647283</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9357320993619538</v>
+        <v>0.9196548245550928</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.276350764401904</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.273670754391363</v>
+        <v>-4.313863941408515</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.001269243163875</v>
+        <v>0.9851919683570143</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.1195740062311853</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.318684967911969</v>
+        <v>-4.358878154929121</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9640710130872225</v>
+        <v>0.9479937382803616</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.1499229015457899</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.585689478184404</v>
+        <v>-4.625882665201556</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8629607713171943</v>
+        <v>0.8468834965103333</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.3442859395887385</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.686887259621576</v>
+        <v>-4.727080446638729</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8216855806388268</v>
+        <v>0.8056083058319659</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.4126947531340577</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.680376293007264</v>
+        <v>-4.720569480024416</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8218899288388686</v>
+        <v>0.8058126540320076</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.4126947531340577</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.661338165299966</v>
+        <v>-4.701531352317119</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8260298991300323</v>
+        <v>0.8099526243231714</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4708783644652522</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.692464796450585</v>
+        <v>-4.732657983467737</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9911611156084654</v>
+        <v>0.9750838408016045</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4708783644652522</v>
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.706331557784503</v>
+        <v>-4.70393046672612</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9864477400610319</v>
+        <v>0.9874081764843852</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.465344451897665</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.564095018769136</v>
+        <v>2.590130116349981</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.661527386244573</v>
+        <v>-4.65912629518619</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.01037793907393</v>
+        <v>1.011338375497283</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5087362811990752</v>
+        <v>-0.465344451897665</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.570103549166062</v>
+        <v>2.596138646746907</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.51378441600957</v>
+        <v>-4.511383324951187</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.148627774959953</v>
+        <v>1.149588211383306</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.2975370946627819</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.749940611299013</v>
+        <v>2.775975708879859</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.615799098540792</v>
+        <v>-4.613398007482409</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.110615523478945</v>
+        <v>1.111575959902298</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3409289239641921</v>
+        <v>-0.2975370946627819</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.752734232830494</v>
+        <v>2.77876933041134</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.609646392488007</v>
+        <v>-4.607245301429624</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.113738954291717</v>
+        <v>1.11469939071507</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3347762179114078</v>
+        <v>-0.2913843886099976</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.757088204853823</v>
+        <v>2.783123302434669</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.626455690638509</v>
+        <v>-4.624054599580126</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.106095711771627</v>
+        <v>1.10705614819498</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3081936867604992</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.746083102703632</v>
+        <v>2.772118200284478</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.564157691862387</v>
+        <v>-4.561756600804004</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.197350465078897</v>
+        <v>1.19831090150225</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3515855160619094</v>
+        <v>-0.3081936867604992</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.812418656500453</v>
+        <v>2.838453754081299</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.362367494197229</v>
+        <v>-4.359966403138846</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9866474165343577</v>
+        <v>0.987607852957711</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.153567323892755</v>
+        <v>-0.1101754945913448</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.639810444191344</v>
+        <v>2.66584554177219</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.288989397108493</v>
+        <v>-4.28658830605011</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.086288887692028</v>
+        <v>1.087249324115381</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.08018922680401847</v>
+        <v>-0.0367973975026083</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.754127534766761</v>
+        <v>2.780162632347607</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.386729941733467</v>
+        <v>-4.384328850675084</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.061820405958081</v>
+        <v>1.062780842381434</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.09607850493699865</v>
+        <v>-0.05268667563558849</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.759221704003016</v>
+        <v>2.785256801583863</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.563067701856396</v>
+        <v>-4.560666610798013</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9898212827335813</v>
+        <v>0.9907817191569346</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2290244357585179</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.65195502875393</v>
+        <v>2.677990126334777</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.48664565542447</v>
+        <v>-4.484244564366087</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.018881719346281</v>
+        <v>1.019842155769634</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2724162650599281</v>
+        <v>-0.2290244357585179</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.650446646793859</v>
+        <v>2.676481744374705</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.442272523785901</v>
+        <v>-4.439871432727518</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.036493839437144</v>
+        <v>1.037454275860497</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1846513041199493</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.676933393212436</v>
+        <v>2.702968490793283</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.434318553491129</v>
+        <v>-4.431917462432746</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.039675427555053</v>
+        <v>1.040635863978406</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.2280431334213595</v>
+        <v>-0.1846513041199493</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.676933393212436</v>
+        <v>2.702968490793283</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.386662822930073</v>
+        <v>-4.38426173187169</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.06511947680728</v>
+        <v>1.066079913230633</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1803874028603038</v>
+        <v>-0.1369955735588936</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.711908588576875</v>
+        <v>2.73794368615772</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.286144664431318</v>
+        <v>-4.283743573372935</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.110219113581507</v>
+        <v>1.11117955000486</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.07986924436154924</v>
+        <v>-0.03647741506013907</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.777111857050852</v>
+        <v>2.803146954631698</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.346811254833707</v>
+        <v>-4.344410163775324</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.072707149896424</v>
+        <v>1.073667586319777</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1615675610800829</v>
+        <v>-0.1181757317786727</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.714847539495604</v>
+        <v>2.74088263707645</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.301972853225308</v>
+        <v>-4.299571762166925</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.094740213150412</v>
+        <v>1.095700649573765</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1570241281352134</v>
+        <v>-0.1136322988338033</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.721671301873154</v>
+        <v>2.747706399454001</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.402731488982306</v>
+        <v>-4.400330397923923</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.05859769847869</v>
+        <v>1.059558134902044</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2458496968622189</v>
+        <v>-0.2024578675608087</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.672536900268029</v>
+        <v>2.698571997848875</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.358528651896406</v>
+        <v>-4.356127560838023</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.082158435840888</v>
+        <v>1.083118872264241</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2016468597763184</v>
+        <v>-0.1582550304749082</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.704938205047406</v>
+        <v>2.730973302628252</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.395507679559849</v>
+        <v>-4.393106588501466</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.065776825244758</v>
+        <v>1.066737261668111</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1212811286835777</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.725532546591452</v>
+        <v>2.751567644172298</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.415565758424689</v>
+        <v>-4.413164667366306</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.109001358881861</v>
+        <v>1.109961795305215</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1646729579849879</v>
+        <v>-0.1212811286835777</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.776780311774492</v>
+        <v>2.802815409355338</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.375635085246799</v>
+        <v>-4.373233994188416</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.123414332747271</v>
+        <v>1.124374769170624</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1247422848070975</v>
+        <v>-0.08135045550568737</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.799179420275479</v>
+        <v>2.825214517856325</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.324602992524271</v>
+        <v>-4.322201901465888</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.138775398074552</v>
+        <v>1.139735834497905</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.07371019208456958</v>
+        <v>-0.03031836278315941</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.824746904147266</v>
+        <v>2.850782001728112</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.259378811397066</v>
+        <v>-4.256977720338683</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.182052474618139</v>
+        <v>1.183012911041492</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.008486010957363954</v>
+        <v>0.03490581834404621</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.881068816916295</v>
+        <v>2.90710391449714</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.221951791325932</v>
+        <v>-4.219550700267549</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.192984254945873</v>
+        <v>1.193944691369226</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.003234472928182297</v>
+        <v>0.04015735637322787</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.880180712033084</v>
+        <v>2.90621580961393</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.24206344736064</v>
+        <v>-4.239662356302257</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.18619638486323</v>
+        <v>1.187156821286583</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0077928720692369</v>
+        <v>0.05118470137064707</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.888053911362776</v>
+        <v>2.914089008943622</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.188318632933435</v>
+        <v>-4.185917541875052</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.368252081655323</v>
+        <v>1.369212518078676</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01785618150969887</v>
+        <v>0.06124801081110903</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.054649668048263</v>
+        <v>3.08068476562911</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.164527064327293</v>
+        <v>-4.16212597326891</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.497881618315597</v>
+        <v>1.49884205473895</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.08503957941725132</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.189037518429766</v>
+        <v>3.215072616010612</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.138442980063485</v>
+        <v>-4.136041889005102</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.500023228034979</v>
+        <v>1.500983664458332</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04164775011584115</v>
+        <v>0.08503957941725132</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.180745494443625</v>
+        <v>3.206780592024471</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.008150449133876</v>
+        <v>-4.005749358075493</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.550333435990602</v>
+        <v>1.551293872413956</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3215752039449861</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.320860064744045</v>
+        <v>3.346895162324892</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.966870011656242</v>
+        <v>-3.996856896682209</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.584400016708447</v>
+        <v>1.57240526269806</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.278183374643576</v>
+        <v>0.3215752039449861</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.338414470470837</v>
+        <v>3.364449568051683</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.13534612862612</v>
+        <v>-4.165333013652086</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.50886461732508</v>
+        <v>1.496869863314693</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2502355389269952</v>
+        <v>0.2936273682284053</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.313500816445472</v>
+        <v>3.339535914026318</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.437546599764536</v>
+        <v>-3.467533484790503</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.769254126057575</v>
+        <v>1.757259372047189</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2232793088579946</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.252561678011088</v>
+        <v>3.278596775591934</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.414825496081384</v>
+        <v>-3.44481238110735</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.769006590027741</v>
+        <v>1.757011836017354</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1798874795565845</v>
+        <v>0.2232793088579946</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.243225700507992</v>
+        <v>3.269260798088838</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.41310045279134</v>
+        <v>-3.443087337817307</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.928602733194928</v>
+        <v>1.916607979184541</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1816125228466282</v>
+        <v>0.2250043521480384</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.403166852333188</v>
+        <v>3.429201949914034</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.567881459569596</v>
+        <v>-3.597868344595562</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.903768152977272</v>
+        <v>1.891773398966885</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1482448487921521</v>
+        <v>0.1916366780935623</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.420224070394148</v>
+        <v>3.446259167974994</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.635141903591513</v>
+        <v>-3.665128788617479</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.87353933135805</v>
+        <v>1.861544577347663</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.080984404770235</v>
+        <v>0.1243762340716452</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.376543159970543</v>
+        <v>3.402578257551389</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.612670369552681</v>
+        <v>-3.642657254578647</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.892534098618324</v>
+        <v>1.880539344607937</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.2600817188876164</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.467972604504868</v>
+        <v>3.494007702085714</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.748623377608997</v>
+        <v>-3.778610262634963</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.022256027540758</v>
+        <v>2.010261273530371</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.2600817188876164</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.652075736649827</v>
+        <v>3.678110834230674</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.771031495413869</v>
+        <v>-3.801018380439835</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.005409475321802</v>
+        <v>1.993414721311416</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2166898895862062</v>
+        <v>0.2600817188876164</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.64419243155282</v>
+        <v>3.670227529133667</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,45 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.422908915724431</v>
+        <v>3.719147660912306</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.918709834572739</v>
+        <v>-3.916097839080178</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.948392139207892</v>
+        <v>1.949436937404915</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2183325288124588</v>
+        <v>0.2920915096021787</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.64723201463821</v>
+        <v>3.691487403112041</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="2" t="n">
+        <v>45468</v>
+      </c>
+      <c r="B2006" t="n">
+        <v>3.796491864476951</v>
+      </c>
+      <c r="C2006" t="n">
+        <v>3.541931362342088</v>
+      </c>
+      <c r="D2006" t="n">
+        <v>-3.916097839080178</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>1.949436937404915</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>0.2920915096021787</v>
+      </c>
+      <c r="G2006" t="n">
+        <v>3.534995159328456</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.0%</t>
+          <t>-686.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-51.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.6%</t>
+          <t>460.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-553.2%</t>
+          <t>-520.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-278.8%</t>
+          <t>-274.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-1060.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>204.1%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-181.3%</t>
+          <t>-168.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-300.5%</t>
+          <t>-294.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-173.5%</t>
+          <t>-172.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-194.8%</t>
+          <t>-193.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-177.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-92.5%</t>
+          <t>-83.4%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.8681992688924716</v>
+        <v>-0.8280060818753194</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.77369263045599</v>
+        <v>2.789769905262851</v>
       </c>
       <c r="F1845" t="n">
         <v>1.394426369574719</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-1.075765053284083</v>
+        <v>-1.035571866266931</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.688491112818586</v>
+        <v>2.704568387625446</v>
       </c>
       <c r="F1846" t="n">
         <v>1.186860585183108</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.493519076830921</v>
+        <v>-1.453325889813768</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.519316394904914</v>
+        <v>2.535393669711775</v>
       </c>
       <c r="F1847" t="n">
         <v>0.7691065616362706</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.783650743436352</v>
+        <v>-1.7434575564192</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.403129944861663</v>
+        <v>2.419207219668524</v>
       </c>
       <c r="F1848" t="n">
         <v>0.7931883563764505</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.991654801789429</v>
+        <v>-1.951461614772277</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.324820466074357</v>
+        <v>2.340897740881218</v>
       </c>
       <c r="F1849" t="n">
         <v>0.7931883563764505</v>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.203067222677404</v>
+        <v>-2.103159697722234</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.235336954057156</v>
+        <v>2.275299964039224</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.5817759354884754</v>
+        <v>0.641490273426494</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.46598582873495</v>
+        <v>3.501814431497761</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.569135949822057</v>
+        <v>-2.469228424866886</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.081993762505744</v>
+        <v>2.121956772487812</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2157072083438227</v>
+        <v>0.2754215462818413</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.239428891754608</v>
+        <v>3.275257494517419</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.777626731273742</v>
+        <v>-2.677719206318571</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.018935739663838</v>
+        <v>2.058898749645906</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.007216426892138306</v>
+        <v>0.06693076483015692</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.134672712622365</v>
+        <v>3.170501315385176</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.024827916038963</v>
+        <v>-2.924920391083792</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.928154016166318</v>
+        <v>1.968117026148386</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.02736978039095073</v>
+        <v>0.08708411832896934</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.154863475130221</v>
+        <v>3.190692077893032</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.51721294406306</v>
+        <v>-3.417305419107889</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.732306397000411</v>
+        <v>1.77226940698248</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.4053009096951274</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.860538850359495</v>
+        <v>2.896367453122306</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.902393334993132</v>
+        <v>-3.802485810037961</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.576776779441246</v>
+        <v>1.616739789423314</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.465015247633146</v>
+        <v>-0.4053009096951274</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.859081389172359</v>
+        <v>2.89490999193517</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.152264015007714</v>
+        <v>-4.052356490052543</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.478597630890029</v>
+        <v>1.518560640872098</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4287525278026827</v>
+        <v>-0.3690381898646641</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.882608144525252</v>
+        <v>2.918436747288064</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.358775791894735</v>
+        <v>-4.258868266939564</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.392098978791479</v>
+        <v>1.432061988773547</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.5755499667516857</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.754807137049298</v>
+        <v>2.790635739812109</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.678119866975237</v>
+        <v>-4.578212342020066</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.266134275459537</v>
+        <v>1.306097285441606</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6352643046897042</v>
+        <v>-0.5755499667516857</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.756580063749557</v>
+        <v>2.792408666512368</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.109925660125024</v>
+        <v>-5.010018135169854</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.079744845667027</v>
+        <v>1.119707855649095</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7716818011309712</v>
+        <v>-0.7119674631929527</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.661062453352201</v>
+        <v>2.696891056115013</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.344619654257577</v>
+        <v>-5.244712129302406</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9741520230160967</v>
+        <v>1.014115032998165</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.765345533901716</v>
+        <v>-0.7056311959636975</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.653148988691845</v>
+        <v>2.688977591454656</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.680282301488029</v>
+        <v>-5.580374776532858</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8384675557798809</v>
+        <v>0.8784305657619491</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8332765193906209</v>
+        <v>-0.7735621814526024</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.610970989054468</v>
+        <v>2.646799591817278</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.043908546388343</v>
+        <v>-5.944001021433172</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.699504618053997</v>
+        <v>0.7394676280360652</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9314981562577467</v>
+        <v>-0.8717838183197282</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.558525567168433</v>
+        <v>2.594354169931245</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.409035929027089</v>
+        <v>-6.309128404071918</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5527081800043296</v>
+        <v>0.5926711899863979</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.227808940556759</v>
+        <v>-1.168094602618741</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.379993611594857</v>
+        <v>2.415822214357668</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.817624706207768</v>
+        <v>-6.717717181252597</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3880342131468169</v>
+        <v>0.4279972231288856</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.133601889301209</v>
+        <v>2.16943049206402</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.094200806523601</v>
+        <v>-6.99429328156843</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2725892054919448</v>
+        <v>0.312552215474013</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.12878732177267</v>
+        <v>2.164615924535481</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.510592680810598</v>
+        <v>-7.410685155855427</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1040265063860231</v>
+        <v>0.1439895163680913</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.126781372381547</v>
+        <v>2.162609975144358</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.754864081537668</v>
+        <v>-7.654956556582497</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01657663676387422</v>
+        <v>0.05653964674594247</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.137040063050226</v>
+        <v>2.172868665813037</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.960115100774428</v>
+        <v>-7.860207575819257</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.06942420578513486</v>
+        <v>-0.02946119580306616</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.133139628195922</v>
+        <v>2.168968230958733</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.123694978958811</v>
+        <v>-8.02378745400364</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1364512370038873</v>
+        <v>-0.09648822702181858</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.636397717737438</v>
+        <v>-1.576683379799419</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.131544548250923</v>
+        <v>2.167373151013734</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.42035632076901</v>
+        <v>-8.320448795813839</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2513367977987584</v>
+        <v>-0.2113737878166897</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.645426515533298</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.129906245502615</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.607076029078312</v>
+        <v>-8.507168504123142</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3300509856568823</v>
+        <v>-0.290087975674814</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.645426515533298</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.125879940968212</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.990077417820943</v>
+        <v>-8.890169892865773</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4833536424755192</v>
+        <v>-0.4433906324934505</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.645426515533298</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.125777839646628</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.171947208805978</v>
+        <v>-9.072039683850807</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5535300428981027</v>
+        <v>-0.5135670329160344</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.827296306518333</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.019227481027037</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.53147753130998</v>
+        <v>-9.431570006354809</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6919918686016531</v>
+        <v>-0.6520288586195848</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.827296306518333</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.024577784325087</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.581826594764202</v>
+        <v>-9.481919069809031</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7042154740261646</v>
+        <v>-0.6642524640440963</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.877645369972555</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.002284366209731</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.679445872185598</v>
+        <v>-9.579538347230427</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7402214343729541</v>
+        <v>-0.7002584243908858</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.975264647393951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>1.946754550378662</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.826971960191241</v>
+        <v>-9.72706443523607</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.796338313253639</v>
+        <v>-0.7563753032715708</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.122790735399595</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.861132453896848</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.0312301355211</v>
+        <v>-9.931322610565934</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.872528386266942</v>
+        <v>-0.8325653762848737</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.250429680013584</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.790062284247097</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.10556311178127</v>
+        <v>-10.0056555868261</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.897779022286572</v>
+        <v>-0.8578160123045033</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.395129203948257</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.707725124370729</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.03209328011382</v>
+        <v>-9.932185755158649</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.853019388126171</v>
+        <v>-0.8130563781441027</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.321659372280808</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.76717872486462</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.20721769750036</v>
+        <v>-10.10731017254519</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9085139343332713</v>
+        <v>-0.8685509243512035</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.496783789667352</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.67665929518021</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.44166979151485</v>
+        <v>-10.34176226655968</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.009513936840663</v>
+        <v>-0.9695509268585956</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.496783789667352</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.669440130278614</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.5460445225413</v>
+        <v>-10.44613699758613</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.057936020025218</v>
+        <v>-1.01797301004315</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.601158520693798</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.600143100888771</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.59883067814163</v>
+        <v>-10.49892315318646</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.077934692426792</v>
+        <v>-1.037971682444724</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.696834007276195</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.543853598777889</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.72486747150992</v>
+        <v>-10.62495994655474</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.125655681144993</v>
+        <v>-1.085692671162926</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.671582384466452</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.561698301092849</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.6728519575411</v>
+        <v>-10.57294443258593</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.100859139871067</v>
+        <v>-1.060896129889</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.671582384466452</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.56568863677925</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.81452379926522</v>
+        <v>-10.71461627431005</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.159003103459457</v>
+        <v>-1.119040093477389</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.671582384466452</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.564213409880508</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.76493295484039</v>
+        <v>-10.66502542988522</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.124113355524651</v>
+        <v>-1.084150345542583</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.621991540041618</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.60902132670028</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.75212556183561</v>
+        <v>-10.65221803688044</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.132041531969425</v>
+        <v>-1.092078521987357</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.67084731505052</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.566656728048257</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.5262804091162</v>
+        <v>-10.42637288416103</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.032124397845452</v>
+        <v>-0.9921613878633839</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.628920639463356</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.601391806436764</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.40170175277861</v>
+        <v>-10.30179422782344</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9811537907543566</v>
+        <v>-0.9411907807722879</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.628920639463356</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.602530950992823</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.4545970408229</v>
+        <v>-10.35468951586773</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9996781318099632</v>
+        <v>-0.9597151218278954</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.62396529337491</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.608137932807998</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.38246386553502</v>
+        <v>-10.28255634057985</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9650911574561745</v>
+        <v>-0.9251281474741058</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.62396529337491</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.613871637046634</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.31109747292537</v>
+        <v>-10.2111899479702</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9462818628061811</v>
+        <v>-0.9063188528241124</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.552598900765262</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.646954210218558</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21763843894015</v>
+        <v>-10.11773091398497</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9187817305249983</v>
+        <v>-0.8788187205429305</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.552598900765262</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.63707072890565</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.950396638071748</v>
+        <v>-9.850489113116577</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8137195706770131</v>
+        <v>-0.7737565606949448</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.552598900765262</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.635236168406277</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.852489599395257</v>
+        <v>-9.752582074440086</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7748570701798778</v>
+        <v>-0.7348940601978096</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.484613150904705</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.67572730334915</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.828536058419299</v>
+        <v>-9.728628533464128</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7646071476440008</v>
+        <v>-0.7246441376619326</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.460659609928748</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.690767934080218</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.564476120096502</v>
+        <v>-9.464568595141332</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6722434884766342</v>
+        <v>-0.6322804784945659</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.196599671605952</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.835943580912143</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.857396496591665</v>
+        <v>-8.757488971636494</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3921986727350002</v>
+        <v>-0.3522356627529319</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.196599671605952</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.833156547251843</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.817212198225475</v>
+        <v>-8.717304673270304</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3757813295006827</v>
+        <v>-0.3358183195186144</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.156415373239761</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.857610750159398</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.653812327286111</v>
+        <v>-8.553904802330941</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3110545599041803</v>
+        <v>-0.271091549922112</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.993015502300398</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.955017493943773</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.420331105056512</v>
+        <v>-8.320423580101341</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2097376421744883</v>
+        <v>-0.1697746321924201</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.7595342800708</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.103030656119384</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.270664714048998</v>
+        <v>-8.170757189093827</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1527632960844416</v>
+        <v>-0.1128002861023734</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.666630788828264</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.155880540551947</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.13838924041811</v>
+        <v>-8.03848171546294</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1044856198850597</v>
+        <v>-0.06452260990299141</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.534355315197377</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.230613311477506</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.982650907858369</v>
+        <v>-7.882743382903198</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.03937522617352629</v>
+        <v>0.000587783808541964</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.378616982637636</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.326871371700987</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.733651109174787</v>
+        <v>-7.633743584219617</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07313103452356495</v>
+        <v>0.1130940445056332</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.378616982637636</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.339777712924646</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607649</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.839241098947892</v>
+        <v>-7.739333573992721</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.0970808909848957</v>
+        <v>-0.05711788100282744</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.48420697241074</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.148447789461565</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.857976001066489</v>
+        <v>-7.758068476111318</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05603050995524805</v>
+        <v>-0.0160674999731798</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.489802982070871</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.193634525542572</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.71003595965889</v>
+        <v>-7.610128434703719</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1167334160803759</v>
+        <v>-0.07677040609830765</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.469482066162314</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.085948152399539</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.657066437404901</v>
+        <v>-7.55715891244973</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1042595934322588</v>
+        <v>-0.06429658345019051</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.416512543908325</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.109015879498454</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.613518030634211</v>
+        <v>-7.51361050567904</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09380084281907575</v>
+        <v>-0.05383783283700749</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.416512543908325</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.102055267403361</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.371369637180353</v>
+        <v>-7.271462112225182</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0175208689436106</v>
+        <v>0.05748387892567886</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.416512543908325</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.116517621784504</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.263110500057831</v>
+        <v>-7.16320297510266</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.0553566442518143</v>
+        <v>0.09531965423388256</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.416512543908325</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.111049742243699</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.1398193652407</v>
+        <v>-7.039911840285529</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1021711921892434</v>
+        <v>0.1421342021713117</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.293221409091195</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.182522517144554</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.118670166337257</v>
+        <v>-7.018762641382086</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1183318499879462</v>
+        <v>0.1582948599700145</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.272072210187751</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.202913014723946</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.874904724353812</v>
+        <v>-6.774997199398642</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2116187351283743</v>
+        <v>0.251581745110443</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.272072210187751</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.198693723070996</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.773141904076518</v>
+        <v>-6.673234379121347</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2544481771593086</v>
+        <v>0.2944111871413768</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.258853141795323</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.20874947802647</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.523291510127443</v>
+        <v>-6.423383985172272</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3471304097226402</v>
+        <v>0.3870934197047089</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.258853141795323</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.201491553010172</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.347399417660011</v>
+        <v>-6.24749189270484</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4210863702302619</v>
+        <v>0.4610493802123301</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.258853141795323</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.20509067653082</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.175952954637547</v>
+        <v>-6.076045429682376</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5029924614938008</v>
+        <v>0.5429554714758695</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.087406678772859</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.321286060398852</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.101663388899208</v>
+        <v>-6.001755863944037</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5317287654054335</v>
+        <v>0.5716917753875022</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-1.01311711303452</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.364880277458153</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.038027646665274</v>
+        <v>-5.938120121710103</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5618778633533248</v>
+        <v>0.601840873335393</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9494813708005855</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.40775652385283</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074786</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.926600887339354</v>
+        <v>-5.826693362384183</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5876428258674884</v>
+        <v>0.6276058358495566</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.9494813708005855</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.388950782636626</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242298</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.686170390534493</v>
+        <v>-5.586262865579323</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6855581012143102</v>
+        <v>0.7255211111963784</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7090508739957252</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.53495215734442</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367688</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.613927822363299</v>
+        <v>-5.514020297408128</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7183844423176082</v>
+        <v>0.7583474522996765</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.7090508739957252</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.53888147117924</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879969</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.560929500081911</v>
+        <v>-5.46102197512674</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7402623551475034</v>
+        <v>0.7802253651295716</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.6537146149937864</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.572761810497743</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.452124614602184</v>
+        <v>-5.352217089647013</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7807823805593874</v>
+        <v>0.8207453905414557</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.6537146149937864</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.569759881717737</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675943</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.232103816565173</v>
+        <v>-5.132196291610002</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8703697367848058</v>
+        <v>0.910332746766874</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5124947699258061</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.656070825769139</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539954</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.099236127501896</v>
+        <v>-4.999328602546725</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.93941099521194</v>
+        <v>0.9793740051940085</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.5124947699258061</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.671965008570962</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.979063044137397</v>
+        <v>-4.879155519182226</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9886260729980416</v>
+        <v>1.02858908298011</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.3923216865613072</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.745214703029963</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.834390899037659</v>
+        <v>-4.734483374082489</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.056583033599376</v>
+        <v>1.096546043581445</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.2476495414615698</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.842106092651246</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.894265726395352</v>
+        <v>-4.794358201440181</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.018670594057725</v>
+        <v>1.058633604039794</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3075243688192619</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.792218687638056</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674517</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.807466228616343</v>
+        <v>-4.707558703661173</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.075790886491895</v>
+        <v>1.115753896473963</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.3075243688192619</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.814619180960622</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.809935935078149</v>
+        <v>-4.710028410122979</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.074875405280584</v>
+        <v>1.114838415262653</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.309994075281068</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.813209758456951</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.87830612140216</v>
+        <v>-4.778398596446989</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.058534253225683</v>
+        <v>1.098497263207751</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3007183762448531</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.829782100353382</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.892094174249206</v>
+        <v>-4.792186649294035</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.043455740718755</v>
+        <v>1.083418750700823</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3007183762448531</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.820218808985273</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417708</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.923087333577912</v>
+        <v>-4.823179808622741</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8557680420276597</v>
+        <v>0.8957310520097281</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3007183762448531</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.64492837402566</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205905</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.747613073785443</v>
+        <v>-4.647705548830272</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9305249779364351</v>
+        <v>0.9704879879185033</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3007183762448531</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.649495606017448</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225449</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.858549326426692</v>
+        <v>-4.758641801471521</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8618925056411424</v>
+        <v>0.9018555156232109</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.3007183762448531</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.625237634778655</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111298</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.82488578095441</v>
+        <v>-4.724978255999239</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8784893090499608</v>
+        <v>0.9184523190320293</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2670548307725713</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.64856714728193</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264168</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.765033161750686</v>
+        <v>-4.665125636795516</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9126027431635826</v>
+        <v>0.9525657531456508</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2670548307725713</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.658739533714062</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742304</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.678789698724309</v>
+        <v>-4.578882173769138</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9420463989479939</v>
+        <v>0.9820094089300624</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2670548307725713</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.653685804287922</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316051</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.724096518123289</v>
+        <v>-4.624188993168118</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9156994466329276</v>
+        <v>0.9556624566149958</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.307864993781802</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.62097548192691</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803196</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.75312962282559</v>
+        <v>-4.653222097870419</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9046380777851086</v>
+        <v>0.9446010877671771</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.307864993781802</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.621527354960011</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809503</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.66031914137473</v>
+        <v>-4.560411616419559</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8710349622568181</v>
+        <v>0.9109979722388866</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.2150545123309427</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.606486335721892</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560431</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.704708610704158</v>
+        <v>-4.604801085748987</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8551526504496481</v>
+        <v>0.8951156604317163</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.2594439816603704</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.581726130048836</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472744</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.592037392467907</v>
+        <v>-4.492129867512737</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.895296846255871</v>
+        <v>0.9352598562379395</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1467727634241202</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.64440456950231</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798543</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.479660391285234</v>
+        <v>-4.379752866330064</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9457389425596074</v>
+        <v>0.9857019525416759</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.1467727634241202</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.649895865332977</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498871</v>
+        <v>3.689597840498868</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.507440789186587</v>
+        <v>-4.407533264231416</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9461239851676055</v>
+        <v>0.9860869951496738</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.1745531613254732</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.644724828360704</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705331</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.590442070211866</v>
+        <v>-4.381290553114201</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7512791927581473</v>
+        <v>0.834939799597213</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.1921827845447852</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.47250277442977</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729276</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.699056148655197</v>
+        <v>-4.489904631557533</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8279832221000203</v>
+        <v>0.9116438289390862</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.1921827845447852</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.592652435148976</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190775</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.663647110407054</v>
+        <v>-4.45449559330939</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8566598635016005</v>
+        <v>0.9403204703406662</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.1921827845447852</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.607165461251299</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913432</v>
+        <v>3.741174069913429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.625263447848903</v>
+        <v>-4.416111930751239</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8694327698672297</v>
+        <v>0.9530933767062955</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.153799121986634</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.627615100128558</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532493</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.448147117813737</v>
+        <v>-4.238995600716073</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9370083307265979</v>
+        <v>1.020668937565664</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.153799121986634</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.62434412897386</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793911</v>
+        <v>3.741328448793907</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.493239362647283</v>
+        <v>-4.284087845549618</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9196548245550928</v>
+        <v>1.003315431394159</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.2156951651560238</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.587889894834139</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011243</v>
+        <v>3.75072937701124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.313863941408515</v>
+        <v>-4.104712424310851</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9851919683570143</v>
+        <v>1.06885257519608</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1195740062311853</v>
+        <v>-0.05891840698530509</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.639349565495456</v>
+        <v>2.675742925042985</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982237</v>
+        <v>3.716991718982234</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.358878154929121</v>
+        <v>-4.149726637831456</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9479937382803616</v>
+        <v>1.031654345119428</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1499229015457899</v>
+        <v>-0.0892673022999097</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.601947683638284</v>
+        <v>2.638341043185812</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509546</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.625882665201556</v>
+        <v>-4.416731148103891</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8468834965103333</v>
+        <v>0.9305441033493993</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3442859395887385</v>
+        <v>-0.2836303403428583</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.49102142315146</v>
+        <v>2.527414782698989</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760817</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.727080446638729</v>
+        <v>-4.517928929541064</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8056083058319659</v>
+        <v>0.8892689126710316</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3520391538881775</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.44918005692077</v>
+        <v>2.485573416468298</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815462</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.720569480024416</v>
+        <v>-4.511417962926751</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8058126540320076</v>
+        <v>0.8894732608710734</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4126947531340577</v>
+        <v>-0.3520391538881775</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.446780018475087</v>
+        <v>2.483173378022615</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378107</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.701531352317119</v>
+        <v>-4.492379835219454</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8099526243231714</v>
+        <v>0.8936132311622371</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.410222765219372</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.408394570884615</v>
+        <v>2.444787930432143</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131259</v>
+        <v>3.731064473131255</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.732657983467737</v>
+        <v>-4.523506466370073</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9750838408016045</v>
+        <v>1.05874444764067</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4708783644652522</v>
+        <v>-0.410222765219372</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.585976439823296</v>
+        <v>2.622369799370824</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067874</v>
+        <v>3.722447362067871</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.70393046672612</v>
+        <v>-4.53737322770399</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9874081764843852</v>
+        <v>1.054031072093237</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.465344451897665</v>
+        <v>-0.4480806819531949</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.590130116349981</v>
+        <v>2.600488378316664</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078913</v>
+        <v>3.787425580789128</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.65912629518619</v>
+        <v>-4.492569056164061</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.011338375497283</v>
+        <v>1.077961271106135</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.465344451897665</v>
+        <v>-0.4480806819531949</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.596138646746907</v>
+        <v>2.60649690871359</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519917</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.511383324951187</v>
+        <v>-4.344826085929058</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.149588211383306</v>
+        <v>1.216211106992158</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2975370946627819</v>
+        <v>-0.2802733247183118</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.775975708879859</v>
+        <v>2.786333970846541</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181179</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.613398007482409</v>
+        <v>-4.446840768460279</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.111575959902298</v>
+        <v>1.17819885551115</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2975370946627819</v>
+        <v>-0.2802733247183118</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.77876933041134</v>
+        <v>2.789127592378022</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394739</v>
+        <v>3.805608985394737</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.607245301429624</v>
+        <v>-4.440688062407495</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.11469939071507</v>
+        <v>1.181322286323922</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2913843886099976</v>
+        <v>-0.2741206186655275</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.783123302434669</v>
+        <v>2.793481564401351</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890618</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.624054599580126</v>
+        <v>-4.457497360557997</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.10705614819498</v>
+        <v>1.173679043803832</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3081936867604992</v>
+        <v>-0.2909299168160291</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.772118200284478</v>
+        <v>2.78247646225116</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798434</v>
+        <v>3.867362636798431</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.561756600804004</v>
+        <v>-4.395199361781875</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.19831090150225</v>
+        <v>1.264933797111101</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3081936867604992</v>
+        <v>-0.2909299168160291</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.838453754081299</v>
+        <v>2.848812016047981</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992201</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.359966403138846</v>
+        <v>-4.193409164116717</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.987607852957711</v>
+        <v>1.054230748566563</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1101754945913448</v>
+        <v>-0.09291172464687475</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.66584554177219</v>
+        <v>2.676203803738872</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785243</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.28658830605011</v>
+        <v>-4.12003106702798</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.087249324115381</v>
+        <v>1.153872219724232</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0367973975026083</v>
+        <v>-0.0195336275581382</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.780162632347607</v>
+        <v>2.790520894314289</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319555</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.384328850675084</v>
+        <v>-4.217771611652955</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.062780842381434</v>
+        <v>1.129403737990286</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.05268667563558849</v>
+        <v>-0.03542290569111839</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.785256801583863</v>
+        <v>2.795615063550545</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489394</v>
+        <v>3.831819032489391</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.560666610798013</v>
+        <v>-4.394109371775884</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9907817191569346</v>
+        <v>1.057404614765786</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2290244357585179</v>
+        <v>-0.2117606658140478</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.677990126334777</v>
+        <v>2.688348388301459</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397803</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.484244564366087</v>
+        <v>-4.317687325343957</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.019842155769634</v>
+        <v>1.086465051378485</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2290244357585179</v>
+        <v>-0.2117606658140478</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.676481744374705</v>
+        <v>2.686840006341387</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024971</v>
+        <v>3.836023391024969</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.439871432727518</v>
+        <v>-4.273314193705389</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.037454275860497</v>
+        <v>1.104077171469349</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1846513041199493</v>
+        <v>-0.1673875341754792</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.702968490793283</v>
+        <v>2.713326752759964</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863232</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.431917462432746</v>
+        <v>-4.265360223410616</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.040635863978406</v>
+        <v>1.107258759587258</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1846513041199493</v>
+        <v>-0.1673875341754792</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.702968490793283</v>
+        <v>2.713326752759964</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83304018194759</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.38426173187169</v>
+        <v>-4.217704492849561</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.066079913230633</v>
+        <v>1.132702808839485</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1369955735588936</v>
+        <v>-0.1197318036144235</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.73794368615772</v>
+        <v>2.748301948124403</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326883</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.283743573372935</v>
+        <v>-4.117186334350806</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.11117955000486</v>
+        <v>1.177802445613712</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.03647741506013907</v>
+        <v>-0.01921364511566898</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.803146954631698</v>
+        <v>2.81350521659838</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314558</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.344410163775324</v>
+        <v>-4.177852924753195</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.073667586319777</v>
+        <v>1.140290481928628</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1181757317786727</v>
+        <v>-0.1009119618342026</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.74088263707645</v>
+        <v>2.751240899043132</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690033</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.299571762166925</v>
+        <v>-4.133014523144796</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.095700649573765</v>
+        <v>1.162323545182616</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.1136322988338033</v>
+        <v>-0.09636852888933317</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.747706399454001</v>
+        <v>2.758064661420682</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674317</v>
+        <v>3.817961388674315</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.400330397923923</v>
+        <v>-4.233773158901794</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.059558134902044</v>
+        <v>1.126181030510895</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.2024578675608087</v>
+        <v>-0.1851940976163386</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.698571997848875</v>
+        <v>2.708930259815557</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163226</v>
+        <v>3.826713779163225</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.356127560838023</v>
+        <v>-4.189570321815894</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.083118872264241</v>
+        <v>1.149741767873093</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1582550304749082</v>
+        <v>-0.1409912605304381</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.730973302628252</v>
+        <v>2.741331564594935</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83822866302291</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.393106588501466</v>
+        <v>-4.226549349479336</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.066737261668111</v>
+        <v>1.133360157276963</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1212811286835777</v>
+        <v>-0.1040173587391076</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.751567644172298</v>
+        <v>2.76192590613898</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042145</v>
+        <v>3.863924114042144</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.413164667366306</v>
+        <v>-4.246607428344177</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.109961795305215</v>
+        <v>1.176584690914066</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1212811286835777</v>
+        <v>-0.1040173587391076</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.802815409355338</v>
+        <v>2.81317367132202</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078287</v>
+        <v>3.865367715078286</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.373233994188416</v>
+        <v>-4.206676755166287</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.124374769170624</v>
+        <v>1.190997664779476</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.08135045550568737</v>
+        <v>-0.06408668556121727</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.825214517856325</v>
+        <v>2.835572779823007</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232404</v>
+        <v>3.864518876232403</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.322201901465888</v>
+        <v>-4.155644662443759</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.139735834497905</v>
+        <v>1.206358730106757</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.03031836278315941</v>
+        <v>-0.01305459283868932</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.850782001728112</v>
+        <v>2.861140263694794</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416212</v>
+        <v>3.842576394162119</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.256977720338683</v>
+        <v>-4.090420481316554</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.183012911041492</v>
+        <v>1.249635806650344</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03490581834404621</v>
+        <v>0.05216958828851631</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.90710391449714</v>
+        <v>2.917462176463823</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639824</v>
+        <v>3.840090220639823</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.219550700267549</v>
+        <v>-4.052993461245419</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.193944691369226</v>
+        <v>1.260567586978078</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04015735637322787</v>
+        <v>0.05742112631769797</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.90621580961393</v>
+        <v>2.916574071580612</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749928</v>
+        <v>3.845198842749927</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.239662356302257</v>
+        <v>-4.073105117280128</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.187156821286583</v>
+        <v>1.253779716895435</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.05118470137064707</v>
+        <v>0.06844847131511717</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.914089008943622</v>
+        <v>2.924447270910304</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393554</v>
+        <v>3.828690479393552</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.185917541875052</v>
+        <v>-4.019360302852923</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.369212518078676</v>
+        <v>1.435835413687528</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.06124801081110903</v>
+        <v>0.07851178075557913</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.08068476562911</v>
+        <v>3.091043027595792</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714892</v>
+        <v>3.81325185471489</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.16212597326891</v>
+        <v>-3.995568734246781</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.49884205473895</v>
+        <v>1.565464950347802</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.08503957941725132</v>
+        <v>0.1023033493617214</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.215072616010612</v>
+        <v>3.225430877977294</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756018</v>
+        <v>3.814259761756016</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.136041889005102</v>
+        <v>-3.969484649982973</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.500983664458332</v>
+        <v>1.567606560067184</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.08503957941725132</v>
+        <v>0.1023033493617214</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.206780592024471</v>
+        <v>3.217138853991153</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654193</v>
+        <v>3.803426852654191</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.005749358075493</v>
+        <v>-3.839192119053363</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.551293872413956</v>
+        <v>1.617916768022807</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3215752039449861</v>
+        <v>0.3388389738894562</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.346895162324892</v>
+        <v>3.357253424291573</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717123</v>
+        <v>3.796293177717121</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.996856896682209</v>
+        <v>-3.830299657660079</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.57240526269806</v>
+        <v>1.639028158306912</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3215752039449861</v>
+        <v>0.3388389738894562</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.364449568051683</v>
+        <v>3.374807830018365</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702632</v>
+        <v>3.794453975702631</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.165333013652086</v>
+        <v>-3.998775774629957</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.496869863314693</v>
+        <v>1.563492758923545</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2936273682284053</v>
+        <v>0.3108911381728754</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.339535914026318</v>
+        <v>3.349894175993001</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539974</v>
+        <v>3.795603100539973</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.467533484790503</v>
+        <v>-3.300976245768374</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.757259372047189</v>
+        <v>1.82388226765604</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2232793088579946</v>
+        <v>0.2405430788024647</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.278596775591934</v>
+        <v>3.288955037558616</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389904</v>
+        <v>3.784700379389903</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.44481238110735</v>
+        <v>-3.278255142085222</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.757011836017354</v>
+        <v>1.823634731626206</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2232793088579946</v>
+        <v>0.2405430788024647</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.269260798088838</v>
+        <v>3.27961906005552</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534942</v>
+        <v>3.78323473053494</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.443087337817307</v>
+        <v>-3.276530098795178</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.916607979184541</v>
+        <v>1.983230874793392</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2250043521480384</v>
+        <v>0.2422681220925085</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.429201949914034</v>
+        <v>3.439560211880716</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77996275940168</v>
+        <v>3.779962759401679</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.597868344595562</v>
+        <v>-3.431311105573433</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.891773398966885</v>
+        <v>1.958396294575737</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1916366780935623</v>
+        <v>0.2089004480380324</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.446259167974994</v>
+        <v>3.456617429941677</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557228</v>
+        <v>3.769472653557226</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.665128788617479</v>
+        <v>-3.49857154959535</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.861544577347663</v>
+        <v>1.928167472956515</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1243762340716452</v>
+        <v>0.1416400040161153</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.402578257551389</v>
+        <v>3.412936519518071</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088383</v>
+        <v>3.766702530088382</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.642657254578647</v>
+        <v>-3.476100015556518</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.880539344607937</v>
+        <v>1.947162240216789</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2600817188876164</v>
+        <v>0.2773454888320865</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.494007702085714</v>
+        <v>3.504365964052396</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541377</v>
+        <v>3.768081101541375</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.778610262634963</v>
+        <v>-3.447895316585102</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.010261273530371</v>
+        <v>2.142547251950315</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2600817188876164</v>
+        <v>0.2773454888320865</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.678110834230674</v>
+        <v>3.688469096197355</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74395453947169</v>
+        <v>3.743954539471688</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.801018380439835</v>
+        <v>-3.470303434389974</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.993414721311416</v>
+        <v>2.12570069973136</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2600817188876164</v>
+        <v>0.2773454888320865</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.670227529133667</v>
+        <v>3.680585791100349</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912306</v>
+        <v>3.719147660912305</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.916097839080178</v>
+        <v>-3.585382893030317</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.949436937404915</v>
+        <v>2.08172291582486</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.2920915096021787</v>
+        <v>0.3093552795466488</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.691487403112041</v>
+        <v>3.701845665078724</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.796491864476951</v>
+        <v>3.748695841503039</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.541931362342088</v>
+        <v>3.63310763422343</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.916097839080178</v>
+        <v>-3.585382893030317</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.949436937404915</v>
+        <v>2.08172291582486</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.2920915096021787</v>
+        <v>0.3093552795466488</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.534995159328456</v>
+        <v>3.626171431209797</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.1%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-686.0%</t>
+          <t>-666.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.7%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.7%</t>
+          <t>460.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-520.1%</t>
+          <t>-496.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-274.8%</t>
+          <t>-266.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-1060.5%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-158.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-294.6%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-217.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-193.1%</t>
+          <t>-182.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-177.1%</t>
+          <t>-170.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.4%</t>
+          <t>-84.9%</t>
         </is>
       </c>
     </row>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.103159697722234</v>
+        <v>-2.162874035660252</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.275299964039224</v>
+        <v>2.251414228864017</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.641490273426494</v>
+        <v>0.5817759354884754</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.501814431497761</v>
+        <v>3.46598582873495</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.469228424866886</v>
+        <v>-2.528942762804905</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.121956772487812</v>
+        <v>2.098071037312605</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2754215462818413</v>
+        <v>0.2157072083438227</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.275257494517419</v>
+        <v>3.239428891754608</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.677719206318571</v>
+        <v>-2.737433544256589</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.058898749645906</v>
+        <v>2.035013014470699</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.06693076483015692</v>
+        <v>0.007216426892138306</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.170501315385176</v>
+        <v>3.134672712622365</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.924920391083792</v>
+        <v>-2.984634729021811</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.968117026148386</v>
+        <v>1.944231290973179</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.08708411832896934</v>
+        <v>0.02736978039095073</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.190692077893032</v>
+        <v>3.154863475130221</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.417305419107889</v>
+        <v>-3.477019757045908</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.77226940698248</v>
+        <v>1.748383671807272</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4053009096951274</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.896367453122306</v>
+        <v>2.860538850359495</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.802485810037961</v>
+        <v>-3.86220014797598</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.616739789423314</v>
+        <v>1.592854054248107</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4053009096951274</v>
+        <v>-0.465015247633146</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.89490999193517</v>
+        <v>2.859081389172359</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.052356490052543</v>
+        <v>-4.112070827990562</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.518560640872098</v>
+        <v>1.49467490569689</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3690381898646641</v>
+        <v>-0.4287525278026827</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.918436747288064</v>
+        <v>2.882608144525252</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.258868266939564</v>
+        <v>-4.318582604877583</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.432061988773547</v>
+        <v>1.40817625359834</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5755499667516857</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.790635739812109</v>
+        <v>2.754807137049298</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.578212342020066</v>
+        <v>-4.637926679958085</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.306097285441606</v>
+        <v>1.282211550266398</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5755499667516857</v>
+        <v>-0.6352643046897042</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.792408666512368</v>
+        <v>2.756580063749557</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.010018135169854</v>
+        <v>-4.812123025539876</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.119707855649095</v>
+        <v>1.198865899501086</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7119674631929527</v>
+        <v>-0.6022854074274706</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.696891056115013</v>
+        <v>2.762700289574302</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.244712129302406</v>
+        <v>-5.046817019672428</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.014115032998165</v>
+        <v>1.093273076850156</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7056311959636975</v>
+        <v>-0.5959491401982154</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.688977591454656</v>
+        <v>2.754786824913945</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.580374776532858</v>
+        <v>-5.38247966690288</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8784305657619491</v>
+        <v>0.9575886096139401</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7735621814526024</v>
+        <v>-0.6638801256871203</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.646799591817278</v>
+        <v>2.712608825276568</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.944001021433172</v>
+        <v>-5.746105911803194</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7394676280360652</v>
+        <v>0.8186256718880562</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8717838183197282</v>
+        <v>-0.7621017625542461</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.594354169931245</v>
+        <v>2.660163403390534</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.309128404071918</v>
+        <v>-6.111233294441941</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5926711899863979</v>
+        <v>0.6718292338383889</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.168094602618741</v>
+        <v>-1.058412546853259</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.415822214357668</v>
+        <v>2.481631447816958</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.717717181252597</v>
+        <v>-6.519822071622619</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4279972231288856</v>
+        <v>0.507155266980877</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.16943049206402</v>
+        <v>2.23523972552331</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.99429328156843</v>
+        <v>-6.796398171938451</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.312552215474013</v>
+        <v>0.3917102593260045</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.164615924535481</v>
+        <v>2.23042515799477</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.410685155855427</v>
+        <v>-7.212790046225448</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1439895163680913</v>
+        <v>0.2231475602200828</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.162609975144358</v>
+        <v>2.228419208603648</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.654956556582497</v>
+        <v>-7.457061446952518</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05653964674594247</v>
+        <v>0.1356976905979339</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.172868665813037</v>
+        <v>2.238677899272327</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.860207575819257</v>
+        <v>-7.662312466189278</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02946119580306616</v>
+        <v>0.04969684804892527</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.168968230958733</v>
+        <v>2.234777464418022</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.02378745400364</v>
+        <v>-7.825892344373662</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09648822702181858</v>
+        <v>-0.01733018316982715</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.576683379799419</v>
+        <v>-1.467001324033937</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.167373151013734</v>
+        <v>2.233182384473023</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.320448795813839</v>
+        <v>-8.12255368618386</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2113737878166897</v>
+        <v>-0.1322157439646983</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.645426515533298</v>
+        <v>-1.535744459767816</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.129906245502615</v>
+        <v>2.195715478961904</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.507168504123142</v>
+        <v>-8.309273394493163</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.290087975674814</v>
+        <v>-0.2109299318228226</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.645426515533298</v>
+        <v>-1.535744459767816</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.125879940968212</v>
+        <v>2.191689174427501</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.890169892865773</v>
+        <v>-8.692274783235794</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4433906324934505</v>
+        <v>-0.364232588641459</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.645426515533298</v>
+        <v>-1.535744459767816</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.125777839646628</v>
+        <v>2.191587073105917</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.072039683850807</v>
+        <v>-8.874144574220828</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5135670329160344</v>
+        <v>-0.434408989064043</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.827296306518333</v>
+        <v>-1.717614250752851</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.019227481027037</v>
+        <v>2.085036714486326</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.431570006354809</v>
+        <v>-9.23367489672483</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6520288586195848</v>
+        <v>-0.5728708147675934</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.827296306518333</v>
+        <v>-1.717614250752851</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.024577784325087</v>
+        <v>2.090387017784376</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.481919069809031</v>
+        <v>-9.284023960179052</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6642524640440963</v>
+        <v>-0.5850944201921044</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.877645369972555</v>
+        <v>-1.767963314207073</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.002284366209731</v>
+        <v>2.06809359966902</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.579538347230427</v>
+        <v>-9.381643237600448</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7002584243908858</v>
+        <v>-0.6211003805388944</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.975264647393951</v>
+        <v>-1.865582591628469</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.946754550378662</v>
+        <v>2.012563783837951</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.72706443523607</v>
+        <v>-9.529169325606091</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7563753032715708</v>
+        <v>-0.6772172594195793</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.122790735399595</v>
+        <v>-2.013108679634113</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.861132453896848</v>
+        <v>1.926941687356137</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.931322610565934</v>
+        <v>-9.733427500935955</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8325653762848737</v>
+        <v>-0.7534073324328823</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.250429680013584</v>
+        <v>-2.140747624248102</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.790062284247097</v>
+        <v>1.855871517706386</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.0056555868261</v>
+        <v>-9.807760477196119</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8578160123045033</v>
+        <v>-0.7786579684525119</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.395129203948257</v>
+        <v>-2.285447148182775</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.707725124370729</v>
+        <v>1.773534357830019</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.932185755158649</v>
+        <v>-9.73429064552867</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8130563781441027</v>
+        <v>-0.7338983342921113</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.321659372280808</v>
+        <v>-2.211977316515326</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.76717872486462</v>
+        <v>1.832987958323909</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.10731017254519</v>
+        <v>-9.909415062915214</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8685509243512035</v>
+        <v>-0.7893928804992116</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.496783789667352</v>
+        <v>-2.38710173390187</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.67665929518021</v>
+        <v>1.742468528639499</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.34176226655968</v>
+        <v>-10.1438671569297</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9695509268585956</v>
+        <v>-0.8903928830066037</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.496783789667352</v>
+        <v>-2.38710173390187</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.669440130278614</v>
+        <v>1.735249363737903</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.44613699758613</v>
+        <v>-10.24824188795615</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.01797301004315</v>
+        <v>-0.9388149661911585</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.601158520693798</v>
+        <v>-2.491476464928315</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.600143100888771</v>
+        <v>1.66595233434806</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.49892315318646</v>
+        <v>-10.30102804355648</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.037971682444724</v>
+        <v>-0.9588136385927326</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.696834007276195</v>
+        <v>-2.587151951510712</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.543853598777889</v>
+        <v>1.609662832237178</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.62495994655474</v>
+        <v>-10.42706483692477</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.085692671162926</v>
+        <v>-1.006534627310934</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.671582384466452</v>
+        <v>-2.56190032870097</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.561698301092849</v>
+        <v>1.627507534552138</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.57294443258593</v>
+        <v>-10.37504932295595</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.060896129889</v>
+        <v>-0.9817380860370077</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.671582384466452</v>
+        <v>-2.56190032870097</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.56568863677925</v>
+        <v>1.631497870238539</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.71461627431005</v>
+        <v>-10.51672116468007</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.119040093477389</v>
+        <v>-1.039882049625398</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.671582384466452</v>
+        <v>-2.56190032870097</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.564213409880508</v>
+        <v>1.630022643339797</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.66502542988522</v>
+        <v>-10.46713032025524</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.084150345542583</v>
+        <v>-1.004992301690592</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.621991540041618</v>
+        <v>-2.512309484276136</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.60902132670028</v>
+        <v>1.67483056015957</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.65221803688044</v>
+        <v>-10.45432292725046</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.092078521987357</v>
+        <v>-1.012920478135365</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.67084731505052</v>
+        <v>-2.561165259285037</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.566656728048257</v>
+        <v>1.632465961507546</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.42637288416103</v>
+        <v>-10.22847777453105</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9921613878633839</v>
+        <v>-0.913003344011392</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.628920639463356</v>
+        <v>-2.519238583697874</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.601391806436764</v>
+        <v>1.667201039896053</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.30179422782344</v>
+        <v>-10.10389911819346</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9411907807722879</v>
+        <v>-0.8620327369202969</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.628920639463356</v>
+        <v>-2.519238583697874</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.602530950992823</v>
+        <v>1.668340184452112</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.35468951586773</v>
+        <v>-10.15679440623775</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9597151218278954</v>
+        <v>-0.8805570779759035</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.62396529337491</v>
+        <v>-2.514283237609428</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.608137932807998</v>
+        <v>1.673947166267287</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.28255634057985</v>
+        <v>-10.08466123094987</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9251281474741058</v>
+        <v>-0.8459701036221148</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.62396529337491</v>
+        <v>-2.514283237609428</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.613871637046634</v>
+        <v>1.679680870505924</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.2111899479702</v>
+        <v>-10.01329483834022</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9063188528241124</v>
+        <v>-0.8271608089721205</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.552598900765262</v>
+        <v>-2.442916844999779</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.646954210218558</v>
+        <v>1.712763443677847</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.11773091398497</v>
+        <v>-9.919835804354996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8788187205429305</v>
+        <v>-0.7996606766909387</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.552598900765262</v>
+        <v>-2.442916844999779</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.63707072890565</v>
+        <v>1.70287996236494</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.850489113116577</v>
+        <v>-9.652594003486598</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7737565606949448</v>
+        <v>-0.6945985168429534</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.552598900765262</v>
+        <v>-2.442916844999779</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.635236168406277</v>
+        <v>1.701045401865566</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.752582074440086</v>
+        <v>-9.554686964810108</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7348940601978096</v>
+        <v>-0.6557360163458177</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.484613150904705</v>
+        <v>-2.374931095139223</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.67572730334915</v>
+        <v>1.741536536808439</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.728628533464128</v>
+        <v>-9.53073342383415</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7246441376619326</v>
+        <v>-0.6454860938099412</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.460659609928748</v>
+        <v>-2.350977554163265</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.690767934080218</v>
+        <v>1.756577167539507</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.464568595141332</v>
+        <v>-9.266673485511353</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6322804784945659</v>
+        <v>-0.5531224346425745</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.196599671605952</v>
+        <v>-2.086917615840469</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.835943580912143</v>
+        <v>1.901752814371433</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.757488971636494</v>
+        <v>-8.559593862006516</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3522356627529319</v>
+        <v>-0.2730776189009405</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.196599671605952</v>
+        <v>-2.086917615840469</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.833156547251843</v>
+        <v>1.898965780711132</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388732</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.717304673270304</v>
+        <v>-8.519409563640325</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3358183195186144</v>
+        <v>-0.256660275666623</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.156415373239761</v>
+        <v>-2.046733317474279</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.857610750159398</v>
+        <v>1.923419983618688</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626478</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.553904802330941</v>
+        <v>-8.356009692700962</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.271091549922112</v>
+        <v>-0.1919335060701206</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.993015502300398</v>
+        <v>-1.883333446534916</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.955017493943773</v>
+        <v>2.020826727403062</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.320423580101341</v>
+        <v>-8.122528470471362</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1697746321924201</v>
+        <v>-0.09061658834042863</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.7595342800708</v>
+        <v>-1.649852224305318</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.103030656119384</v>
+        <v>2.168839889578674</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.170757189093827</v>
+        <v>-7.972862079463847</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1128002861023734</v>
+        <v>-0.03364224225038148</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.666630788828264</v>
+        <v>-1.556948733062782</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.155880540551947</v>
+        <v>2.221689774011236</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.03848171546294</v>
+        <v>-7.840586605832961</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06452260990299141</v>
+        <v>0.01463543394900002</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.534355315197377</v>
+        <v>-1.424673259431895</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.230613311477506</v>
+        <v>2.296422544936795</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.882743382903198</v>
+        <v>-7.684848273273219</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.000587783808541964</v>
+        <v>0.0797458276605334</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.378616982637636</v>
+        <v>-1.268934926872153</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.326871371700987</v>
+        <v>2.392680605160276</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75388257196099</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.633743584219617</v>
+        <v>-7.435848474589638</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1130940445056332</v>
+        <v>0.1922520883576246</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.378616982637636</v>
+        <v>-1.268934926872153</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.339777712924646</v>
+        <v>2.405586946383935</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607649</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.739333573992721</v>
+        <v>-7.541438464362742</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05711788100282744</v>
+        <v>0.02204016284916399</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.48420697241074</v>
+        <v>-1.374524916645258</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.148447789461565</v>
+        <v>2.214257022920854</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987906</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.758068476111318</v>
+        <v>-7.560173366481339</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0160674999731798</v>
+        <v>0.06309054387881163</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.489802982070871</v>
+        <v>-1.380120926305389</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.193634525542572</v>
+        <v>2.259443759001861</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.610128434703719</v>
+        <v>-7.41223332507374</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07677040609830765</v>
+        <v>0.00238763775368378</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.469482066162314</v>
+        <v>-1.359800010396832</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.085948152399539</v>
+        <v>2.151757385858828</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.55715891244973</v>
+        <v>-7.359263802819751</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06429658345019051</v>
+        <v>0.01486146040180092</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.416512543908325</v>
+        <v>-1.306830488142843</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.109015879498454</v>
+        <v>2.174825112957744</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.51361050567904</v>
+        <v>-7.315715396049061</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05383783283700749</v>
+        <v>0.02532021101498394</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.416512543908325</v>
+        <v>-1.306830488142843</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.102055267403361</v>
+        <v>2.167864500862651</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.271462112225182</v>
+        <v>-7.073567002595203</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05748387892567886</v>
+        <v>0.1366419227776703</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.416512543908325</v>
+        <v>-1.306830488142843</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.116517621784504</v>
+        <v>2.182326855243794</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.16320297510266</v>
+        <v>-6.965307865472681</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09531965423388256</v>
+        <v>0.174477698085874</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.416512543908325</v>
+        <v>-1.306830488142843</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.111049742243699</v>
+        <v>2.176858975702989</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.039911840285529</v>
+        <v>-6.84201673065555</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1421342021713117</v>
+        <v>0.2212922460233036</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.293221409091195</v>
+        <v>-1.183539353325712</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.182522517144554</v>
+        <v>2.248331750603844</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919909</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.018762641382086</v>
+        <v>-6.820867531752107</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1582948599700145</v>
+        <v>0.2374529038220059</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.272072210187751</v>
+        <v>-1.162390154422269</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.202913014723946</v>
+        <v>2.268722248183235</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.774997199398642</v>
+        <v>-6.577102089768663</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.251581745110443</v>
+        <v>0.3307397889624344</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.272072210187751</v>
+        <v>-1.162390154422269</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.198693723070996</v>
+        <v>2.264502956530285</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.673234379121347</v>
+        <v>-6.475339269491368</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2944111871413768</v>
+        <v>0.3735692309933683</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.258853141795323</v>
+        <v>-1.14917108602984</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.20874947802647</v>
+        <v>2.274558711485759</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.423383985172272</v>
+        <v>-6.225488875542293</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3870934197047089</v>
+        <v>0.4662514635567003</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.258853141795323</v>
+        <v>-1.14917108602984</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.201491553010172</v>
+        <v>2.267300786469461</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.24749189270484</v>
+        <v>-6.049596783074861</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4610493802123301</v>
+        <v>0.540207424064322</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.258853141795323</v>
+        <v>-1.14917108602984</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.20509067653082</v>
+        <v>2.27089990999011</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.076045429682376</v>
+        <v>-5.878150320052398</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5429554714758695</v>
+        <v>0.622113515327861</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.087406678772859</v>
+        <v>-0.9777246230073772</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.321286060398852</v>
+        <v>2.387095293858141</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.001755863944037</v>
+        <v>-5.803860754314059</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5716917753875022</v>
+        <v>0.6508498192394936</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.01311711303452</v>
+        <v>-0.9034350572690379</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.364880277458153</v>
+        <v>2.430689510917442</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.938120121710103</v>
+        <v>-5.740225012080124</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.601840873335393</v>
+        <v>0.6809989171873845</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9494813708005855</v>
+        <v>-0.8397993150351034</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.40775652385283</v>
+        <v>2.47356575731212</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.826693362384183</v>
+        <v>-5.628798252754204</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6276058358495566</v>
+        <v>0.7067638797015485</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9494813708005855</v>
+        <v>-0.8397993150351034</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.388950782636626</v>
+        <v>2.454760016095916</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.586262865579323</v>
+        <v>-5.388367755949344</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7255211111963784</v>
+        <v>0.8046791550483698</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7090508739957252</v>
+        <v>-0.5993688182302431</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.53495215734442</v>
+        <v>2.600761390803709</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.514020297408128</v>
+        <v>-5.316125187778149</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7583474522996765</v>
+        <v>0.8375054961516679</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7090508739957252</v>
+        <v>-0.5993688182302431</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.53888147117924</v>
+        <v>2.604690704638529</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.46102197512674</v>
+        <v>-5.263126865496761</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7802253651295716</v>
+        <v>0.8593834089815631</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6537146149937864</v>
+        <v>-0.5440325592283043</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.572761810497743</v>
+        <v>2.638571043957032</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.352217089647013</v>
+        <v>-5.154321980017034</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8207453905414557</v>
+        <v>0.8999034343934476</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6537146149937864</v>
+        <v>-0.5440325592283043</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.569759881717737</v>
+        <v>2.635569115177026</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.132196291610002</v>
+        <v>-4.934301181980024</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.910332746766874</v>
+        <v>0.9894907906188657</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5124947699258061</v>
+        <v>-0.402812714160324</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.656070825769139</v>
+        <v>2.721880059228428</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.999328602546725</v>
+        <v>-4.801433492916746</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9793740051940085</v>
+        <v>1.058532049046</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5124947699258061</v>
+        <v>-0.402812714160324</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.671965008570962</v>
+        <v>2.737774242030252</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.879155519182226</v>
+        <v>-4.681260409552247</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.02858908298011</v>
+        <v>1.107747126832102</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3923216865613072</v>
+        <v>-0.2826396307958251</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.745214703029963</v>
+        <v>2.811023936489253</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.734483374082489</v>
+        <v>-4.53658826445251</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.096546043581445</v>
+        <v>1.175704087433436</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2476495414615698</v>
+        <v>-0.1379674856960877</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.842106092651246</v>
+        <v>2.907915326110535</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.794358201440181</v>
+        <v>-4.596463091810202</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.058633604039794</v>
+        <v>1.137791647891785</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3075243688192619</v>
+        <v>-0.1978423130537798</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.792218687638056</v>
+        <v>2.858027921097346</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.707558703661173</v>
+        <v>-4.509663594031194</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.115753896473963</v>
+        <v>1.194911940325955</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3075243688192619</v>
+        <v>-0.1978423130537798</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.814619180960622</v>
+        <v>2.880428414419912</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.710028410122979</v>
+        <v>-4.512133300493</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.114838415262653</v>
+        <v>1.193996459114644</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.309994075281068</v>
+        <v>-0.200312019515586</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.813209758456951</v>
+        <v>2.87901899191624</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.778398596446989</v>
+        <v>-4.58050348681701</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.098497263207751</v>
+        <v>1.177655307059742</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3007183762448531</v>
+        <v>-0.191036320479371</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.829782100353382</v>
+        <v>2.895591333812671</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.792186649294035</v>
+        <v>-4.594291539664057</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.083418750700823</v>
+        <v>1.162576794552815</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3007183762448531</v>
+        <v>-0.191036320479371</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.820218808985273</v>
+        <v>2.886028042444563</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.823179808622741</v>
+        <v>-4.492449106153027</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8957310520097281</v>
+        <v>1.028023332997614</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3007183762448531</v>
+        <v>-0.191036320479371</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.64492837402566</v>
+        <v>2.710737607484949</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.647705548830272</v>
+        <v>-4.316974846360557</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9704879879185033</v>
+        <v>1.102780268906389</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3007183762448531</v>
+        <v>-0.191036320479371</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.649495606017448</v>
+        <v>2.715304839476737</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.758641801471521</v>
+        <v>-4.427911099001806</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9018555156232109</v>
+        <v>1.034147796611097</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3007183762448531</v>
+        <v>-0.191036320479371</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.625237634778655</v>
+        <v>2.691046868237944</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.724978255999239</v>
+        <v>-4.394247553529524</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9184523190320293</v>
+        <v>1.050744600019915</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2670548307725713</v>
+        <v>-0.1573727750070892</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.64856714728193</v>
+        <v>2.714376380741219</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.665125636795516</v>
+        <v>-4.3343949343258</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9525657531456508</v>
+        <v>1.084858034133537</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2670548307725713</v>
+        <v>-0.1573727750070892</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.658739533714062</v>
+        <v>2.724548767173351</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.578882173769138</v>
+        <v>-4.248151471299423</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9820094089300624</v>
+        <v>1.114301689917948</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2670548307725713</v>
+        <v>-0.1573727750070892</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.653685804287922</v>
+        <v>2.719495037747211</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.624188993168118</v>
+        <v>-4.293458290698402</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9556624566149958</v>
+        <v>1.087954737602882</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.307864993781802</v>
+        <v>-0.19818293801632</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.62097548192691</v>
+        <v>2.686784715386199</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.653222097870419</v>
+        <v>-4.322491395400704</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9446010877671771</v>
+        <v>1.076893368755063</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.307864993781802</v>
+        <v>-0.19818293801632</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.621527354960011</v>
+        <v>2.6873365884193</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.560411616419559</v>
+        <v>-4.229680913949844</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9109979722388866</v>
+        <v>1.043290253226773</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2150545123309427</v>
+        <v>-0.1053724565654606</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.606486335721892</v>
+        <v>2.672295569181181</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.604801085748987</v>
+        <v>-4.274070383279271</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8951156604317163</v>
+        <v>1.027407941419602</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2594439816603704</v>
+        <v>-0.1497619258948883</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.581726130048836</v>
+        <v>2.647535363508126</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.492129867512737</v>
+        <v>-4.161399165043021</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9352598562379395</v>
+        <v>1.067552137225825</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1467727634241202</v>
+        <v>-0.03709070765863809</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.64440456950231</v>
+        <v>2.710213802961599</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.379752866330064</v>
+        <v>-4.049022163860348</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9857019525416759</v>
+        <v>1.117994233529562</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1467727634241202</v>
+        <v>-0.03709070765863809</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.649895865332977</v>
+        <v>2.715705098792266</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498868</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.407533264231416</v>
+        <v>-4.076802561761701</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9860869951496738</v>
+        <v>1.11837927613756</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1745531613254732</v>
+        <v>-0.06487110555999115</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.644724828360704</v>
+        <v>2.710534061819993</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.381290553114201</v>
+        <v>-4.15980384278698</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.834939799597213</v>
+        <v>0.9235344837281017</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1921827845447852</v>
+        <v>-0.08344199008716491</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.47250277442977</v>
+        <v>2.537747251104342</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.489904631557533</v>
+        <v>-4.268417921230311</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9116438289390862</v>
+        <v>1.000238513069975</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1921827845447852</v>
+        <v>-0.08344199008716491</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.592652435148976</v>
+        <v>2.657896911823548</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.45449559330939</v>
+        <v>-4.233008882982168</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9403204703406662</v>
+        <v>1.028915154471555</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1921827845447852</v>
+        <v>-0.08344199008716491</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.607165461251299</v>
+        <v>2.672409937925871</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913429</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.416111930751239</v>
+        <v>-4.194625220424017</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9530933767062955</v>
+        <v>1.041688060837184</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.153799121986634</v>
+        <v>-0.04505832752901373</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.627615100128558</v>
+        <v>2.69285957680313</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.238995600716073</v>
+        <v>-4.017508890388851</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.020668937565664</v>
+        <v>1.109263621696552</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.153799121986634</v>
+        <v>-0.04505832752901373</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.62434412897386</v>
+        <v>2.689588605648432</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793907</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.284087845549618</v>
+        <v>-4.062601135222397</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.003315431394159</v>
+        <v>1.091910115525047</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2156951651560238</v>
+        <v>-0.1069543706984035</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587889894834139</v>
+        <v>2.653134371508711</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701124</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.104712424310851</v>
+        <v>-3.883225713983629</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.06885257519608</v>
+        <v>1.157447259326969</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05891840698530509</v>
+        <v>0.04982238747231515</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.675742925042985</v>
+        <v>2.740987401717557</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982234</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.149726637831456</v>
+        <v>-3.928239927504235</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.031654345119428</v>
+        <v>1.120249029250316</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0892673022999097</v>
+        <v>0.01947349215771055</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.638341043185812</v>
+        <v>2.703585519860384</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.416731148103891</v>
+        <v>-4.195244437776671</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9305441033493993</v>
+        <v>1.019138787480288</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2836303403428583</v>
+        <v>-0.174889545885238</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.527414782698989</v>
+        <v>2.592659259373561</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.517928929541064</v>
+        <v>-4.296442219213843</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8892689126710316</v>
+        <v>0.9778635968019198</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3520391538881775</v>
+        <v>-0.2432983594305572</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.485573416468298</v>
+        <v>2.55081789314287</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.511417962926751</v>
+        <v>-4.289931252599531</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8894732608710734</v>
+        <v>0.9780679450019616</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3520391538881775</v>
+        <v>-0.2432983594305572</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.483173378022615</v>
+        <v>2.548417854697187</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.492379835219454</v>
+        <v>-4.270893124892233</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8936132311622371</v>
+        <v>0.9822079152931256</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.410222765219372</v>
+        <v>-0.3014819707617518</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.444787930432143</v>
+        <v>2.510032407106715</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131255</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.523506466370073</v>
+        <v>-4.302019756042852</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.05874444764067</v>
+        <v>1.147339131771559</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.410222765219372</v>
+        <v>-0.3014819707617518</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.622369799370824</v>
+        <v>2.687614276045396</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067871</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.53737322770399</v>
+        <v>-4.31588651737677</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.054031072093237</v>
+        <v>1.142625756224125</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4480806819531949</v>
+        <v>-0.3393398874955747</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.600488378316664</v>
+        <v>2.665732854991236</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789128</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.492569056164061</v>
+        <v>-4.27108234583684</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.077961271106135</v>
+        <v>1.166555955237023</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4480806819531949</v>
+        <v>-0.3393398874955747</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.60649690871359</v>
+        <v>2.671741385388162</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.344826085929058</v>
+        <v>-4.123339375601837</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.216211106992158</v>
+        <v>1.304805791123046</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2802733247183118</v>
+        <v>-0.1715325302606915</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.786333970846541</v>
+        <v>2.851578447521113</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.446840768460279</v>
+        <v>-4.225354058133059</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.17819885551115</v>
+        <v>1.266793539642038</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2802733247183118</v>
+        <v>-0.1715325302606915</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.789127592378022</v>
+        <v>2.854372069052594</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394737</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.440688062407495</v>
+        <v>-4.219201352080274</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.181322286323922</v>
+        <v>1.269916970454811</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2741206186655275</v>
+        <v>-0.1653798242079073</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.793481564401351</v>
+        <v>2.858726041075923</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.457497360557997</v>
+        <v>-4.236010650230776</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.173679043803832</v>
+        <v>1.26227372793472</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2909299168160291</v>
+        <v>-0.1821891223584089</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.78247646225116</v>
+        <v>2.847720938925733</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798431</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.395199361781875</v>
+        <v>-4.173712651454654</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.264933797111101</v>
+        <v>1.35352848124199</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2909299168160291</v>
+        <v>-0.1821891223584089</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.848812016047981</v>
+        <v>2.914056492722553</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.193409164116717</v>
+        <v>-3.971922453789496</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.054230748566563</v>
+        <v>1.142825432697451</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.09291172464687475</v>
+        <v>0.0158290698107455</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.676203803738872</v>
+        <v>2.741448280413444</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.12003106702798</v>
+        <v>-3.898544356700759</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.153872219724232</v>
+        <v>1.242466903855121</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.0195336275581382</v>
+        <v>0.08920716689948205</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.790520894314289</v>
+        <v>2.855765370988861</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.217771611652955</v>
+        <v>-3.996284901325734</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.129403737990286</v>
+        <v>1.217998422121175</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.03542290569111839</v>
+        <v>0.07331788876650186</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.795615063550545</v>
+        <v>2.860859540225117</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489391</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.394109371775884</v>
+        <v>-4.172622661448663</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.057404614765786</v>
+        <v>1.145999298896675</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2117606658140478</v>
+        <v>-0.1030198713564275</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.688348388301459</v>
+        <v>2.753592864976031</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.317687325343957</v>
+        <v>-4.096200615016737</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.086465051378485</v>
+        <v>1.175059735509374</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2117606658140478</v>
+        <v>-0.1030198713564275</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.686840006341387</v>
+        <v>2.75208448301596</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024969</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.273314193705389</v>
+        <v>-4.051827483378168</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.104077171469349</v>
+        <v>1.192671855600237</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1673875341754792</v>
+        <v>-0.05864673971785894</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.713326752759964</v>
+        <v>2.778571229434537</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.265360223410616</v>
+        <v>-4.043873513083396</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.107258759587258</v>
+        <v>1.195853443718146</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1673875341754792</v>
+        <v>-0.05864673971785894</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.713326752759964</v>
+        <v>2.778571229434537</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.217704492849561</v>
+        <v>-3.99621778252234</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.132702808839485</v>
+        <v>1.221297492970373</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1197318036144235</v>
+        <v>-0.01099100915680329</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.748301948124403</v>
+        <v>2.813546424798975</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.117186334350806</v>
+        <v>-3.895699624023585</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.177802445613712</v>
+        <v>1.2663971297446</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.01921364511566898</v>
+        <v>0.08952714934195127</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.81350521659838</v>
+        <v>2.878749693272952</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.177852924753195</v>
+        <v>-3.956366214425974</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.140290481928628</v>
+        <v>1.228885166059517</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.1009119618342026</v>
+        <v>0.007828832623417603</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.751240899043132</v>
+        <v>2.816485375717704</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690031</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.133014523144796</v>
+        <v>-3.911527812817576</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.162323545182616</v>
+        <v>1.250918229313504</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.09636852888933317</v>
+        <v>0.01237226556828708</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.758064661420682</v>
+        <v>2.823309138095255</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674315</v>
+        <v>3.817961388674308</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.233773158901794</v>
+        <v>-4.012286448574574</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.126181030510895</v>
+        <v>1.214775714641783</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1851940976163386</v>
+        <v>-0.07645330315871834</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.708930259815557</v>
+        <v>2.774174736490129</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163225</v>
+        <v>3.826713779163217</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.189570321815894</v>
+        <v>-3.968083611488674</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.149741767873093</v>
+        <v>1.23833645200398</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1409912605304381</v>
+        <v>-0.0322504660728179</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.741331564594935</v>
+        <v>2.806576041269507</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022909</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.226549349479336</v>
+        <v>-4.005062639152117</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.133360157276963</v>
+        <v>1.221954841407851</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.1040173587391076</v>
+        <v>0.004723435718512636</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.76192590613898</v>
+        <v>2.827170382813553</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042144</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.246607428344177</v>
+        <v>-4.025120718016957</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.176584690914066</v>
+        <v>1.265179375044954</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.1040173587391076</v>
+        <v>0.004723435718512636</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.81317367132202</v>
+        <v>2.878418147996592</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078286</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.206676755166287</v>
+        <v>-3.985190044839067</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.190997664779476</v>
+        <v>1.279592348910364</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.06408668556121727</v>
+        <v>0.04465410889640298</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.835572779823007</v>
+        <v>2.90081725649758</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232403</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.155644662443759</v>
+        <v>-3.934157952116539</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.206358730106757</v>
+        <v>1.294953414237645</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.01305459283868932</v>
+        <v>0.09568620161893093</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.861140263694794</v>
+        <v>2.926384740369366</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162119</v>
+        <v>3.84257639416211</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.090420481316554</v>
+        <v>-3.868933770989333</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.249635806650344</v>
+        <v>1.338230490781232</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.05216958828851631</v>
+        <v>0.1609103827461366</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.917462176463823</v>
+        <v>2.982706653138395</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639823</v>
+        <v>3.840090220639814</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.052993461245419</v>
+        <v>-3.831506750918199</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.260567586978078</v>
+        <v>1.349162271108966</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.05742112631769797</v>
+        <v>0.1661619207753182</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.916574071580612</v>
+        <v>2.981818548255184</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749927</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.073105117280128</v>
+        <v>-3.851618406952908</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.253779716895435</v>
+        <v>1.342374401026323</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.06844847131511717</v>
+        <v>0.1771892657727374</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.924447270910304</v>
+        <v>2.989691747584876</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393552</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.019360302852923</v>
+        <v>-3.797873592525703</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.435835413687528</v>
+        <v>1.524430097818416</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.07851178075557913</v>
+        <v>0.1872525752131994</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.091043027595792</v>
+        <v>3.156287504270364</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81325185471489</v>
+        <v>3.813251854714882</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.995568734246781</v>
+        <v>-3.77408202391956</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.565464950347802</v>
+        <v>1.65405963447869</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1023033493617214</v>
+        <v>0.2110441438193417</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.225430877977294</v>
+        <v>3.290675354651866</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756016</v>
+        <v>3.814259761756008</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.969484649982973</v>
+        <v>-3.747997939655753</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.567606560067184</v>
+        <v>1.656201244198072</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1023033493617214</v>
+        <v>0.2110441438193417</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.217138853991153</v>
+        <v>3.282383330665725</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654191</v>
+        <v>3.803426852654183</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.839192119053363</v>
+        <v>-3.617705408726143</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.617916768022807</v>
+        <v>1.706511452153695</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.3388389738894562</v>
+        <v>0.4475797683470765</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.357253424291573</v>
+        <v>3.422497900966146</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717121</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.830299657660079</v>
+        <v>-3.60881294733286</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.639028158306912</v>
+        <v>1.7276228424378</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.3388389738894562</v>
+        <v>0.4475797683470765</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.374807830018365</v>
+        <v>3.440052306692937</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702631</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.998775774629957</v>
+        <v>-3.777289064302737</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.563492758923545</v>
+        <v>1.652087443054433</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.3108911381728754</v>
+        <v>0.4196319326304957</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.349894175993001</v>
+        <v>3.415138652667573</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539973</v>
+        <v>3.795603100539965</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.300976245768374</v>
+        <v>-3.079489535441154</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.82388226765604</v>
+        <v>1.912476951786928</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.2405430788024647</v>
+        <v>0.349283873260085</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.288955037558616</v>
+        <v>3.354199514233188</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389903</v>
+        <v>3.784700379389894</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.278255142085222</v>
+        <v>-3.056768431758002</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.823634731626206</v>
+        <v>1.912229415757093</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.2405430788024647</v>
+        <v>0.349283873260085</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.27961906005552</v>
+        <v>3.344863536730093</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78323473053494</v>
+        <v>3.783234730534931</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.276530098795178</v>
+        <v>-3.055043388467958</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.983230874793392</v>
+        <v>2.07182555892428</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.2422681220925085</v>
+        <v>0.3510089165501287</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.439560211880716</v>
+        <v>3.504804688555288</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401679</v>
+        <v>3.779962759401671</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.431311105573433</v>
+        <v>-3.209824395246213</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.958396294575737</v>
+        <v>2.046990978706624</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.2089004480380324</v>
+        <v>0.3176412424956526</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.456617429941677</v>
+        <v>3.521861906616249</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557226</v>
+        <v>3.769472653557219</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.49857154959535</v>
+        <v>-3.27708483926813</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.928167472956515</v>
+        <v>2.016762157087403</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.1416400040161153</v>
+        <v>0.2503807984737355</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.412936519518071</v>
+        <v>3.478180996192644</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088382</v>
+        <v>3.766702530088375</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.476100015556518</v>
+        <v>-3.254613305229298</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.947162240216789</v>
+        <v>2.035756924347677</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.2773454888320865</v>
+        <v>0.3860862832897067</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.504365964052396</v>
+        <v>3.569610440726968</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541375</v>
+        <v>3.768081101541367</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.447895316585102</v>
+        <v>-3.211867895841856</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.142547251950315</v>
+        <v>2.236958220247613</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.2773454888320865</v>
+        <v>0.3860862832897067</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.688469096197355</v>
+        <v>3.753713572871928</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471688</v>
+        <v>3.743954539471681</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.470303434389974</v>
+        <v>-3.234276013646728</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.12570069973136</v>
+        <v>2.220111668028658</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.2773454888320865</v>
+        <v>0.3860862832897067</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.680585791100349</v>
+        <v>3.745830267774921</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912305</v>
+        <v>3.719147660912293</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.585382893030317</v>
+        <v>-3.349355472287071</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.08172291582486</v>
+        <v>2.176133884122158</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.3093552795466488</v>
+        <v>0.4180960740042691</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.701845665078724</v>
+        <v>3.767090141753296</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.748695841503039</v>
+        <v>3.758647133936188</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.63310763422343</v>
+        <v>3.617846702263856</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.585382893030317</v>
+        <v>-3.349355472287071</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.08172291582486</v>
+        <v>2.176133884122158</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.3093552795466488</v>
+        <v>0.4180960740042691</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.626171431209797</v>
+        <v>3.610910499250224</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-666.3%</t>
+          <t>-692.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.1%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-496.5%</t>
+          <t>-566.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.9%</t>
+          <t>-277.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.7%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>141.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-186.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-300.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-217.5%</t>
+          <t>-166.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-182.2%</t>
+          <t>-213.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-170.5%</t>
+          <t>-180.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.9%</t>
+          <t>-113.6%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.812123025539876</v>
+        <v>-5.069732473107872</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.198865899501086</v>
+        <v>1.095822120473888</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6022854074274706</v>
+        <v>-0.7716818011309712</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.762700289574302</v>
+        <v>2.661062453352201</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.046817019672428</v>
+        <v>-5.304426467240424</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.093273076850156</v>
+        <v>0.9902292978229577</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5959491401982154</v>
+        <v>-0.765345533901716</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.754786824913945</v>
+        <v>2.653148988691845</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.38247966690288</v>
+        <v>-5.640089114470877</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9575886096139401</v>
+        <v>0.8545448305867418</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6638801256871203</v>
+        <v>-0.8332765193906209</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.712608825276568</v>
+        <v>2.610970989054468</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.746105911803194</v>
+        <v>-6.00371535937119</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8186256718880562</v>
+        <v>0.7155818928608579</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7621017625542461</v>
+        <v>-0.9314981562577467</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.660163403390534</v>
+        <v>2.558525567168433</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.111233294441941</v>
+        <v>-6.368842742009937</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6718292338383889</v>
+        <v>0.5687854548111906</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.058412546853259</v>
+        <v>-1.227808940556759</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.481631447816958</v>
+        <v>2.379993611594857</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.519822071622619</v>
+        <v>-6.777431519190616</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.507155266980877</v>
+        <v>0.4041114879536778</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.23523972552331</v>
+        <v>2.133601889301209</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.796398171938451</v>
+        <v>-6.970216533276535</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3917102593260045</v>
+        <v>0.3221829147907709</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.23042515799477</v>
+        <v>2.12878732177267</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.212790046225448</v>
+        <v>-7.386608407563532</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2231475602200828</v>
+        <v>0.1536202156848496</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.228419208603648</v>
+        <v>2.126781372381547</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.457061446952518</v>
+        <v>-7.630879808290602</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1356976905979339</v>
+        <v>0.06617034606270078</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.238677899272327</v>
+        <v>2.137040063050226</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.662312466189278</v>
+        <v>-7.836130827527362</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.04969684804892527</v>
+        <v>-0.0198304964863083</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.234777464418022</v>
+        <v>2.133139628195922</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.825892344373662</v>
+        <v>-7.999710705711745</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.01733018316982715</v>
+        <v>-0.08685752770506072</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.467001324033937</v>
+        <v>-1.636397717737438</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.233182384473023</v>
+        <v>2.131544548250923</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.12255368618386</v>
+        <v>-8.296372047521944</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1322157439646983</v>
+        <v>-0.2017430884999318</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.535744459767816</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.195715478961904</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.309273394493163</v>
+        <v>-8.483091755831246</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2109299318228226</v>
+        <v>-0.2804572763580562</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.535744459767816</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.191689174427501</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.692274783235794</v>
+        <v>-8.866093144573878</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.364232588641459</v>
+        <v>-0.4337599331766926</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.535744459767816</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.191587073105917</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.874144574220828</v>
+        <v>-9.047962935558912</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.434408989064043</v>
+        <v>-0.5039363335992761</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.717614250752851</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.085036714486326</v>
+        <v>1.983398878264226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.23367489672483</v>
+        <v>-9.407493258062914</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5728708147675934</v>
+        <v>-0.642398159302827</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.717614250752851</v>
+        <v>-1.887010644456351</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.090387017784376</v>
+        <v>1.988749181562276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.284023960179052</v>
+        <v>-9.457842321517136</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5850944201921044</v>
+        <v>-0.654621764727338</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.767963314207073</v>
+        <v>-1.937359707910573</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.06809359966902</v>
+        <v>1.96645576344692</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.381643237600448</v>
+        <v>-9.555461598938532</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6211003805388944</v>
+        <v>-0.6906277250741275</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.865582591628469</v>
+        <v>-2.03497898533197</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.012563783837951</v>
+        <v>1.91092594761585</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937495</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.529169325606091</v>
+        <v>-9.702987686944175</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6772172594195793</v>
+        <v>-0.7467446039548125</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.013108679634113</v>
+        <v>-2.182505073337614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.926941687356137</v>
+        <v>1.825303851134037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.733427500935955</v>
+        <v>-9.907245862274038</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7534073324328823</v>
+        <v>-0.8229346769681158</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.140747624248102</v>
+        <v>-2.310144017951603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.855871517706386</v>
+        <v>1.754233681484286</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.807760477196119</v>
+        <v>-9.981578838534203</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7786579684525119</v>
+        <v>-0.8481853129877455</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.285447148182775</v>
+        <v>-2.454843541886275</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.773534357830019</v>
+        <v>1.671896521607918</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.73429064552867</v>
+        <v>-9.908109006866754</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7338983342921113</v>
+        <v>-0.8034256788273448</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.211977316515326</v>
+        <v>-2.381373710218827</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.832987958323909</v>
+        <v>1.731350122101808</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.909415062915214</v>
+        <v>-10.0832334242533</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.7893928804992116</v>
+        <v>-0.8589202250344457</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.38710173390187</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.742468528639499</v>
+        <v>1.640830692417399</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.1438671569297</v>
+        <v>-10.31768551826779</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.8903928830066037</v>
+        <v>-0.9599202275418368</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.38710173390187</v>
+        <v>-2.556498127605371</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.735249363737903</v>
+        <v>1.633611527515803</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.24824188795615</v>
+        <v>-10.42206024929423</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9388149661911585</v>
+        <v>-1.008342310726392</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.491476464928315</v>
+        <v>-2.660872858631816</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.66595233434806</v>
+        <v>1.564314498125959</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.30102804355648</v>
+        <v>-10.47484640489456</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9588136385927326</v>
+        <v>-1.028340983127967</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.587151951510712</v>
+        <v>-2.756548345214213</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.609662832237178</v>
+        <v>1.508024996015078</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.42706483692477</v>
+        <v>-10.60088319826285</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.006534627310934</v>
+        <v>-1.076061971846168</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.56190032870097</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.627507534552138</v>
+        <v>1.525869698330037</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.37504932295595</v>
+        <v>-10.54886768429404</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9817380860370077</v>
+        <v>-1.051265430572241</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.56190032870097</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.631497870238539</v>
+        <v>1.529860034016438</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.51672116468007</v>
+        <v>-10.69053952601816</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.039882049625398</v>
+        <v>-1.109409394160631</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.56190032870097</v>
+        <v>-2.731296722404471</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.630022643339797</v>
+        <v>1.528384807117697</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.46713032025524</v>
+        <v>-10.64094868159332</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.004992301690592</v>
+        <v>-1.074519646225825</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.512309484276136</v>
+        <v>-2.681705877979637</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.67483056015957</v>
+        <v>1.573192723937469</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.45432292725046</v>
+        <v>-10.62814128858855</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.012920478135365</v>
+        <v>-1.082447822670598</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.561165259285037</v>
+        <v>-2.730561652988538</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.632465961507546</v>
+        <v>1.530828125285446</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.22847777453105</v>
+        <v>-10.40229613586914</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.913003344011392</v>
+        <v>-0.9825306885466252</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.519238583697874</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.667201039896053</v>
+        <v>1.565563203673952</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.10389911819346</v>
+        <v>-10.27771747953154</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8620327369202969</v>
+        <v>-0.9315600814555292</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.519238583697874</v>
+        <v>-2.688634977401374</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.668340184452112</v>
+        <v>1.566702348230011</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.15679440623775</v>
+        <v>-10.33061276757583</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8805570779759035</v>
+        <v>-0.9500844225111367</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.514283237609428</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.673947166267287</v>
+        <v>1.572309330045187</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.08466123094987</v>
+        <v>-10.25847959228795</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8459701036221148</v>
+        <v>-0.915497448157347</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.514283237609428</v>
+        <v>-2.683679631312928</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.679680870505924</v>
+        <v>1.578043034283823</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.01329483834022</v>
+        <v>-10.1871131996783</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8271608089721205</v>
+        <v>-0.8966881535073536</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.442916844999779</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.712763443677847</v>
+        <v>1.611125607455747</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.919835804354996</v>
+        <v>-10.09365416569308</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7996606766909387</v>
+        <v>-0.8691880212261718</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.442916844999779</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.70287996236494</v>
+        <v>1.601242126142839</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.652594003486598</v>
+        <v>-9.924199947928738</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6945985168429534</v>
+        <v>-0.8032408946198091</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.442916844999779</v>
+        <v>-2.61231323870328</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.701045401865566</v>
+        <v>1.599407565643466</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.554686964810108</v>
+        <v>-9.826292909252247</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6557360163458177</v>
+        <v>-0.7643783941226738</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.374931095139223</v>
+        <v>-2.544327488842724</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.741536536808439</v>
+        <v>1.639898700586339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.53073342383415</v>
+        <v>-9.802339368276289</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6454860938099412</v>
+        <v>-0.7541284715867969</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.350977554163265</v>
+        <v>-2.520373947866766</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.756577167539507</v>
+        <v>1.654939331317407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.266673485511353</v>
+        <v>-9.538279429953493</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5531224346425745</v>
+        <v>-0.6617648124194302</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.086917615840469</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.901752814371433</v>
+        <v>1.800114978149332</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.559593862006516</v>
+        <v>-8.831199806448655</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2730776189009405</v>
+        <v>-0.3817199966777962</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.086917615840469</v>
+        <v>-2.25631400954397</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.898965780711132</v>
+        <v>1.797327944489031</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.519409563640325</v>
+        <v>-8.791015508082465</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.256660275666623</v>
+        <v>-0.3653026534434787</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.046733317474279</v>
+        <v>-2.216129711177779</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.923419983618688</v>
+        <v>1.821782147396587</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.356009692700962</v>
+        <v>-8.627615637143101</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1919335060701206</v>
+        <v>-0.3005758838469763</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.883333446534916</v>
+        <v>-2.052729840238417</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.020826727403062</v>
+        <v>1.919188891180962</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.122528470471362</v>
+        <v>-8.394134414913502</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09061658834042863</v>
+        <v>-0.1992589661172843</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.649852224305318</v>
+        <v>-1.819248618008818</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.168839889578674</v>
+        <v>2.067202053356573</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.972862079463847</v>
+        <v>-8.244468023905988</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03364224225038148</v>
+        <v>-0.1422846200272376</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.556948733062782</v>
+        <v>-1.726345126766282</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.221689774011236</v>
+        <v>2.120051937789135</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.840586605832961</v>
+        <v>-8.1121925502751</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01463543394900002</v>
+        <v>-0.09400694382785568</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.424673259431895</v>
+        <v>-1.594069653135396</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.296422544936795</v>
+        <v>2.194784708714694</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.684848273273219</v>
+        <v>-7.956454217715359</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.0797458276605334</v>
+        <v>-0.02889655011632231</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.268934926872153</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.392680605160276</v>
+        <v>2.291042768938176</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.435848474589638</v>
+        <v>-7.707454419031778</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1922520883576246</v>
+        <v>0.08360971058076894</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.268934926872153</v>
+        <v>-1.438331320575654</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.405586946383935</v>
+        <v>2.303949110161835</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.541438464362742</v>
+        <v>-7.813044408804882</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.02204016284916399</v>
+        <v>-0.08660221492769171</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.374524916645258</v>
+        <v>-1.543921310348759</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.214257022920854</v>
+        <v>2.112619186698754</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987904</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.560173366481339</v>
+        <v>-7.831779310923479</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06309054387881163</v>
+        <v>-0.04555183389804407</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.380120926305389</v>
+        <v>-1.54951732000889</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.259443759001861</v>
+        <v>2.157805922779761</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.41223332507374</v>
+        <v>-7.68383926951588</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.00238763775368378</v>
+        <v>-0.1062547400231719</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.359800010396832</v>
+        <v>-1.529196404100332</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.151757385858828</v>
+        <v>2.050119549636728</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409201</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.359263802819751</v>
+        <v>-7.630869747261891</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01486146040180092</v>
+        <v>-0.09378091737505478</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.306830488142843</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.174825112957744</v>
+        <v>2.073187276735643</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.315715396049061</v>
+        <v>-7.587321340491201</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02532021101498394</v>
+        <v>-0.08332216676187176</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.306830488142843</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.167864500862651</v>
+        <v>2.06622666464055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.073567002595203</v>
+        <v>-7.345172947037343</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1366419227776703</v>
+        <v>0.02799954500081459</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.306830488142843</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.182326855243794</v>
+        <v>2.080689019021693</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.965307865472681</v>
+        <v>-7.236913809914821</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.174477698085874</v>
+        <v>0.06583532030901829</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.306830488142843</v>
+        <v>-1.476226881846344</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.176858975702989</v>
+        <v>2.075221139480888</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.84201673065555</v>
+        <v>-7.11362267509769</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2212922460233036</v>
+        <v>0.1126498682464474</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.183539353325712</v>
+        <v>-1.352935747029213</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.248331750603844</v>
+        <v>2.146693914381743</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.820867531752107</v>
+        <v>-7.092473476194247</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2374529038220059</v>
+        <v>0.1288105260451502</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.162390154422269</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.268722248183235</v>
+        <v>2.167084411961135</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.577102089768663</v>
+        <v>-6.848708034210802</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3307397889624344</v>
+        <v>0.2220974111855782</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.162390154422269</v>
+        <v>-1.33178654812577</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.264502956530285</v>
+        <v>2.162865120308185</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.475339269491368</v>
+        <v>-6.746945213933508</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3735692309933683</v>
+        <v>0.2649268532165125</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.14917108602984</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.274558711485759</v>
+        <v>2.172920875263658</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.225488875542293</v>
+        <v>-6.497094819984433</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4662514635567003</v>
+        <v>0.3576090857798442</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.14917108602984</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.267300786469461</v>
+        <v>2.165662950247361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.049596783074861</v>
+        <v>-6.321202727517001</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.540207424064322</v>
+        <v>0.4315650462874658</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.14917108602984</v>
+        <v>-1.318567479733341</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.27089990999011</v>
+        <v>2.169262073768009</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.878150320052398</v>
+        <v>-6.149756264494537</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.622113515327861</v>
+        <v>0.5134711375510048</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9777246230073772</v>
+        <v>-1.147121016710878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.387095293858141</v>
+        <v>2.285457457636041</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.803860754314059</v>
+        <v>-6.075466698756198</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6508498192394936</v>
+        <v>0.5422074414626374</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9034350572690379</v>
+        <v>-1.072831450972539</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.430689510917442</v>
+        <v>2.329051674695342</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.740225012080124</v>
+        <v>-6.011830956522264</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6809989171873845</v>
+        <v>0.5723565394105288</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8397993150351034</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.47356575731212</v>
+        <v>2.37192792109002</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.628798252754204</v>
+        <v>-5.900404197196344</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7067638797015485</v>
+        <v>0.5981215019246924</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8397993150351034</v>
+        <v>-1.009195708738604</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.454760016095916</v>
+        <v>2.353122179873815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.388367755949344</v>
+        <v>-5.659973700391483</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8046791550483698</v>
+        <v>0.6960367772715141</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5993688182302431</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.600761390803709</v>
+        <v>2.499123554581609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.316125187778149</v>
+        <v>-5.587731132220289</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8375054961516679</v>
+        <v>0.7288631183748122</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5993688182302431</v>
+        <v>-0.7687652119337436</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.604690704638529</v>
+        <v>2.503052868416429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.263126865496761</v>
+        <v>-5.534732809938901</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8593834089815631</v>
+        <v>0.7507410312047074</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5440325592283043</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.638571043957032</v>
+        <v>2.536933207734932</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.154321980017034</v>
+        <v>-5.425927924459174</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8999034343934476</v>
+        <v>0.7912610566165914</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5440325592283043</v>
+        <v>-0.7134289529318047</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.635569115177026</v>
+        <v>2.533931278954926</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.934301181980024</v>
+        <v>-5.205907126422163</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9894907906188657</v>
+        <v>0.8808484128420098</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.402812714160324</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.721880059228428</v>
+        <v>2.620242223006328</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.801433492916746</v>
+        <v>-5.073039437358886</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.058532049046</v>
+        <v>0.949889671269144</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.402812714160324</v>
+        <v>-0.5722091078638245</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.737774242030252</v>
+        <v>2.636136405808151</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.681260409552247</v>
+        <v>-4.952866353994387</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.107747126832102</v>
+        <v>0.9991047490552456</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2826396307958251</v>
+        <v>-0.4520360244993256</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.811023936489253</v>
+        <v>2.709386100267153</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.53658826445251</v>
+        <v>-4.808194208894649</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.175704087433436</v>
+        <v>1.06706170965658</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1379674856960877</v>
+        <v>-0.3073638793995881</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.907915326110535</v>
+        <v>2.806277489888435</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.596463091810202</v>
+        <v>-4.868069036252342</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.137791647891785</v>
+        <v>1.029149270114929</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1978423130537798</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.858027921097346</v>
+        <v>2.756390084875245</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.509663594031194</v>
+        <v>-4.781269538473333</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.194911940325955</v>
+        <v>1.086269562549099</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1978423130537798</v>
+        <v>-0.3672387067572803</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.880428414419912</v>
+        <v>2.778790578197811</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.512133300493</v>
+        <v>-4.783739244935139</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.193996459114644</v>
+        <v>1.085354081337788</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.200312019515586</v>
+        <v>-0.3697084132190864</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.87901899191624</v>
+        <v>2.77738115569414</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.58050348681701</v>
+        <v>-4.85210943125915</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.177655307059742</v>
+        <v>1.069012929282886</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.191036320479371</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.895591333812671</v>
+        <v>2.793953497590571</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.594291539664057</v>
+        <v>-4.865897484106196</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.162576794552815</v>
+        <v>1.053934416775959</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.191036320479371</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.886028042444563</v>
+        <v>2.784390206222462</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.492449106153027</v>
+        <v>-4.896890643434902</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.028023332997614</v>
+        <v>0.8662467180848636</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.191036320479371</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.710737607484949</v>
+        <v>2.609099771262849</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.316974846360557</v>
+        <v>-4.721416383642433</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.102780268906389</v>
+        <v>0.9410036539936391</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.191036320479371</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.715304839476737</v>
+        <v>2.613667003254637</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.427911099001806</v>
+        <v>-4.832352636283682</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.034147796611097</v>
+        <v>0.8723711816983464</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.191036320479371</v>
+        <v>-0.3604327141828715</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.691046868237944</v>
+        <v>2.589409032015844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.394247553529524</v>
+        <v>-4.7986890908114</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.050744600019915</v>
+        <v>0.8889679851071648</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1573727750070892</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.714376380741219</v>
+        <v>2.612738544519118</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.3343949343258</v>
+        <v>-4.738836471607677</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.084858034133537</v>
+        <v>0.9230814192207866</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1573727750070892</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.724548767173351</v>
+        <v>2.622910930951251</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.248151471299423</v>
+        <v>-4.652593008581299</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.114301689917948</v>
+        <v>0.9525250750051979</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1573727750070892</v>
+        <v>-0.3267691687105896</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.719495037747211</v>
+        <v>2.617857201525111</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316042</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.293458290698402</v>
+        <v>-4.697899827980279</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.087954737602882</v>
+        <v>0.9261781226901316</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.19818293801632</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.686784715386199</v>
+        <v>2.585146879164098</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.322491395400704</v>
+        <v>-4.72693293268258</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.076893368755063</v>
+        <v>0.9151167538423126</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.19818293801632</v>
+        <v>-0.3675793317198204</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.6873365884193</v>
+        <v>2.5856987521972</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.229680913949844</v>
+        <v>-4.63412245123172</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.043290253226773</v>
+        <v>0.8815136383140221</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1053724565654606</v>
+        <v>-0.2747688502689611</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.672295569181181</v>
+        <v>2.570657732959081</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.274070383279271</v>
+        <v>-4.678511920561148</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.027407941419602</v>
+        <v>0.865631326506852</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1497619258948883</v>
+        <v>-0.3191583195983888</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.647535363508126</v>
+        <v>2.545897527286025</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472742</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.161399165043021</v>
+        <v>-4.565840702324897</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.067552137225825</v>
+        <v>0.905775522313075</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03709070765863809</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.710213802961599</v>
+        <v>2.608575966739498</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798542</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.049022163860348</v>
+        <v>-4.453463701142224</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117994233529562</v>
+        <v>0.9562176186168114</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03709070765863809</v>
+        <v>-0.2064871013621385</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.715705098792266</v>
+        <v>2.614067262570166</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498869</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.076802561761701</v>
+        <v>-4.481244099043577</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.11837927613756</v>
+        <v>0.9566026612248095</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.06487110555999115</v>
+        <v>-0.2342674992634916</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.710534061819993</v>
+        <v>2.608896225597893</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170533</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.15980384278698</v>
+        <v>-4.564245380068856</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9235344837281017</v>
+        <v>0.7617578688153512</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.08344199008716491</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.537747251104342</v>
+        <v>2.436109414882242</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729274</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.268417921230311</v>
+        <v>-4.672859458512187</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.000238513069975</v>
+        <v>0.8384618981572243</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.08344199008716491</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.657896911823548</v>
+        <v>2.556259075601448</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.233008882982168</v>
+        <v>-4.637450420264044</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.028915154471555</v>
+        <v>0.8671385395588045</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.08344199008716491</v>
+        <v>-0.2528383837906654</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.672409937925871</v>
+        <v>2.570772101703771</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913431</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.194625220424017</v>
+        <v>-4.599066757705893</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.041688060837184</v>
+        <v>0.8799114459244337</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.04505832752901373</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.69285957680313</v>
+        <v>2.59122174058103</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532491</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.017508890388851</v>
+        <v>-4.421950427670727</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.109263621696552</v>
+        <v>0.9474870067838019</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.04505832752901373</v>
+        <v>-0.2144547212325142</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.689588605648432</v>
+        <v>2.587950769426332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793909</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.062601135222397</v>
+        <v>-4.467042672504273</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.091910115525047</v>
+        <v>0.9301335006122968</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1069543706984035</v>
+        <v>-0.276350764401904</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.653134371508711</v>
+        <v>2.551496535286611</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011242</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.883225713983629</v>
+        <v>-4.406244088534566</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.157447259326969</v>
+        <v>0.9482399095065936</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04982238747231515</v>
+        <v>-0.265731905710716</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.740987401717557</v>
+        <v>2.551654825807738</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982236</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.928239927504235</v>
+        <v>-4.451258302055173</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.120249029250316</v>
+        <v>0.9110416794299407</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01947349215771055</v>
+        <v>-0.2960808010253206</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.703585519860384</v>
+        <v>2.514252943950565</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509544</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.195244437776671</v>
+        <v>-4.718262812327608</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.019138787480288</v>
+        <v>0.8099314376599125</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.174889545885238</v>
+        <v>-0.4904438390682692</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.592659259373561</v>
+        <v>2.403326683463742</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.296442219213843</v>
+        <v>-4.819460593764781</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9778635968019198</v>
+        <v>0.768656246981545</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2432983594305572</v>
+        <v>-0.5588526526135884</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.55081789314287</v>
+        <v>2.361485317233051</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.289931252599531</v>
+        <v>-4.812949627150468</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9780679450019616</v>
+        <v>0.7688605951815868</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2432983594305572</v>
+        <v>-0.5588526526135884</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.548417854697187</v>
+        <v>2.359085278787369</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.270893124892233</v>
+        <v>-4.793911499443171</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9822079152931256</v>
+        <v>0.7730005654727505</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3014819707617518</v>
+        <v>-0.6170362639447829</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.510032407106715</v>
+        <v>2.320699831196896</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131257</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.302019756042852</v>
+        <v>-4.825038130593789</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.147339131771559</v>
+        <v>0.9381317819511836</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3014819707617518</v>
+        <v>-0.6170362639447829</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.687614276045396</v>
+        <v>2.498281700135577</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067872</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.31588651737677</v>
+        <v>-4.838904891927707</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.142625756224125</v>
+        <v>0.9334184064037501</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3393398874955747</v>
+        <v>-0.6548941806786058</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.665732854991236</v>
+        <v>2.476400279081417</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789129</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.27108234583684</v>
+        <v>-4.794100720387777</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.166555955237023</v>
+        <v>0.957348605416648</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3393398874955747</v>
+        <v>-0.6548941806786058</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.671741385388162</v>
+        <v>2.482408809478343</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519915</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.123339375601837</v>
+        <v>-4.646357750152775</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.304805791123046</v>
+        <v>1.095598441302671</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1715325302606915</v>
+        <v>-0.4870868234437227</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.851578447521113</v>
+        <v>2.662245871611295</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181177</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.225354058133059</v>
+        <v>-4.748372432683996</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.266793539642038</v>
+        <v>1.057586189821663</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1715325302606915</v>
+        <v>-0.4870868234437227</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.854372069052594</v>
+        <v>2.665039493142776</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394738</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.219201352080274</v>
+        <v>-4.742219726631212</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.269916970454811</v>
+        <v>1.060709620634436</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1653798242079073</v>
+        <v>-0.4809341173909384</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.858726041075923</v>
+        <v>2.669393465166105</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890616</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.236010650230776</v>
+        <v>-4.759029024781714</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.26227372793472</v>
+        <v>1.053066378114345</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1821891223584089</v>
+        <v>-0.49774341554144</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.847720938925733</v>
+        <v>2.658388363015914</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798432</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.173712651454654</v>
+        <v>-4.696731026005591</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.35352848124199</v>
+        <v>1.144321131421615</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1821891223584089</v>
+        <v>-0.49774341554144</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.914056492722553</v>
+        <v>2.724723916812735</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992198</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.971922453789496</v>
+        <v>-4.494940828340433</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.142825432697451</v>
+        <v>0.9336180828770759</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.0158290698107455</v>
+        <v>-0.2997252233722856</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.741448280413444</v>
+        <v>2.552115704503625</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852428</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.898544356700759</v>
+        <v>-4.421562731251697</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.242466903855121</v>
+        <v>1.033259554034746</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.08920716689948205</v>
+        <v>-0.2263471262835491</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.855765370988861</v>
+        <v>2.666432795079043</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.996284901325734</v>
+        <v>-4.519303275876672</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.217998422121175</v>
+        <v>1.0087910723008</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.07331788876650186</v>
+        <v>-0.2422364044165293</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.860859540225117</v>
+        <v>2.671526964315298</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489391</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.172622661448663</v>
+        <v>-4.695641035999601</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145999298896675</v>
+        <v>0.9367919490762995</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1030198713564275</v>
+        <v>-0.4185741645394587</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.753592864976031</v>
+        <v>2.564260289066212</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397801</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.096200615016737</v>
+        <v>-4.619218989567674</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.175059735509374</v>
+        <v>0.9658523856889989</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1030198713564275</v>
+        <v>-0.4185741645394587</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.75208448301596</v>
+        <v>2.562751907106141</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024969</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.051827483378168</v>
+        <v>-4.574845857929105</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.192671855600237</v>
+        <v>0.9834645057798626</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.05864673971785894</v>
+        <v>-0.3742010329008901</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.778571229434537</v>
+        <v>2.589238653524718</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863229</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.043873513083396</v>
+        <v>-4.566891887634333</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.195853443718146</v>
+        <v>0.9866460938977712</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.05864673971785894</v>
+        <v>-0.3742010329008901</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.778571229434537</v>
+        <v>2.589238653524718</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947588</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.99621778252234</v>
+        <v>-4.519236157073277</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.221297492970373</v>
+        <v>1.012090143149998</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.01099100915680329</v>
+        <v>-0.3265453023398344</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.813546424798975</v>
+        <v>2.624213848889156</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326881</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.895699624023585</v>
+        <v>-4.418717998574523</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.2663971297446</v>
+        <v>1.057189779924225</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.08952714934195127</v>
+        <v>-0.2260271438410799</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.878749693272952</v>
+        <v>2.689417117363134</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314556</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.956366214425974</v>
+        <v>-4.479384588976911</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.228885166059517</v>
+        <v>1.019677816239142</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.007828832623417603</v>
+        <v>-0.3077254605596135</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.816485375717704</v>
+        <v>2.627152799807886</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690031</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.911527812817576</v>
+        <v>-4.434546187368513</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.250918229313504</v>
+        <v>1.04171087949313</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01237226556828708</v>
+        <v>-0.3031820276147441</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.823309138095255</v>
+        <v>2.633976562185436</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674308</v>
+        <v>3.817961388674315</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.012286448574574</v>
+        <v>-4.535304823125511</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.214775714641783</v>
+        <v>1.005568364821408</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07645330315871834</v>
+        <v>-0.3920075963417495</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.774174736490129</v>
+        <v>2.58484216058031</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163217</v>
+        <v>3.826713779163224</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.968083611488674</v>
+        <v>-4.49110198603961</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.23833645200398</v>
+        <v>1.029129102183606</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.0322504660728179</v>
+        <v>-0.347804759255849</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.806576041269507</v>
+        <v>2.617243465359688</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022909</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.005062639152117</v>
+        <v>-4.528081013703053</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.221954841407851</v>
+        <v>1.012747491587476</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.004723435718512636</v>
+        <v>-0.3108308574645185</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.827170382813553</v>
+        <v>2.637837806903734</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042143</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.025120718016957</v>
+        <v>-4.548139092567894</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.265179375044954</v>
+        <v>1.05597202522458</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.004723435718512636</v>
+        <v>-0.3108308574645185</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.878418147996592</v>
+        <v>2.689085572086773</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078285</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.985190044839067</v>
+        <v>-4.508208419390003</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.279592348910364</v>
+        <v>1.070384999089989</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04465410889640298</v>
+        <v>-0.2709001842866282</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.90081725649758</v>
+        <v>2.711484680587761</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232403</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.934157952116539</v>
+        <v>-4.457176326667476</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.294953414237645</v>
+        <v>1.08574606441727</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.09568620161893093</v>
+        <v>-0.2198680915641002</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.926384740369366</v>
+        <v>2.737052164459548</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416211</v>
+        <v>3.842576394162117</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.868933770989333</v>
+        <v>-4.39195214554027</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.338230490781232</v>
+        <v>1.129023140960857</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1609103827461366</v>
+        <v>-0.1546439104368946</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.982706653138395</v>
+        <v>2.793374077228576</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639814</v>
+        <v>3.840090220639822</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.831506750918199</v>
+        <v>-4.354525125469136</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.349162271108966</v>
+        <v>1.139954921288591</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1661619207753182</v>
+        <v>-0.1493923724077129</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.981818548255184</v>
+        <v>2.792485972345365</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749927</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.851618406952908</v>
+        <v>-4.374636781503844</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.342374401026323</v>
+        <v>1.133167051205948</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1771892657727374</v>
+        <v>-0.1383650274102937</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.989691747584876</v>
+        <v>2.800359171675057</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393552</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.797873592525703</v>
+        <v>-4.32089196707664</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.524430097818416</v>
+        <v>1.315222747998041</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1872525752131994</v>
+        <v>-0.1283017179698318</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.156287504270364</v>
+        <v>2.966954928360545</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714882</v>
+        <v>3.81325185471489</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.77408202391956</v>
+        <v>-4.297100398470498</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.65405963447869</v>
+        <v>1.444852284658315</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2110441438193417</v>
+        <v>-0.1045101493636895</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.290675354651866</v>
+        <v>3.101342778742048</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756008</v>
+        <v>3.814259761756016</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.747997939655753</v>
+        <v>-4.271016314206689</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.656201244198072</v>
+        <v>1.446993894377697</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2110441438193417</v>
+        <v>-0.1045101493636895</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.282383330665725</v>
+        <v>3.093050754755907</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654183</v>
+        <v>3.803426852654191</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.617705408726143</v>
+        <v>-4.14072378327708</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.706511452153695</v>
+        <v>1.49730410233332</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.4475797683470765</v>
+        <v>0.1320254751640453</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.422497900966146</v>
+        <v>3.233165325056327</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717113</v>
+        <v>3.796293177717121</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.60881294733286</v>
+        <v>-4.131831321883797</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.7276228424378</v>
+        <v>1.518415492617425</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.4475797683470765</v>
+        <v>0.1320254751640453</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.440052306692937</v>
+        <v>3.250719730783119</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702631</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.777289064302737</v>
+        <v>-4.300307438853674</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.652087443054433</v>
+        <v>1.442880093234058</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.4196319326304957</v>
+        <v>0.1040776394474646</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.415138652667573</v>
+        <v>3.225806076757754</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539965</v>
+        <v>3.795603100539973</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.079489535441154</v>
+        <v>-3.602507909992091</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.912476951786928</v>
+        <v>1.703269601966553</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.349283873260085</v>
+        <v>0.03372958007705384</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.354199514233188</v>
+        <v>3.164866938323369</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389894</v>
+        <v>3.784700379389902</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.056768431758002</v>
+        <v>-3.579786806308939</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.912229415757093</v>
+        <v>1.703022065936719</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.349283873260085</v>
+        <v>0.03372958007705384</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.344863536730093</v>
+        <v>3.155530960820274</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534931</v>
+        <v>3.783234730534939</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.055043388467958</v>
+        <v>-3.578061763018895</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.07182555892428</v>
+        <v>1.862618209103905</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.3510089165501287</v>
+        <v>0.03545462336709759</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.504804688555288</v>
+        <v>3.315472112645469</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401671</v>
+        <v>3.779962759401678</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.209824395246213</v>
+        <v>-3.73284276979715</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.046990978706624</v>
+        <v>1.83778362888625</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3176412424956526</v>
+        <v>0.002086949312621489</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.521861906616249</v>
+        <v>3.33252933070643</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557219</v>
+        <v>3.769472653557226</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.27708483926813</v>
+        <v>-3.800103213819067</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.016762157087403</v>
+        <v>1.807554807267028</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2503807984737355</v>
+        <v>-0.06517349470929562</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.478180996192644</v>
+        <v>3.288848420282825</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088375</v>
+        <v>3.766702530088382</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.254613305229298</v>
+        <v>-3.777631679780236</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.035756924347677</v>
+        <v>1.826549574527302</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3860862832897067</v>
+        <v>0.0705319901066756</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.569610440726968</v>
+        <v>3.380277864817149</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541367</v>
+        <v>3.768081101541374</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.211867895841856</v>
+        <v>-3.913584687836551</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.236958220247613</v>
+        <v>1.956271503449735</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3860862832897067</v>
+        <v>0.0705319901066756</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.753713572871928</v>
+        <v>3.564380996962109</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471681</v>
+        <v>3.743954539471687</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.234276013646728</v>
+        <v>-3.935992805641424</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.220111668028658</v>
+        <v>1.93942495123078</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3860862832897067</v>
+        <v>0.0705319901066756</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.745830267774921</v>
+        <v>3.556497691865102</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912293</v>
+        <v>3.719147660912299</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.349355472287071</v>
+        <v>-4.051072264281766</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.176133884122158</v>
+        <v>1.89544716732428</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4180960740042691</v>
+        <v>0.1025417808212379</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.767090141753296</v>
+        <v>3.577757565843477</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.758647133936188</v>
+        <v>3.422200500930965</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.617846702263856</v>
+        <v>3.331565823202216</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.349355472287071</v>
+        <v>-4.051072264281766</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.176133884122158</v>
+        <v>1.89544716732428</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.4180960740042691</v>
+        <v>0.1025417808212379</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.610910499250224</v>
+        <v>3.324629620188584</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>61.2%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>55.3%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>30.7%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-68.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>459.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-566.7%</t>
+          <t>-533.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>141.9%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.7%</t>
+          <t>-173.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-187.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.7%</t>
+          <t>-183.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.6%</t>
+          <t>-70.0%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.970216533276535</v>
+        <v>-7.054007619506448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3221829147907709</v>
+        <v>0.2886664802988057</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.636397717737438</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.386608407563532</v>
+        <v>-7.470399493793446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1536202156848496</v>
+        <v>0.120103781192884</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.636397717737438</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.630879808290602</v>
+        <v>-7.714670894520515</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06617034606270078</v>
+        <v>0.03265391157073516</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.636397717737438</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.836130827527362</v>
+        <v>-7.919921913757276</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0198304964863083</v>
+        <v>-0.05334693097827392</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.636397717737438</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.999710705711745</v>
+        <v>-8.083501791941659</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.08685752770506072</v>
+        <v>-0.1203739621970263</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.636397717737438</v>
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.296372047521944</v>
+        <v>-8.171305399860103</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2017430884999318</v>
+        <v>-0.1517164294351954</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.590545120834721</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.094077642739804</v>
+        <v>2.16283508232176</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.483091755831246</v>
+        <v>-8.358025108169405</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2804572763580562</v>
+        <v>-0.2304306172933197</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.590545120834721</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0900513382054</v>
+        <v>2.158808777787357</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.866093144573878</v>
+        <v>-8.741026496912037</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4337599331766926</v>
+        <v>-0.3837332741119561</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.705140853471316</v>
+        <v>-1.590545120834721</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.089949236883816</v>
+        <v>2.158706676465773</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.047962935558912</v>
+        <v>-8.922896287897071</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5039363335992761</v>
+        <v>-0.4539096745345401</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.772414911819757</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.983398878264226</v>
+        <v>2.052156317846182</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.407493258062914</v>
+        <v>-9.282426610401073</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.642398159302827</v>
+        <v>-0.5923715002380905</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.887010644456351</v>
+        <v>-1.772414911819757</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.988749181562276</v>
+        <v>2.057506621144233</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.457842321517136</v>
+        <v>-9.332775673855295</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.654621764727338</v>
+        <v>-0.6045951056626016</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.937359707910573</v>
+        <v>-1.822763975273979</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.96645576344692</v>
+        <v>2.035213203028877</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.555461598938532</v>
+        <v>-9.430394951276691</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6906277250741275</v>
+        <v>-0.6406010660093915</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.03497898533197</v>
+        <v>-1.920383252695375</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.91092594761585</v>
+        <v>1.979683387197808</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.702987686944175</v>
+        <v>-9.577921039282334</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7467446039548125</v>
+        <v>-0.6967179448900764</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.182505073337614</v>
+        <v>-2.067909340701019</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.825303851134037</v>
+        <v>1.894061290715994</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.907245862274038</v>
+        <v>-9.782179214612198</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8229346769681158</v>
+        <v>-0.7729080179033794</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.310144017951603</v>
+        <v>-2.195548285315008</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.754233681484286</v>
+        <v>1.822991121066243</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.981578838534203</v>
+        <v>-9.856512190872362</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8481853129877455</v>
+        <v>-0.798158653923009</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.454843541886275</v>
+        <v>-2.34024780924968</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.671896521607918</v>
+        <v>1.740653961189875</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.908109006866754</v>
+        <v>-9.783042359204913</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8034256788273448</v>
+        <v>-0.7533990197626084</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.381373710218827</v>
+        <v>-2.266777977582232</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.731350122101808</v>
+        <v>1.800107561683765</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.0832334242533</v>
+        <v>-9.958166776591456</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8589202250344457</v>
+        <v>-0.8088935659697087</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.441902394968776</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.640830692417399</v>
+        <v>1.709588131999356</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31768551826779</v>
+        <v>-10.19261887060595</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9599202275418368</v>
+        <v>-0.9098935684771008</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.556498127605371</v>
+        <v>-2.441902394968776</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.633611527515803</v>
+        <v>1.70236896709776</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.42206024929423</v>
+        <v>-10.29699360163239</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.008342310726392</v>
+        <v>-0.9583156516616556</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.660872858631816</v>
+        <v>-2.546277125995222</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.564314498125959</v>
+        <v>1.633071937707916</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.47484640489456</v>
+        <v>-10.34977975723272</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.028340983127967</v>
+        <v>-0.9783143240632297</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.756548345214213</v>
+        <v>-2.641952612577619</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.508024996015078</v>
+        <v>1.576782435597034</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.60088319826285</v>
+        <v>-10.47581655060101</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.076061971846168</v>
+        <v>-1.026035312781431</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.616700989767876</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.525869698330037</v>
+        <v>1.594627137911994</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.54886768429404</v>
+        <v>-10.4238010366322</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.051265430572241</v>
+        <v>-1.001238771507505</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.616700989767876</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.529860034016438</v>
+        <v>1.598617473598395</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.69053952601816</v>
+        <v>-10.56547287835632</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.109409394160631</v>
+        <v>-1.059382735095895</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.731296722404471</v>
+        <v>-2.616700989767876</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.528384807117697</v>
+        <v>1.597142246699653</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.64094868159332</v>
+        <v>-10.51588203393148</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.074519646225825</v>
+        <v>-1.024492987161089</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.681705877979637</v>
+        <v>-2.567110145343042</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.573192723937469</v>
+        <v>1.641950163519426</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.62814128858855</v>
+        <v>-10.50307464092671</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.082447822670598</v>
+        <v>-1.032421163605862</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.730561652988538</v>
+        <v>-2.615965920351944</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.530828125285446</v>
+        <v>1.599585564867402</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.40229613586914</v>
+        <v>-10.2772294882073</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9825306885466252</v>
+        <v>-0.9325040294818892</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.57403924476478</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.565563203673952</v>
+        <v>1.634320643255909</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.27771747953154</v>
+        <v>-10.15265083186971</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9315600814555292</v>
+        <v>-0.881533422390794</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.688634977401374</v>
+        <v>-2.57403924476478</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.566702348230011</v>
+        <v>1.635459787811968</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.33061276757583</v>
+        <v>-10.20554611991399</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9500844225111367</v>
+        <v>-0.9000577634464006</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.569083898676334</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.572309330045187</v>
+        <v>1.641066769627143</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25847959228795</v>
+        <v>-10.13341294462611</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.915497448157347</v>
+        <v>-0.8654707890926119</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.683679631312928</v>
+        <v>-2.569083898676334</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.578043034283823</v>
+        <v>1.64680047386578</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.1871131996783</v>
+        <v>-10.06204655201646</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8966881535073536</v>
+        <v>-0.8466614944426176</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.497717506066686</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.611125607455747</v>
+        <v>1.679883047037704</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.09365416569308</v>
+        <v>-9.968587518031239</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8691880212261718</v>
+        <v>-0.8191613621614358</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.497717506066686</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.601242126142839</v>
+        <v>1.669999565724796</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.924199947928738</v>
+        <v>-9.701345717162841</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8032408946198091</v>
+        <v>-0.7140992023134505</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.61231323870328</v>
+        <v>-2.497717506066686</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.599407565643466</v>
+        <v>1.668165005225422</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.826292909252247</v>
+        <v>-9.60343867848635</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7643783941226738</v>
+        <v>-0.6752367018163148</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.544327488842724</v>
+        <v>-2.429731756206129</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.639898700586339</v>
+        <v>1.708656140168295</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.802339368276289</v>
+        <v>-9.579485137510392</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7541284715867969</v>
+        <v>-0.6649867792804383</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.520373947866766</v>
+        <v>-2.405778215230172</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.654939331317407</v>
+        <v>1.723696770899364</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.538279429953493</v>
+        <v>-9.315425199187596</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6617648124194302</v>
+        <v>-0.5726231201130716</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.141718276907376</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.800114978149332</v>
+        <v>1.868872417731289</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.831199806448655</v>
+        <v>-8.608345575682758</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3817199966777962</v>
+        <v>-0.2925783043714376</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.25631400954397</v>
+        <v>-2.141718276907376</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.797327944489031</v>
+        <v>1.866085384070988</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.791015508082465</v>
+        <v>-8.568161277316568</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3653026534434787</v>
+        <v>-0.2761609611371201</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.216129711177779</v>
+        <v>-2.101533978541185</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.821782147396587</v>
+        <v>1.890539586978544</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.627615637143101</v>
+        <v>-8.404761406377204</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3005758838469763</v>
+        <v>-0.2114341915406177</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.052729840238417</v>
+        <v>-1.938134107601822</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.919188891180962</v>
+        <v>1.987946330762918</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.394134414913502</v>
+        <v>-8.171280184147605</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1992589661172843</v>
+        <v>-0.1101172738109257</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.819248618008818</v>
+        <v>-1.704652885372224</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.067202053356573</v>
+        <v>2.13595949293853</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.244468023905988</v>
+        <v>-8.021613793140091</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1422846200272376</v>
+        <v>-0.05314292772087903</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.726345126766282</v>
+        <v>-1.611749394129688</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.120051937789135</v>
+        <v>2.188809377371092</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.1121925502751</v>
+        <v>-7.889338319509204</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.09400694382785568</v>
+        <v>-0.004865251521497527</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.594069653135396</v>
+        <v>-1.479473920498801</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.194784708714694</v>
+        <v>2.263542148296651</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.956454217715359</v>
+        <v>-7.733599986949462</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02889655011632231</v>
+        <v>0.06024514219003585</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.32373558793906</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.291042768938176</v>
+        <v>2.359800208520133</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.707454419031778</v>
+        <v>-7.484600188265881</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08360971058076894</v>
+        <v>0.1727514028871271</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.438331320575654</v>
+        <v>-1.32373558793906</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.303949110161835</v>
+        <v>2.372706549743792</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.813044408804882</v>
+        <v>-7.590190178038986</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08660221492769171</v>
+        <v>0.002539477378666888</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.543921310348759</v>
+        <v>-1.429325577712164</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.112619186698754</v>
+        <v>2.18137662628071</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.831779310923479</v>
+        <v>-7.608925080157583</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.04555183389804407</v>
+        <v>0.04358985840831409</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.54951732000889</v>
+        <v>-1.434921587372295</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.157805922779761</v>
+        <v>2.226563362361718</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.68383926951588</v>
+        <v>-7.460985038749984</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1062547400231719</v>
+        <v>-0.01711304771681377</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.529196404100332</v>
+        <v>-1.414600671463738</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.050119549636728</v>
+        <v>2.118876989218685</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.630869747261891</v>
+        <v>-7.408015516495995</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.09378091737505478</v>
+        <v>-0.004639225068696184</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.361631149209749</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.073187276735643</v>
+        <v>2.1419447163176</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.587321340491201</v>
+        <v>-7.364467109725305</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08332216676187176</v>
+        <v>0.005819525544486837</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.361631149209749</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.06622666464055</v>
+        <v>2.134984104222507</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.345172947037343</v>
+        <v>-7.122318716271447</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02799954500081459</v>
+        <v>0.1171412373071732</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.361631149209749</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.080689019021693</v>
+        <v>2.14944645860365</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.236913809914821</v>
+        <v>-7.014059579148925</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06583532030901829</v>
+        <v>0.1549770126153769</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.476226881846344</v>
+        <v>-1.361631149209749</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.075221139480888</v>
+        <v>2.143978579062845</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.11362267509769</v>
+        <v>-6.890768444331794</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1126498682464474</v>
+        <v>0.201791560552806</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.352935747029213</v>
+        <v>-1.238340014392619</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.146693914381743</v>
+        <v>2.2154513539637</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.092473476194247</v>
+        <v>-6.869619245428351</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1288105260451502</v>
+        <v>0.2179522183515084</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.217190815489175</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.167084411961135</v>
+        <v>2.235841851543091</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.848708034210802</v>
+        <v>-6.625853803444906</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2220974111855782</v>
+        <v>0.3112391034919368</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.33178654812577</v>
+        <v>-1.217190815489175</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.162865120308185</v>
+        <v>2.231622559890142</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.746945213933508</v>
+        <v>-6.524090983167611</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2649268532165125</v>
+        <v>0.3540685455228707</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.203971747096747</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.172920875263658</v>
+        <v>2.241678314845615</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.497094819984433</v>
+        <v>-6.274240589218537</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3576090857798442</v>
+        <v>0.4467507780862028</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.203971747096747</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.165662950247361</v>
+        <v>2.234420389829317</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.321202727517001</v>
+        <v>-6.098348496751104</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4315650462874658</v>
+        <v>0.5207067385938249</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.318567479733341</v>
+        <v>-1.203971747096747</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.169262073768009</v>
+        <v>2.238019513349966</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.149756264494537</v>
+        <v>-5.92690203372864</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5134711375510048</v>
+        <v>0.6026128298573639</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.147121016710878</v>
+        <v>-1.032525284074283</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.285457457636041</v>
+        <v>2.354214897217997</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.075466698756198</v>
+        <v>-5.852612467990301</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5422074414626374</v>
+        <v>0.6313491337689965</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.072831450972539</v>
+        <v>-0.958235718335944</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.329051674695342</v>
+        <v>2.397809114277298</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.011830956522264</v>
+        <v>-5.788976725756367</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5723565394105288</v>
+        <v>0.6614982317168874</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8945999761020095</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.37192792109002</v>
+        <v>2.440685360671976</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.900404197196344</v>
+        <v>-5.677549966430447</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5981215019246924</v>
+        <v>0.6872631942310514</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.009195708738604</v>
+        <v>-0.8945999761020095</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.353122179873815</v>
+        <v>2.421879619455772</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.659973700391483</v>
+        <v>-5.437119469625586</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6960367772715141</v>
+        <v>0.7851784695778727</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6541694792971492</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.499123554581609</v>
+        <v>2.567880994163565</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.587731132220289</v>
+        <v>-5.364876901454392</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7288631183748122</v>
+        <v>0.8180048106811708</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7687652119337436</v>
+        <v>-0.6541694792971492</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.503052868416429</v>
+        <v>2.571810307998386</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.534732809938901</v>
+        <v>-5.311878579173004</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7507410312047074</v>
+        <v>0.839882723511066</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5988332202952104</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.536933207734932</v>
+        <v>2.605690647316889</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.425927924459174</v>
+        <v>-5.203073693693277</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7912610566165914</v>
+        <v>0.8804027489229505</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7134289529318047</v>
+        <v>-0.5988332202952104</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.533931278954926</v>
+        <v>2.602688718536883</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675941</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.205907126422163</v>
+        <v>-4.983052895656266</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8808484128420098</v>
+        <v>0.9699901051483686</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.4576133752272301</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.620242223006328</v>
+        <v>2.688999662588285</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.073039437358886</v>
+        <v>-4.850185206592989</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.949889671269144</v>
+        <v>1.039031363575503</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5722091078638245</v>
+        <v>-0.4576133752272301</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.636136405808151</v>
+        <v>2.704893845390108</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.952866353994387</v>
+        <v>-4.73001212322849</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9991047490552456</v>
+        <v>1.088246441361604</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4520360244993256</v>
+        <v>-0.3374402918627312</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.709386100267153</v>
+        <v>2.778143539849109</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.808194208894649</v>
+        <v>-4.585339978128752</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.06706170965658</v>
+        <v>1.156203401962939</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3073638793995881</v>
+        <v>-0.1927681467629938</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.806277489888435</v>
+        <v>2.875034929470392</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.868069036252342</v>
+        <v>-4.645214805486445</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.029149270114929</v>
+        <v>1.118290962421288</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2526429741206859</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.756390084875245</v>
+        <v>2.825147524457202</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.781269538473333</v>
+        <v>-4.558415307707437</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.086269562549099</v>
+        <v>1.175411254855458</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3672387067572803</v>
+        <v>-0.2526429741206859</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.778790578197811</v>
+        <v>2.847548017779768</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.783739244935139</v>
+        <v>-4.560885014169243</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.085354081337788</v>
+        <v>1.174495773644147</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3697084132190864</v>
+        <v>-0.255112680582492</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.77738115569414</v>
+        <v>2.846138595276097</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.85210943125915</v>
+        <v>-4.629255200493253</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.069012929282886</v>
+        <v>1.158154621589245</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2458369815462771</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.793953497590571</v>
+        <v>2.862710937172527</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.865897484106196</v>
+        <v>-4.643043253340299</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.053934416775959</v>
+        <v>1.143076109082318</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2458369815462771</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.784390206222462</v>
+        <v>2.853147645804419</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.896890643434902</v>
+        <v>-4.674036412669005</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8662467180848636</v>
+        <v>0.9553884103912225</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2458369815462771</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.609099771262849</v>
+        <v>2.677857210844806</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.721416383642433</v>
+        <v>-4.498562152876536</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9410036539936391</v>
+        <v>1.030145346299998</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2458369815462771</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.613667003254637</v>
+        <v>2.682424442836593</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.832352636283682</v>
+        <v>-4.609498405517785</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8723711816983464</v>
+        <v>0.9615128740047052</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3604327141828715</v>
+        <v>-0.2458369815462771</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.589409032015844</v>
+        <v>2.6581664715978</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.7986890908114</v>
+        <v>-4.575834860045503</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8889679851071648</v>
+        <v>0.9781096774135236</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2121734360739952</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.612738544519118</v>
+        <v>2.681495984101075</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.738836471607677</v>
+        <v>-4.51598224084178</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9230814192207866</v>
+        <v>1.012223111527145</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2121734360739952</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.622910930951251</v>
+        <v>2.691668370533208</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.652593008581299</v>
+        <v>-4.429738777815402</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9525250750051979</v>
+        <v>1.041666767311557</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3267691687105896</v>
+        <v>-0.2121734360739952</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.617857201525111</v>
+        <v>2.686614641107068</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.697899827980279</v>
+        <v>-4.475045597214382</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9261781226901316</v>
+        <v>1.01531981499649</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.252983599083226</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.585146879164098</v>
+        <v>2.653904318746055</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.72693293268258</v>
+        <v>-4.504078701916683</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9151167538423126</v>
+        <v>1.004258446148671</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3675793317198204</v>
+        <v>-0.252983599083226</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.5856987521972</v>
+        <v>2.654456191779157</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.63412245123172</v>
+        <v>-4.411268220465823</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8815136383140221</v>
+        <v>0.9706553306203809</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2747688502689611</v>
+        <v>-0.1601731176323667</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.570657732959081</v>
+        <v>2.639415172541038</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.678511920561148</v>
+        <v>-4.455657689795251</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.865631326506852</v>
+        <v>0.9547730188132109</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3191583195983888</v>
+        <v>-0.2045625869617944</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.545897527286025</v>
+        <v>2.614654966867982</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.565840702324897</v>
+        <v>-4.342986471559001</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.905775522313075</v>
+        <v>0.9949172146194338</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.09189136872554415</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.608575966739498</v>
+        <v>2.677333406321455</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.453463701142224</v>
+        <v>-4.230609470376328</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9562176186168114</v>
+        <v>1.04535931092317</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2064871013621385</v>
+        <v>-0.09189136872554415</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.614067262570166</v>
+        <v>2.682824702152122</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.481244099043577</v>
+        <v>-4.25838986827768</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9566026612248095</v>
+        <v>1.045744353531168</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2342674992634916</v>
+        <v>-0.1196717666268972</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.608896225597893</v>
+        <v>2.67765366517985</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.564245380068856</v>
+        <v>-4.341391149302959</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7617578688153512</v>
+        <v>0.8508995611217101</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.138242651154071</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.436109414882242</v>
+        <v>2.504866854464199</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.672859458512187</v>
+        <v>-4.45000522774629</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8384618981572243</v>
+        <v>0.9276035904635831</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.138242651154071</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.556259075601448</v>
+        <v>2.625016515183404</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.637450420264044</v>
+        <v>-4.414596189498147</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8671385395588045</v>
+        <v>0.9562802318651633</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2528383837906654</v>
+        <v>-0.138242651154071</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.570772101703771</v>
+        <v>2.639529541285727</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.599066757705893</v>
+        <v>-4.376212526939996</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8799114459244337</v>
+        <v>0.9690531382307923</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.0998589885959198</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.59122174058103</v>
+        <v>2.659979180162987</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.421950427670727</v>
+        <v>-4.19909619690483</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9474870067838019</v>
+        <v>1.036628699090161</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2144547212325142</v>
+        <v>-0.0998589885959198</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.587950769426332</v>
+        <v>2.656708209008289</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.467042672504273</v>
+        <v>-4.244188441738376</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9301335006122968</v>
+        <v>1.019275192918656</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.276350764401904</v>
+        <v>-0.1617550317653096</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.551496535286611</v>
+        <v>2.620253974868568</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.406244088534566</v>
+        <v>-4.064813020499608</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9482399095065936</v>
+        <v>1.084812336720577</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.265731905710716</v>
+        <v>-0.00497827359459091</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.551654825807738</v>
+        <v>2.708107005077413</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.451258302055173</v>
+        <v>-4.109827234020214</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9110416794299407</v>
+        <v>1.047614106643924</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2960808010253206</v>
+        <v>-0.03532716890919552</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.514252943950565</v>
+        <v>2.67070512322024</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509544</v>
+        <v>3.737026608509545</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.718262812327608</v>
+        <v>-4.376831744292649</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8099314376599125</v>
+        <v>0.9465038648738962</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4904438390682692</v>
+        <v>-0.2296902069521441</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.403326683463742</v>
+        <v>2.559778862733417</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.819460593764781</v>
+        <v>-4.478029525729822</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.768656246981545</v>
+        <v>0.9052286741955284</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5588526526135884</v>
+        <v>-0.2980990204974633</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.361485317233051</v>
+        <v>2.517937496502727</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.812949627150468</v>
+        <v>-4.471518559115509</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7688605951815868</v>
+        <v>0.9054330223955702</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5588526526135884</v>
+        <v>-0.2980990204974633</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.359085278787369</v>
+        <v>2.515537458057044</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.793911499443171</v>
+        <v>-4.452480431408212</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7730005654727505</v>
+        <v>0.9095729926867342</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.6170362639447829</v>
+        <v>-0.3562826318286578</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.320699831196896</v>
+        <v>2.477152010466572</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.825038130593789</v>
+        <v>-4.48360706255883</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9381317819511836</v>
+        <v>1.074704209165167</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.6170362639447829</v>
+        <v>-0.3562826318286578</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.498281700135577</v>
+        <v>2.654733879405252</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.838904891927707</v>
+        <v>-4.497473823892748</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9334184064037501</v>
+        <v>1.069990833617734</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.6548941806786058</v>
+        <v>-0.3941405485624808</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.476400279081417</v>
+        <v>2.632852458351092</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.794100720387777</v>
+        <v>-4.452669652352818</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.957348605416648</v>
+        <v>1.093921032630632</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.6548941806786058</v>
+        <v>-0.3941405485624808</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.482408809478343</v>
+        <v>2.638860988748018</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.646357750152775</v>
+        <v>-4.304926682117816</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.095598441302671</v>
+        <v>1.232170868516655</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4870868234437227</v>
+        <v>-0.2263331913275976</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.662245871611295</v>
+        <v>2.81869805088097</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.748372432683996</v>
+        <v>-4.406941364649037</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.057586189821663</v>
+        <v>1.194158617035647</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4870868234437227</v>
+        <v>-0.2263331913275976</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.665039493142776</v>
+        <v>2.821491672412451</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394738</v>
+        <v>3.805608985394739</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.742219726631212</v>
+        <v>-4.400788658596253</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.060709620634436</v>
+        <v>1.197282047848419</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4809341173909384</v>
+        <v>-0.2201804852748133</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.669393465166105</v>
+        <v>2.82584564443578</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.759029024781714</v>
+        <v>-4.417597956746754</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.053066378114345</v>
+        <v>1.189638805328329</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.49774341554144</v>
+        <v>-0.236989783425315</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.658388363015914</v>
+        <v>2.814840542285589</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.696731026005591</v>
+        <v>-4.355299957970632</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.144321131421615</v>
+        <v>1.280893558635599</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.49774341554144</v>
+        <v>-0.236989783425315</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.724723916812735</v>
+        <v>2.88117609608241</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992198</v>
+        <v>3.848729139992199</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.494940828340433</v>
+        <v>-4.153509760305474</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9336180828770759</v>
+        <v>1.07019051009106</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.2997252233722856</v>
+        <v>-0.03897159125616056</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.552115704503625</v>
+        <v>2.708567883773301</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852428</v>
+        <v>3.841444817852429</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.421562731251697</v>
+        <v>-4.080131663216738</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.033259554034746</v>
+        <v>1.169831981248729</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.2263471262835491</v>
+        <v>0.03440650583257598</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.666432795079043</v>
+        <v>2.822884974348718</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.819063300319553</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.519303275876672</v>
+        <v>-4.177872207841713</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.0087910723008</v>
+        <v>1.145363499514783</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.2422364044165293</v>
+        <v>0.0185172276995958</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.671526964315298</v>
+        <v>2.827979143584973</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489391</v>
+        <v>3.831819032489392</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.695641035999601</v>
+        <v>-4.354209967964642</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9367919490762995</v>
+        <v>1.073364376290283</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.4185741645394587</v>
+        <v>-0.1578205324233336</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.564260289066212</v>
+        <v>2.720712468335887</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.619218989567674</v>
+        <v>-4.277787921532715</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9658523856889989</v>
+        <v>1.102424812902982</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.4185741645394587</v>
+        <v>-0.1578205324233336</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.562751907106141</v>
+        <v>2.719204086375816</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024969</v>
+        <v>3.83602339102497</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.574845857929105</v>
+        <v>-4.233414789894146</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9834645057798626</v>
+        <v>1.120036932993846</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3742010329008901</v>
+        <v>-0.113447400784765</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.589238653524718</v>
+        <v>2.745690832794393</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.566891887634333</v>
+        <v>-4.225460819599374</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9866460938977712</v>
+        <v>1.123218521111755</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3742010329008901</v>
+        <v>-0.113447400784765</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.589238653524718</v>
+        <v>2.745690832794393</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.519236157073277</v>
+        <v>-4.177805089038318</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.012090143149998</v>
+        <v>1.148662570363982</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.3265453023398344</v>
+        <v>-0.06579167022370935</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.624213848889156</v>
+        <v>2.780666028158831</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.418717998574523</v>
+        <v>-4.077286930539564</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.057189779924225</v>
+        <v>1.193762207138209</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.2260271438410799</v>
+        <v>0.03472648827504521</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.689417117363134</v>
+        <v>2.845869296632809</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.479384588976911</v>
+        <v>-4.137953520941952</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.019677816239142</v>
+        <v>1.156250243453125</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.3077254605596135</v>
+        <v>-0.04697182844348846</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.627152799807886</v>
+        <v>2.783604979077561</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.434546187368513</v>
+        <v>-4.093115119333554</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.04171087949313</v>
+        <v>1.178283306707113</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.3031820276147441</v>
+        <v>-0.04242839549861899</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.633976562185436</v>
+        <v>2.790428741455111</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.535304823125511</v>
+        <v>-4.193873755090552</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.005568364821408</v>
+        <v>1.142140792035392</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.3920075963417495</v>
+        <v>-0.1312539642256244</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.58484216058031</v>
+        <v>2.741294339849986</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.49110198603961</v>
+        <v>-4.149670918004651</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.029129102183606</v>
+        <v>1.165701529397589</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.347804759255849</v>
+        <v>-0.08705112713972396</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.617243465359688</v>
+        <v>2.773695644629363</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.528081013703053</v>
+        <v>-4.186649945668094</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.012747491587476</v>
+        <v>1.14931991880146</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.3108308574645185</v>
+        <v>-0.05007722534839343</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.637837806903734</v>
+        <v>2.794289986173409</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.548139092567894</v>
+        <v>-4.206708024532935</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.05597202522458</v>
+        <v>1.192544452438563</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.3108308574645185</v>
+        <v>-0.05007722534839343</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.689085572086773</v>
+        <v>2.845537751356449</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.508208419390003</v>
+        <v>-4.166777351355044</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.070384999089989</v>
+        <v>1.206957426303973</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.2709001842866282</v>
+        <v>-0.01014655217050309</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.711484680587761</v>
+        <v>2.867936859857436</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.457176326667476</v>
+        <v>-4.115745258632517</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.08574606441727</v>
+        <v>1.222318491631254</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.2198680915641002</v>
+        <v>0.04088554055202487</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.737052164459548</v>
+        <v>2.893504343729223</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162117</v>
+        <v>3.842576394162118</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.39195214554027</v>
+        <v>-4.050521077505311</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.129023140960857</v>
+        <v>1.265595568174841</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.1546439104368946</v>
+        <v>0.1061097216792305</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.793374077228576</v>
+        <v>2.949826256498251</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.354525125469136</v>
+        <v>-4.013094057434177</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.139954921288591</v>
+        <v>1.276527348502575</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1493923724077129</v>
+        <v>0.1113612597084122</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.792485972345365</v>
+        <v>2.948938151615041</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.374636781503844</v>
+        <v>-3.937055559933169</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.133167051205948</v>
+        <v>1.308199539834218</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1383650274102937</v>
+        <v>0.1667878751359986</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.800359171675057</v>
+        <v>2.983450913202833</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393552</v>
+        <v>3.828690479393553</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.32089196707664</v>
+        <v>-3.883310745505964</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.315222747998041</v>
+        <v>1.490255236626311</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.1283017179698318</v>
+        <v>0.1768511845764605</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.966954928360545</v>
+        <v>3.15004666988832</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81325185471489</v>
+        <v>3.813251854714891</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.297100398470498</v>
+        <v>-3.859519176899822</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.444852284658315</v>
+        <v>1.619884773286585</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.1045101493636895</v>
+        <v>0.2006427531826028</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.101342778742048</v>
+        <v>3.284434520269823</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.271016314206689</v>
+        <v>-3.833435092636014</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.446993894377697</v>
+        <v>1.622026383005967</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.1045101493636895</v>
+        <v>0.2006427531826028</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.093050754755907</v>
+        <v>3.276142496283682</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.14072378327708</v>
+        <v>-3.703142561706404</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.49730410233332</v>
+        <v>1.672336590961591</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1320254751640453</v>
+        <v>0.4371783777103376</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.233165325056327</v>
+        <v>3.416257066584103</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.131831321883797</v>
+        <v>-3.694250100313121</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.518415492617425</v>
+        <v>1.693447981245696</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1320254751640453</v>
+        <v>0.4371783777103376</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.250719730783119</v>
+        <v>3.433811472310894</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.300307438853674</v>
+        <v>-3.862726217282999</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.442880093234058</v>
+        <v>1.617912581862328</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1040776394474646</v>
+        <v>0.4092305419937569</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.225806076757754</v>
+        <v>3.408897818285529</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.602507909992091</v>
+        <v>-3.164926688421415</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.703269601966553</v>
+        <v>1.878302090594823</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.03372958007705384</v>
+        <v>0.3388824826233461</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.164866938323369</v>
+        <v>3.347958679851145</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389902</v>
+        <v>3.784700379389903</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.579786806308939</v>
+        <v>-3.142205584738263</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.703022065936719</v>
+        <v>1.878054554564989</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.03372958007705384</v>
+        <v>0.3388824826233461</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.155530960820274</v>
+        <v>3.338622702348049</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534939</v>
+        <v>3.78323473053494</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.578061763018895</v>
+        <v>-3.140480541448219</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.862618209103905</v>
+        <v>2.037650697732175</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.03545462336709759</v>
+        <v>0.3406075259133899</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.315472112645469</v>
+        <v>3.498563854173244</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401678</v>
+        <v>3.779962759401679</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.73284276979715</v>
+        <v>-3.295261548226474</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.83778362888625</v>
+        <v>2.01281611751452</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.002086949312621489</v>
+        <v>0.3072398518589138</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.33252933070643</v>
+        <v>3.515621072234206</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.800103213819067</v>
+        <v>-3.362521992248391</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.807554807267028</v>
+        <v>1.982587295895298</v>
       </c>
       <c r="F2001" t="n">
-        <v>-0.06517349470929562</v>
+        <v>0.2399794078369967</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.288848420282825</v>
+        <v>3.471940161810601</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.777631679780236</v>
+        <v>-3.340050458209559</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.826549574527302</v>
+        <v>2.001582063155573</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.0705319901066756</v>
+        <v>0.3756848926529679</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.380277864817149</v>
+        <v>3.563369606344925</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541374</v>
+        <v>3.768081101541375</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.913584687836551</v>
+        <v>-3.476003466265875</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.956271503449735</v>
+        <v>2.131303992078006</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.0705319901066756</v>
+        <v>0.3756848926529679</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.564380996962109</v>
+        <v>3.747472738489884</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471687</v>
+        <v>3.743954539471688</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.935992805641424</v>
+        <v>-3.498411584070747</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.93942495123078</v>
+        <v>2.11445743985905</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.0705319901066756</v>
+        <v>0.3756848926529679</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.556497691865102</v>
+        <v>3.739589433392878</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912299</v>
+        <v>3.719147660912297</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-4.051072264281766</v>
+        <v>-3.61349104271109</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.89544716732428</v>
+        <v>2.070479655952551</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.1025417808212379</v>
+        <v>0.4076946833675302</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.577757565843477</v>
+        <v>3.760849307371252</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.422200500930965</v>
+        <v>3.827904403490383</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.331565823202216</v>
+        <v>3.515864382084098</v>
       </c>
       <c r="D2006" t="n">
-        <v>-4.051072264281766</v>
+        <v>-3.714858310411099</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.89544716732428</v>
+        <v>2.029564633605911</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.1025417808212379</v>
+        <v>0.4076946833675302</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.324629620188584</v>
+        <v>3.760481192104616</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240625.xlsx
+++ b/tame_output/ON/bt/strategyON_20240625.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.1%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.9%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>459.4%</t>
+          <t>459.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-533.1%</t>
+          <t>-527.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-39.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-173.3%</t>
+          <t>-171.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-187.2%</t>
+          <t>-130.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-183.2%</t>
+          <t>-162.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.0%</t>
+          <t>-57.2%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.171305399860103</v>
+        <v>-8.380163133751857</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1517164294351954</v>
+        <v>-0.2352595229918975</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.590545120834721</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.16283508232176</v>
+        <v>2.094077642739804</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.358025108169405</v>
+        <v>-8.56688284206116</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2304306172933197</v>
+        <v>-0.3139737108500213</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.590545120834721</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.158808777787357</v>
+        <v>2.0900513382054</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.741026496912037</v>
+        <v>-8.949884230803791</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3837332741119561</v>
+        <v>-0.4672763676686582</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.590545120834721</v>
+        <v>-1.705140853471316</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.158706676465773</v>
+        <v>2.089949236883816</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.922896287897071</v>
+        <v>-9.008103444105194</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4539096745345401</v>
+        <v>-0.4879925370177891</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.772414911819757</v>
+        <v>-1.763360066772719</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.052156317846182</v>
+        <v>2.057589224874405</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.282426610401073</v>
+        <v>-9.367633766609195</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5923715002380905</v>
+        <v>-0.6264543627213395</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.772414911819757</v>
+        <v>-1.763360066772719</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.057506621144233</v>
+        <v>2.062939528172455</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.332775673855295</v>
+        <v>-9.417982830063417</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6045951056626016</v>
+        <v>-0.6386779681458505</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.822763975273979</v>
+        <v>-1.813709130226941</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.035213203028877</v>
+        <v>2.040646110057099</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.430394951276691</v>
+        <v>-9.515602107484813</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6406010660093915</v>
+        <v>-0.6746839284926405</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.920383252695375</v>
+        <v>-1.770709777894683</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.979683387197808</v>
+        <v>2.069487472078223</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.577921039282334</v>
+        <v>-9.535927553836919</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6967179448900764</v>
+        <v>-0.6799205507119104</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.067909340701019</v>
+        <v>-1.791035224246788</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.894061290715994</v>
+        <v>2.060185760588532</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.782179214612198</v>
+        <v>-9.740185729166782</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7729080179033794</v>
+        <v>-0.7561106237252133</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.195548285315008</v>
+        <v>-1.918674168860777</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.822991121066243</v>
+        <v>1.989115590938781</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.856512190872362</v>
+        <v>-9.814518705426947</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.798158653923009</v>
+        <v>-0.7813612597448429</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.34024780924968</v>
+        <v>-2.06337369279545</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.740653961189875</v>
+        <v>1.906778431062413</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.783042359204913</v>
+        <v>-9.741048873759498</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7533990197626084</v>
+        <v>-0.7366016255844423</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.266777977582232</v>
+        <v>-1.989903861128001</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.800107561683765</v>
+        <v>1.966232031556304</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.958166776591456</v>
+        <v>-9.916173291146041</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8088935659697087</v>
+        <v>-0.7920961717915427</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.441902394968776</v>
+        <v>-2.165028278514545</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.709588131999356</v>
+        <v>1.875712601871894</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.19261887060595</v>
+        <v>-10.15062538516053</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9098935684771008</v>
+        <v>-0.8930961742989347</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.441902394968776</v>
+        <v>-2.165028278514545</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.70236896709776</v>
+        <v>1.868493436970298</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.29699360163239</v>
+        <v>-10.25500011618698</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9583156516616556</v>
+        <v>-0.9415182574834895</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.546277125995222</v>
+        <v>-2.269403009540991</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.633071937707916</v>
+        <v>1.799196407580454</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.34977975723272</v>
+        <v>-10.3077862717873</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9783143240632297</v>
+        <v>-0.9615169298850637</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.641952612577619</v>
+        <v>-2.365078496123388</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.576782435597034</v>
+        <v>1.742906905469572</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.47581655060101</v>
+        <v>-10.43382306515559</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.026035312781431</v>
+        <v>-1.009237918603265</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.616700989767876</v>
+        <v>-2.339826873313646</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.594627137911994</v>
+        <v>1.760751607784533</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.4238010366322</v>
+        <v>-10.38180755118678</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.001238771507505</v>
+        <v>-0.9844413773293388</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.616700989767876</v>
+        <v>-2.339826873313646</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.598617473598395</v>
+        <v>1.764741943470933</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.56547287835632</v>
+        <v>-10.5234793929109</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.059382735095895</v>
+        <v>-1.042585340917729</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.616700989767876</v>
+        <v>-2.339826873313646</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.597142246699653</v>
+        <v>1.763266716572192</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.51588203393148</v>
+        <v>-10.47388854848607</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.024492987161089</v>
+        <v>-1.007695592982923</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.567110145343042</v>
+        <v>-2.290236028888812</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.641950163519426</v>
+        <v>1.808074633391964</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.50307464092671</v>
+        <v>-10.46108115548129</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.032421163605862</v>
+        <v>-1.015623769427696</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.615965920351944</v>
+        <v>-2.339091803897713</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.599585564867402</v>
+        <v>1.765710034739941</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.2772294882073</v>
+        <v>-10.23523600276188</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9325040294818892</v>
+        <v>-0.9157066353037222</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.57403924476478</v>
+        <v>-2.297165128310549</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.634320643255909</v>
+        <v>1.800445113128448</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.15265083186971</v>
+        <v>-10.11065734642429</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.881533422390794</v>
+        <v>-0.8647360282126271</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.57403924476478</v>
+        <v>-2.297165128310549</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.635459787811968</v>
+        <v>1.801584257684506</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.20554611991399</v>
+        <v>-10.16355263446857</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9000577634464006</v>
+        <v>-0.8832603692682337</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.569083898676334</v>
+        <v>-2.292209782222103</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.641066769627143</v>
+        <v>1.807191239499682</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.13341294462611</v>
+        <v>-10.09141945918069</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8654707890926119</v>
+        <v>-0.8486733949144449</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.569083898676334</v>
+        <v>-2.292209782222103</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.64680047386578</v>
+        <v>1.812924943738318</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.06204655201646</v>
+        <v>-10.02005306657105</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8466614944426176</v>
+        <v>-0.8298641002644516</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.497717506066686</v>
+        <v>-2.220843389612455</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.679883047037704</v>
+        <v>1.846007516910242</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.968587518031239</v>
+        <v>-9.926594032585822</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8191613621614358</v>
+        <v>-0.8023639679832688</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.497717506066686</v>
+        <v>-2.220843389612455</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.669999565724796</v>
+        <v>1.836124035597334</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.701345717162841</v>
+        <v>-9.659352231717424</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7140992023134505</v>
+        <v>-0.6973018081352835</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.497717506066686</v>
+        <v>-2.220843389612455</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.668165005225422</v>
+        <v>1.834289475097961</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.60343867848635</v>
+        <v>-9.561445193040933</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6752367018163148</v>
+        <v>-0.6584393076381483</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.429731756206129</v>
+        <v>-2.152857639751899</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.708656140168295</v>
+        <v>1.874780610040834</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.579485137510392</v>
+        <v>-9.537491652064976</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6649867792804383</v>
+        <v>-0.6481893851022713</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.405778215230172</v>
+        <v>-2.128904098775941</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.723696770899364</v>
+        <v>1.889821240771902</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.315425199187596</v>
+        <v>-9.273431713742179</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5726231201130716</v>
+        <v>-0.5558257259349046</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.141718276907376</v>
+        <v>-1.864844160453145</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.868872417731289</v>
+        <v>2.034996887603827</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.608345575682758</v>
+        <v>-8.566352090237341</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2925783043714376</v>
+        <v>-0.2757809101932707</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.141718276907376</v>
+        <v>-1.864844160453145</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.866085384070988</v>
+        <v>2.032209853943526</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.568161277316568</v>
+        <v>-8.526167791871151</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2761609611371201</v>
+        <v>-0.2593635669589531</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.101533978541185</v>
+        <v>-1.824659862086954</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.890539586978544</v>
+        <v>2.056664056851083</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.404761406377204</v>
+        <v>-8.362767920931788</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2114341915406177</v>
+        <v>-0.1946367973624508</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.938134107601822</v>
+        <v>-1.661259991147592</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.987946330762918</v>
+        <v>2.154070800635457</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.171280184147605</v>
+        <v>-8.12624832637546</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1101172738109257</v>
+        <v>-0.09210453070206759</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.704652885372224</v>
+        <v>-1.424740396591264</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.13595949293853</v>
+        <v>2.303906986207106</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.021613793140091</v>
+        <v>-7.976581935367945</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05314292772087903</v>
+        <v>-0.03513018461202089</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.611749394129688</v>
+        <v>-1.331836905348728</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.188809377371092</v>
+        <v>2.356756870639668</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.889338319509204</v>
+        <v>-7.844306461737059</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.004865251521497527</v>
+        <v>0.01314749158736062</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.479473920498801</v>
+        <v>-1.199561431717842</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.263542148296651</v>
+        <v>2.431489641565227</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105953</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.733599986949462</v>
+        <v>-7.688568129177317</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.06024514219003585</v>
+        <v>0.07825788529889444</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.32373558793906</v>
+        <v>-1.0438230991581</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.359800208520133</v>
+        <v>2.527747701788709</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.75388257196099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.484600188265881</v>
+        <v>-7.439568330493736</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1727514028871271</v>
+        <v>0.1907641459959852</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.32373558793906</v>
+        <v>-1.0438230991581</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.372706549743792</v>
+        <v>2.540654043012367</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.590190178038986</v>
+        <v>-7.54515832026684</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.002539477378666888</v>
+        <v>0.02055222048752503</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.429325577712164</v>
+        <v>-1.149413088931204</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.18137662628071</v>
+        <v>2.349324119549286</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987904</v>
+        <v>3.770422583987906</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.608925080157583</v>
+        <v>-7.563893222385437</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.04358985840831409</v>
+        <v>0.06160260151717267</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.434921587372295</v>
+        <v>-1.155009098591336</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.226563362361718</v>
+        <v>2.394510855630294</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.460985038749984</v>
+        <v>-7.415953180977838</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.01711304771681377</v>
+        <v>0.0008996953920448192</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.414600671463738</v>
+        <v>-1.134688182682778</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.118876989218685</v>
+        <v>2.286824482487261</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.408015516495995</v>
+        <v>-7.36298365872385</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.004639225068696184</v>
+        <v>0.01337351804016196</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.361631149209749</v>
+        <v>-1.081718660428789</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1419447163176</v>
+        <v>2.309892209586176</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.364467109725305</v>
+        <v>-7.319435251953159</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.005819525544486837</v>
+        <v>0.02383226865334498</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.361631149209749</v>
+        <v>-1.081718660428789</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.134984104222507</v>
+        <v>2.302931597491082</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.122318716271447</v>
+        <v>-7.077286858499301</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1171412373071732</v>
+        <v>0.1351539804160313</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.361631149209749</v>
+        <v>-1.081718660428789</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14944645860365</v>
+        <v>2.317393951872226</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.014059579148925</v>
+        <v>-6.969027721376779</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1549770126153769</v>
+        <v>0.172989755724235</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.361631149209749</v>
+        <v>-1.081718660428789</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.143978579062845</v>
+        <v>2.311926072331421</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.890768444331794</v>
+        <v>-6.845736586559648</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.201791560552806</v>
+        <v>0.2198043036616641</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.238340014392619</v>
+        <v>-0.9584275256116589</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2154513539637</v>
+        <v>2.383398847232276</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.869619245428351</v>
+        <v>-6.824587387656205</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2179522183515084</v>
+        <v>0.2359649614603665</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.217190815489175</v>
+        <v>-0.9372783267082155</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.235841851543091</v>
+        <v>2.403789344811667</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.625853803444906</v>
+        <v>-6.580821945672761</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3112391034919368</v>
+        <v>0.329251846600795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.217190815489175</v>
+        <v>-0.9372783267082155</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.231622559890142</v>
+        <v>2.399570053158718</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.524090983167611</v>
+        <v>-6.479059125395466</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3540685455228707</v>
+        <v>0.3720812886317288</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.203971747096747</v>
+        <v>-0.9240592583157868</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.241678314845615</v>
+        <v>2.409625808114191</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.274240589218537</v>
+        <v>-6.229208731446391</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4467507780862028</v>
+        <v>0.4647635211950609</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.203971747096747</v>
+        <v>-0.9240592583157868</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.234420389829317</v>
+        <v>2.402367883097893</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.098348496751104</v>
+        <v>-6.053316638978959</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5207067385938249</v>
+        <v>0.5387194817026826</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.203971747096747</v>
+        <v>-0.9240592583157868</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.238019513349966</v>
+        <v>2.405967006618542</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.92690203372864</v>
+        <v>-5.881870175956496</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6026128298573639</v>
+        <v>0.6206255729662216</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.032525284074283</v>
+        <v>-0.7526127952933237</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.354214897217997</v>
+        <v>2.522162390486574</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.852612467990301</v>
+        <v>-5.807580610218157</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6313491337689965</v>
+        <v>0.6493618768778542</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.958235718335944</v>
+        <v>-0.6783232295549844</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.397809114277298</v>
+        <v>2.565756607545874</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.788976725756367</v>
+        <v>-5.743944867984222</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6614982317168874</v>
+        <v>0.6795109748257455</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8945999761020095</v>
+        <v>-0.6146874873210498</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.440685360671976</v>
+        <v>2.608632853940552</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074786</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.677549966430447</v>
+        <v>-5.632518108658302</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6872631942310514</v>
+        <v>0.7052759373399091</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8945999761020095</v>
+        <v>-0.6146874873210498</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.421879619455772</v>
+        <v>2.589827112724348</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242298</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.437119469625586</v>
+        <v>-5.392087611853442</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7851784695778727</v>
+        <v>0.8031912126867304</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6541694792971492</v>
+        <v>-0.3742569905161895</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.567880994163565</v>
+        <v>2.735828487432141</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.364876901454392</v>
+        <v>-5.319845043682247</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8180048106811708</v>
+        <v>0.8360175537900285</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6541694792971492</v>
+        <v>-0.3742569905161895</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.571810307998386</v>
+        <v>2.739757801266961</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.311878579173004</v>
+        <v>-5.266846721400859</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.839882723511066</v>
+        <v>0.8578954666199237</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5988332202952104</v>
+        <v>-0.3189207315142507</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.605690647316889</v>
+        <v>2.773638140585465</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.203073693693277</v>
+        <v>-5.158041835921132</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8804027489229505</v>
+        <v>0.8984154920318081</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5988332202952104</v>
+        <v>-0.3189207315142507</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.602688718536883</v>
+        <v>2.770636211805458</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.818668951675943</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.983052895656266</v>
+        <v>-4.938021037884122</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9699901051483686</v>
+        <v>0.9880028482572265</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4576133752272301</v>
+        <v>-0.1777008864462705</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.688999662588285</v>
+        <v>2.85694715585686</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.850185206592989</v>
+        <v>-4.805153348820844</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.039031363575503</v>
+        <v>1.057044106684361</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4576133752272301</v>
+        <v>-0.1777008864462705</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.704893845390108</v>
+        <v>2.872841338658684</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.73001212322849</v>
+        <v>-4.684980265456345</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.088246441361604</v>
+        <v>1.106259184470462</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3374402918627312</v>
+        <v>-0.05752780308177152</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.778143539849109</v>
+        <v>2.946091033117685</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.585339978128752</v>
+        <v>-4.540308120356608</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.156203401962939</v>
+        <v>1.174216145071797</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1927681467629938</v>
+        <v>0.08714434201796589</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.875034929470392</v>
+        <v>3.042982422738967</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.645214805486445</v>
+        <v>-4.6001829477143</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.118290962421288</v>
+        <v>1.136303705530146</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2526429741206859</v>
+        <v>0.02726951466027377</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.825147524457202</v>
+        <v>2.993095017725778</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.558415307707437</v>
+        <v>-4.513383449935292</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.175411254855458</v>
+        <v>1.193423997964315</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2526429741206859</v>
+        <v>0.02726951466027377</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.847548017779768</v>
+        <v>3.015495511048344</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.560885014169243</v>
+        <v>-4.515853156397098</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.174495773644147</v>
+        <v>1.192508516753005</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.255112680582492</v>
+        <v>0.02479980819846761</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.846138595276097</v>
+        <v>3.014086088544672</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.629255200493253</v>
+        <v>-4.584223342721108</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.158154621589245</v>
+        <v>1.176167364698103</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2458369815462771</v>
+        <v>0.03407550723468256</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.862710937172527</v>
+        <v>3.030658430441104</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.643043253340299</v>
+        <v>-4.598011395568155</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.143076109082318</v>
+        <v>1.161088852191176</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2458369815462771</v>
+        <v>0.03407550723468256</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.853147645804419</v>
+        <v>3.021095139072995</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417708</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.674036412669005</v>
+        <v>-4.62900455489686</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9553884103912225</v>
+        <v>0.9734011535000804</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2458369815462771</v>
+        <v>0.03407550723468256</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.677857210844806</v>
+        <v>2.845804704113382</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205903</v>
+        <v>3.746042526205905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.498562152876536</v>
+        <v>-4.453530295104391</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.030145346299998</v>
+        <v>1.048158089408856</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2458369815462771</v>
+        <v>0.03407550723468256</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.682424442836593</v>
+        <v>2.850371936105169</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.609498405517785</v>
+        <v>-4.56446654774564</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9615128740047052</v>
+        <v>0.9795256171135631</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2458369815462771</v>
+        <v>0.03407550723468256</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.6581664715978</v>
+        <v>2.826113964866376</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111298</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.575834860045503</v>
+        <v>-4.530803002273358</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9781096774135236</v>
+        <v>0.9961224205223815</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2121734360739952</v>
+        <v>0.0677390527069644</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.681495984101075</v>
+        <v>2.849443477369651</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264168</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.51598224084178</v>
+        <v>-4.470950383069635</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.012223111527145</v>
+        <v>1.030235854636003</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2121734360739952</v>
+        <v>0.0677390527069644</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.691668370533208</v>
+        <v>2.859615863801783</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742304</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.429738777815402</v>
+        <v>-4.384706920043257</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.041666767311557</v>
+        <v>1.059679510420415</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2121734360739952</v>
+        <v>0.0677390527069644</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.686614641107068</v>
+        <v>2.854562134375644</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316051</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.475045597214382</v>
+        <v>-4.430013739442237</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.01531981499649</v>
+        <v>1.033332558105348</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.252983599083226</v>
+        <v>0.0269288896977336</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.653904318746055</v>
+        <v>2.821851812014631</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803196</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.504078701916683</v>
+        <v>-4.459046844144538</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.004258446148671</v>
+        <v>1.022271189257529</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.252983599083226</v>
+        <v>0.0269288896977336</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.654456191779157</v>
+        <v>2.822403685047732</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.411268220465823</v>
+        <v>-4.366236362693678</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9706553306203809</v>
+        <v>0.9886680737292388</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1601731176323667</v>
+        <v>0.119739371148593</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.639415172541038</v>
+        <v>2.807362665809614</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560429</v>
+        <v>3.748285816560431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.455657689795251</v>
+        <v>-4.410625832023106</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9547730188132109</v>
+        <v>0.9727857619220686</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2045625869617944</v>
+        <v>0.07534990181916529</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.614654966867982</v>
+        <v>2.782602460136558</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472742</v>
+        <v>3.721077195472744</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.342986471559001</v>
+        <v>-4.297954613786856</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9949172146194338</v>
+        <v>1.012929957728292</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.09189136872554415</v>
+        <v>0.1880211200554155</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.677333406321455</v>
+        <v>2.845280899590031</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798542</v>
+        <v>3.743047603798543</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.230609470376328</v>
+        <v>-4.185577612604183</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.04535931092317</v>
+        <v>1.063372054032028</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.09189136872554415</v>
+        <v>0.1880211200554155</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.682824702152122</v>
+        <v>2.850772195420698</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498869</v>
+        <v>3.689597840498871</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.25838986827768</v>
+        <v>-4.213358010505535</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.045744353531168</v>
+        <v>1.063757096640026</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1196717666268972</v>
+        <v>0.1602407221540624</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.67765366517985</v>
+        <v>2.845601158448425</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170533</v>
+        <v>3.643069621705331</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.341391149302959</v>
+        <v>-4.296359291530814</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8508995611217101</v>
+        <v>0.8689123042305678</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.138242651154071</v>
+        <v>0.1416698376268887</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.504866854464199</v>
+        <v>2.672814347732774</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729274</v>
+        <v>3.682716310729276</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.45000522774629</v>
+        <v>-4.404973369974146</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9276035904635831</v>
+        <v>0.945616333572441</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.138242651154071</v>
+        <v>0.1416698376268887</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.625016515183404</v>
+        <v>2.79296400845198</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190773</v>
+        <v>3.733012441190775</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.414596189498147</v>
+        <v>-4.369564331726003</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9562802318651633</v>
+        <v>0.9742929749740212</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.138242651154071</v>
+        <v>0.1416698376268887</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.639529541285727</v>
+        <v>2.807477034554303</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913431</v>
+        <v>3.741174069913432</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.376212526939996</v>
+        <v>-4.331180669167852</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9690531382307923</v>
+        <v>0.9870658813396502</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.0998589885959198</v>
+        <v>0.1800535001850398</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.659979180162987</v>
+        <v>2.827926673431562</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532491</v>
+        <v>3.751147197532493</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.19909619690483</v>
+        <v>-4.154064339132685</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.036628699090161</v>
+        <v>1.054641442199019</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.0998589885959198</v>
+        <v>0.1800535001850398</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.656708209008289</v>
+        <v>2.824655702276864</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793909</v>
+        <v>3.741328448793911</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.244188441738376</v>
+        <v>-4.199156583966231</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.019275192918656</v>
+        <v>1.037287936027513</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1617550317653096</v>
+        <v>0.1181574570156501</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.620253974868568</v>
+        <v>2.788201468137144</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011242</v>
+        <v>3.750729377011243</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.064813020499608</v>
+        <v>-4.019781162727464</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.084812336720577</v>
+        <v>1.102825079829435</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.00497827359459091</v>
+        <v>0.2749342151863687</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.708107005077413</v>
+        <v>2.876054498345989</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982236</v>
+        <v>3.716991718982237</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.109827234020214</v>
+        <v>-4.064795376248069</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.047614106643924</v>
+        <v>1.065626849752782</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.03532716890919552</v>
+        <v>0.2445853198717641</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.67070512322024</v>
+        <v>2.838652616488816</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509545</v>
+        <v>3.737026608509546</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.376831744292649</v>
+        <v>-4.331799886520504</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9465038648738962</v>
+        <v>0.9645166079827541</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2296902069521441</v>
+        <v>0.05022228182881555</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.559778862733417</v>
+        <v>2.727726356001993</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760817</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.478029525729822</v>
+        <v>-4.432997667957677</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9052286741955284</v>
+        <v>0.9232414173043864</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2980990204974633</v>
+        <v>-0.01818653171650364</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.517937496502727</v>
+        <v>2.685884989771302</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815462</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.471518559115509</v>
+        <v>-4.426486701343364</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9054330223955702</v>
+        <v>0.9234457655044281</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2980990204974633</v>
+        <v>-0.01818653171650364</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.515537458057044</v>
+        <v>2.683484951325619</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378107</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.452480431408212</v>
+        <v>-4.407448573636067</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9095729926867342</v>
+        <v>0.9275857357955921</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3562826318286578</v>
+        <v>-0.07637014304769818</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.477152010466572</v>
+        <v>2.645099503735147</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131257</v>
+        <v>3.731064473131259</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.48360706255883</v>
+        <v>-4.438575204786686</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.074704209165167</v>
+        <v>1.092716952274025</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3562826318286578</v>
+        <v>-0.07637014304769818</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.654733879405252</v>
+        <v>2.822681372673828</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067872</v>
+        <v>3.722447362067874</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.497473823892748</v>
+        <v>-4.452441966120603</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.069990833617734</v>
+        <v>1.088003576726592</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3941405485624808</v>
+        <v>-0.1142280597815211</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.632852458351092</v>
+        <v>2.800799951619668</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789129</v>
+        <v>3.78742558078913</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.452669652352818</v>
+        <v>-4.407637794580674</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.093921032630632</v>
+        <v>1.11193377573949</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3941405485624808</v>
+        <v>-0.1142280597815211</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.638860988748018</v>
+        <v>2.806808482016594</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519915</v>
+        <v>3.781501250519917</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.304926682117816</v>
+        <v>-4.259894824345671</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.232170868516655</v>
+        <v>1.250183611625513</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2263331913275976</v>
+        <v>0.05357929745336204</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.81869805088097</v>
+        <v>2.986645544149546</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181177</v>
+        <v>3.802245929181179</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.406941364649037</v>
+        <v>-4.361909506876892</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.194158617035647</v>
+        <v>1.212171360144505</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2263331913275976</v>
+        <v>0.05357929745336204</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.821491672412451</v>
+        <v>2.989439165681027</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.400788658596253</v>
+        <v>-4.355756800824108</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.197282047848419</v>
+        <v>1.215294790957277</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2201804852748133</v>
+        <v>0.05973200350614633</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.82584564443578</v>
+        <v>2.993793137704356</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890616</v>
+        <v>3.798239794890618</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.417597956746754</v>
+        <v>-4.37256609897461</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.189638805328329</v>
+        <v>1.207651548437187</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.236989783425315</v>
+        <v>0.04292270535564469</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.814840542285589</v>
+        <v>2.982788035554165</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798432</v>
+        <v>3.867362636798434</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.355299957970632</v>
+        <v>-4.310268100198487</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.280893558635599</v>
+        <v>1.298906301744456</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.236989783425315</v>
+        <v>0.04292270535564469</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.88117609608241</v>
+        <v>3.049123589350986</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992199</v>
+        <v>3.848729139992201</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.153509760305474</v>
+        <v>-4.10847790253333</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.07019051009106</v>
+        <v>1.088203253199918</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.03897159125616056</v>
+        <v>0.2409408975247991</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.708567883773301</v>
+        <v>2.876515377041876</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852429</v>
+        <v>3.84144481785243</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.080131663216738</v>
+        <v>-4.035099805444593</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.169831981248729</v>
+        <v>1.187844724357587</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.03440650583257598</v>
+        <v>0.3143189946135356</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.822884974348718</v>
+        <v>2.990832467617293</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319553</v>
+        <v>3.819063300319555</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.177872207841713</v>
+        <v>-4.132840350069568</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.145363499514783</v>
+        <v>1.163376242623641</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.0185172276995958</v>
+        <v>0.2984297164805554</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.827979143584973</v>
+        <v>2.995926636853549</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489392</v>
+        <v>3.831819032489394</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.354209967964642</v>
+        <v>-4.309178110192497</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.073364376290283</v>
+        <v>1.091377119399141</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1578205324233336</v>
+        <v>0.122091956357626</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.720712468335887</v>
+        <v>2.888659961604463</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397801</v>
+        <v>3.836411672397803</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.277787921532715</v>
+        <v>-4.191048752459328</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.102424812902982</v>
+        <v>1.137120480532337</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1578205324233336</v>
+        <v>0.122091956357626</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.719204086375816</v>
+        <v>2.887151579644391</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102497</v>
+        <v>3.836023391024971</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.233414789894146</v>
+        <v>-4.146675620820759</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.120036932993846</v>
+        <v>1.154732600623201</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.113447400784765</v>
+        <v>0.1664650879961946</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.745690832794393</v>
+        <v>2.913638326062969</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863229</v>
+        <v>3.821591150863232</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.225460819599374</v>
+        <v>-4.138721650525987</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.123218521111755</v>
+        <v>1.15791418874111</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.113447400784765</v>
+        <v>0.1664650879961946</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.745690832794393</v>
+        <v>2.913638326062969</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947588</v>
+        <v>3.83304018194759</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.177805089038318</v>
+        <v>-4.091065919964931</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.148662570363982</v>
+        <v>1.183358237993337</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.06579167022370935</v>
+        <v>0.2141208185572503</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.780666028158831</v>
+        <v>2.948613521427407</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326881</v>
+        <v>3.822707244326883</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.077286930539564</v>
+        <v>-3.990547761466177</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.193762207138209</v>
+        <v>1.228457874767563</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.03472648827504521</v>
+        <v>0.3146389770560049</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.845869296632809</v>
+        <v>3.013816789901385</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314556</v>
+        <v>3.828837911314558</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.137953520941952</v>
+        <v>-4.051214351868566</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.156250243453125</v>
+        <v>1.19094591108248</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.04697182844348846</v>
+        <v>0.2329406603374712</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.783604979077561</v>
+        <v>2.951552472346136</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690031</v>
+        <v>3.816866067690033</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.093115119333554</v>
+        <v>-4.006375950260168</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.178283306707113</v>
+        <v>1.212978974336468</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.04242839549861899</v>
+        <v>0.2374840932823407</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.790428741455111</v>
+        <v>2.958376234723687</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674315</v>
+        <v>3.817961388674317</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.193873755090552</v>
+        <v>-4.107134586017166</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.142140792035392</v>
+        <v>1.176836459664746</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1312539642256244</v>
+        <v>0.1486585245553352</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.741294339849986</v>
+        <v>2.909241833118561</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163224</v>
+        <v>3.826713779163226</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.149670918004651</v>
+        <v>-4.062931748931265</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.165701529397589</v>
+        <v>1.200397197026944</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.08705112713972396</v>
+        <v>0.1928613616412357</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.773695644629363</v>
+        <v>2.941643137897939</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022909</v>
+        <v>3.83822866302291</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.186649945668094</v>
+        <v>-4.099910776594709</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.14931991880146</v>
+        <v>1.184015586430814</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.05007722534839343</v>
+        <v>0.2298352634325662</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.794289986173409</v>
+        <v>2.962237479441985</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042143</v>
+        <v>3.863924114042145</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.206708024532935</v>
+        <v>-4.119968855459549</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.192544452438563</v>
+        <v>1.227240120067917</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.05007722534839343</v>
+        <v>0.2298352634325662</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.845537751356449</v>
+        <v>3.013485244625024</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078285</v>
+        <v>3.865367715078287</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.166777351355044</v>
+        <v>-4.080038182281659</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.206957426303973</v>
+        <v>1.241653093933326</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.01014655217050309</v>
+        <v>0.2697659366104566</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.867936859857436</v>
+        <v>3.035884353126012</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232403</v>
+        <v>3.864518876232404</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.115745258632517</v>
+        <v>-4.029006089559132</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.222318491631254</v>
+        <v>1.257014159260607</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.04088554055202487</v>
+        <v>0.3207980293329845</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.893504343729223</v>
+        <v>3.061451836997799</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162118</v>
+        <v>3.84257639416212</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.050521077505311</v>
+        <v>-3.963781908431926</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.265595568174841</v>
+        <v>1.300291235804194</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1061097216792305</v>
+        <v>0.3860222104601901</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.949826256498251</v>
+        <v>3.117773749766827</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639822</v>
+        <v>3.840090220639824</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.013094057434177</v>
+        <v>-3.926354888360792</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.276527348502575</v>
+        <v>1.311223016131928</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1113612597084122</v>
+        <v>0.3912737484893718</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.948938151615041</v>
+        <v>3.116885644883616</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749927</v>
+        <v>3.845198842749928</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.937055559933169</v>
+        <v>-3.946466544395501</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.308199539834218</v>
+        <v>1.304435146049285</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1667878751359986</v>
+        <v>0.402301093486791</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.983450913202833</v>
+        <v>3.124758844213308</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393553</v>
+        <v>3.828690479393554</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.883310745505964</v>
+        <v>-3.892721729968296</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.490255236626311</v>
+        <v>1.486490842841378</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1768511845764605</v>
+        <v>0.412364402927253</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.15004666988832</v>
+        <v>3.291354600898796</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714891</v>
+        <v>3.813251854714892</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.859519176899822</v>
+        <v>-3.868930161362154</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.619884773286585</v>
+        <v>1.616120379501652</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.2006427531826028</v>
+        <v>0.4361559715333952</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.284434520269823</v>
+        <v>3.425742451280299</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756016</v>
+        <v>3.814259761756018</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.833435092636014</v>
+        <v>-3.842846077098346</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.622026383005967</v>
+        <v>1.618261989221034</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.2006427531826028</v>
+        <v>0.4361559715333952</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.276142496283682</v>
+        <v>3.417450427294157</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654191</v>
+        <v>3.803426852654193</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.703142561706404</v>
+        <v>-3.712553546168736</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.672336590961591</v>
+        <v>1.668572197176658</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.4371783777103376</v>
+        <v>0.67269159606113</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.416257066584103</v>
+        <v>3.557564997594578</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717121</v>
+        <v>3.796293177717123</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.694250100313121</v>
+        <v>-3.703661084775453</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.693447981245696</v>
+        <v>1.689683587460762</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.4371783777103376</v>
+        <v>0.67269159606113</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.433811472310894</v>
+        <v>3.575119403321369</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702631</v>
+        <v>3.794453975702632</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.862726217282999</v>
+        <v>-3.872137201745331</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.617912581862328</v>
+        <v>1.614148188077395</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.4092305419937569</v>
+        <v>0.6447437603445493</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.408897818285529</v>
+        <v>3.550205749296005</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539973</v>
+        <v>3.795603100539974</v>
       </c>
       <c r="C1997" t="n">
         <v>3.144629190277137</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.164926688421415</v>
+        <v>-3.174337672883747</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.878302090594823</v>
+        <v>1.87453769680989</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.3388824826233461</v>
+        <v>0.5743957009741385</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.347958679851145</v>
+        <v>3.48926661086162</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389903</v>
+        <v>3.784700379389904</v>
       </c>
       <c r="C1998" t="n">
         <v>3.135293212774041</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.142205584738263</v>
+        <v>-3.151616569200595</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.878054554564989</v>
+        <v>1.874290160780056</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.3388824826233461</v>
+        <v>0.5743957009741385</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.338622702348049</v>
+        <v>3.479930633358525</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78323473053494</v>
+        <v>3.783234730534942</v>
       </c>
       <c r="C1999" t="n">
         <v>3.29419933862521</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.140480541448219</v>
+        <v>-3.149891525910551</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.037650697732175</v>
+        <v>2.033886303947242</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.3406075259133899</v>
+        <v>0.5761207442641822</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.498563854173244</v>
+        <v>3.63987178518372</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779962759401679</v>
+        <v>3.77996275940168</v>
       </c>
       <c r="C2000" t="n">
         <v>3.331277161118857</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.295261548226474</v>
+        <v>-3.304672532688806</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.01281611751452</v>
+        <v>2.009051723729587</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.3072398518589138</v>
+        <v>0.5427530702097061</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.515621072234206</v>
+        <v>3.656929003244681</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769472653557226</v>
+        <v>3.769472653557228</v>
       </c>
       <c r="C2001" t="n">
         <v>3.327952517108402</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.362521992248391</v>
+        <v>-3.371932976710723</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.982587295895298</v>
+        <v>1.978822902110365</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.2399794078369967</v>
+        <v>0.475492626187789</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.471940161810601</v>
+        <v>3.613248092821076</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766702530088382</v>
+        <v>3.766702530088383</v>
       </c>
       <c r="C2002" t="n">
         <v>3.337958670753144</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.340050458209559</v>
+        <v>-3.349461442671891</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.001582063155573</v>
+        <v>1.997817669370639</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.3756848926529679</v>
+        <v>0.6111981110037602</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.563369606344925</v>
+        <v>3.7046775373554</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768081101541375</v>
+        <v>3.768081101541377</v>
       </c>
       <c r="C2003" t="n">
         <v>3.522061802898103</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.476003466265875</v>
+        <v>-3.485414450728207</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.131303992078006</v>
+        <v>2.127539598293073</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.3756848926529679</v>
+        <v>0.6111981110037602</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.747472738489884</v>
+        <v>3.88878066950036</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743954539471688</v>
+        <v>3.74395453947169</v>
       </c>
       <c r="C2004" t="n">
         <v>3.514178497801097</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.498411584070747</v>
+        <v>-3.507822568533079</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.11445743985905</v>
+        <v>2.110693046074117</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.3756848926529679</v>
+        <v>0.6111981110037602</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.739589433392878</v>
+        <v>3.880897364403353</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719147660912297</v>
+        <v>3.719147660912299</v>
       </c>
       <c r="C2005" t="n">
         <v>3.516232497350734</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.61349104271109</v>
+        <v>-3.622902027173422</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.070479655952551</v>
+        <v>2.066715262167618</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.4076946833675302</v>
+        <v>0.6432079017183225</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.760849307371252</v>
+        <v>3.902157238381728</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.827904403490383</v>
+        <v>3.779043662043739</v>
       </c>
       <c r="C2006" t="n">
         <v>3.515864382084098</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.714858310411099</v>
+        <v>-3.663460155210377</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.029564633605911</v>
+        <v>2.050123895686199</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.4076946833675302</v>
+        <v>0.6201032074797568</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.760481192104616</v>
+        <v>3.887926306571952</v>
       </c>
     </row>
   </sheetData>
